--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -417,43 +429,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Actual Winner</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>46092</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,142 +493,562 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>46092</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.6986759429842281</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.4626511856295711</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.4361005220957239</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Orlando Magic</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Cleveland Cavaliers</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Orlando Magic</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E6" t="n">
         <v>0.710714006852612</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Orlando Magic</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>46092</v>
-      </c>
-      <c r="B4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.5589872319235494</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.4852893920007732</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.4852893920007732</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.4626511856295711</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Sacramento Kings</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Charlotte Hornets</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Charlotte Hornets</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E11" t="n">
         <v>0.4361005220957239</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Charlotte Hornets</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>46092</v>
-      </c>
-      <c r="B5" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.710714006852612</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.6986759429842281</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.6416335152753547</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8590492227065436</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Denver Nuggets</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0.4626511856295711</v>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7496280754313392</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Denver Nuggets</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>46092</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0.4852893920007732</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>46092</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0.6986759429842281</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.6468508031883885</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8470377309589494</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.2970138311682546</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8596300685545497</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.6543681885696864</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.6312136768470223</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
     </row>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,6 +463,11 @@
           <t>Actual Winner</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>gameId</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -491,6 +496,7 @@
           <t>New Orleans Pelicans</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -498,27 +504,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.6986759429842281</v>
+        <v>0.4852893920007732</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -547,6 +554,7 @@
           <t>Denver Nuggets</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -575,6 +583,7 @@
           <t>Charlotte Hornets</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -603,6 +612,7 @@
           <t>Orlando Magic</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -610,194 +620,213 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5589872319235494</v>
+        <v>0.6986759429842281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.4852893920007732</v>
+        <v>0.8590492191605033</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
-        </is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>22500957</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.4852893920007732</v>
+        <v>0.6416335120899616</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
-        </is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>22501111</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.4626511856295711</v>
+        <v>0.654368185331398</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
-        </is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>22500953</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.4361005220957239</v>
+        <v>0.8596300648781309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
-        </is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>22500956</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.710714006852612</v>
+        <v>0.2970138352607768</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
-        </is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>22500954</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.6986759429842281</v>
+        <v>0.8470377267810785</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
-        </is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>22500955</v>
       </c>
     </row>
     <row r="14">
@@ -806,26 +835,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.6416335152753547</v>
+        <v>0.6468508019870481</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
-        </is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>22500960</v>
       </c>
     </row>
     <row r="15">
@@ -834,27 +866,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.8590492227065436</v>
+        <v>0.6312136779711028</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -862,27 +895,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.7496280754313392</v>
+        <v>0.8590492227065436</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -890,27 +924,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.6468508031883885</v>
+        <v>0.6416335152753547</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -918,26 +953,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.8470377309589494</v>
+        <v>0.749628072689052</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
-        </is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>22500958</v>
       </c>
     </row>
     <row r="19">
@@ -946,27 +984,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.2970138311682546</v>
+        <v>0.7496280754313392</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -974,27 +1013,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.8596300685545497</v>
+        <v>0.6468508031883885</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1002,27 +1042,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.6543681885696864</v>
+        <v>0.8470377309589494</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1030,26 +1071,116 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.8596300685545497</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.2970138311682546</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.6543681885696864</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>Oklahoma City Thunder</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Boston Celtics</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Oklahoma City Thunder</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>0.6312136768470223</v>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="E25" t="n">
+        <v>0.6312136769140898</v>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>Oklahoma City Thunder</t>
         </is>
+      </c>
+      <c r="G25" t="n">
+        <v>22500959</v>
       </c>
     </row>
   </sheetData>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,177 +471,201 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5589872319235494</v>
+        <v>0.8590492246463678</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>22500957.0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4852893920007732</v>
+        <v>0.6312136768269763</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>22500959.0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.4626511856295711</v>
+        <v>0.6416335120899616</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>22501111.0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4361005220957239</v>
+        <v>0.654368185331398</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>22500953.0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.710714006852612</v>
+        <v>0.8596300648781309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>22500956.0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6986759429842281</v>
+        <v>0.6543681885696864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -649,29 +673,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.8590492191605033</v>
+        <v>0.8470377267810785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>22500957</v>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>22500955.0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -680,29 +706,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.6416335120899616</v>
+        <v>0.6468508019870481</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>22501111</v>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>22500960.0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -711,29 +739,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.654368185331398</v>
+        <v>0.749628072689052</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>22500953</v>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>22500958.0</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -742,445 +772,279 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.8596300648781309</v>
+        <v>0.2970138352607768</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>22500956</v>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>22500954.0</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.2970138352607768</v>
+        <v>0.3942169236533269</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>22500954</v>
+        <v>22500964</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.8470377267810785</v>
+        <v>0.730219433274207</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>22500955</v>
+        <v>22500968</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.6468508019870481</v>
+        <v>0.5861016864721887</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>22500960</v>
+        <v>22500966</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.6312136779711028</v>
+        <v>0.4188486482337365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>22500965</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8590492227065436</v>
+        <v>0.3162462892533334</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>22500962</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>Memphis Grizzlies</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.6416335152753547</v>
+        <v>0.695789951599302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>22500961</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.749628072689052</v>
+        <v>0.4189104333098274</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>22500958</v>
+        <v>22500963</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.7496280754313392</v>
+        <v>0.5696450348251237</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>46093</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>0.6468508031883885</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>46093</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>0.8470377309589494</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>46093</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Brooklyn Nets</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>0.8596300685545497</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>46093</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Indiana Pacers</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>0.2970138311682546</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>46093</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>0.6543681885696864</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>46093</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>0.6312136769140898</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>22500959</v>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>22500967</v>
       </c>
     </row>
   </sheetData>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.8590492246463678</v>
+        <v>0.859049225</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.6312136768269763</v>
+        <v>0.631213677</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.6416335120899616</v>
+        <v>0.641633512</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.654368185331398</v>
+        <v>0.654368185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8596300648781309</v>
+        <v>0.8596300650000001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6543681885696864</v>
+        <v>0.654368189</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.8470377267810785</v>
+        <v>0.847037727</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.6468508019870481</v>
+        <v>0.646850802</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.749628072689052</v>
+        <v>0.749628073</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.2970138352607768</v>
+        <v>0.297013835</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -805,29 +805,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.3942169236533269</v>
+        <v>0.730219433</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>22500964</v>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>22500968.0</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -836,29 +838,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.730219433274207</v>
+        <v>0.418848648</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>22500968</v>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>22500965.0</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -867,29 +871,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.5861016864721887</v>
+        <v>0.394216924</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>22500966</v>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>22500964.0</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -898,29 +904,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.4188486482337365</v>
+        <v>0.586101686</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>22500965</v>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>22500966.0</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -929,29 +937,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.3162462892533334</v>
+        <v>0.695789952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>22500962</v>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>22500961.0</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -960,29 +970,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.695789951599302</v>
+        <v>0.569645035</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>22500961</v>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>22500967.0</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -991,29 +1003,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.4189104333098274</v>
+        <v>0.316246289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>22500963</v>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>22500962.0</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1022,29 +1036,248 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.5696450348251237</v>
+        <v>0.418910433</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>22500967</v>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>22500963.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.5775021314620972</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>22500969</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8429240584373474</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>22500970</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.6524375677108765</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>22500973</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.8574886322021484</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>22500971</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.4993022978305817</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>22500972</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.6525467038154602</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>22500974</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.5777215957641602</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>22500975</v>
       </c>
     </row>
   </sheetData>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,48 +417,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Actual Winner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>gameId</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +491,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -536,7 +524,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -569,7 +557,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +590,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,7 +623,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -661,14 +649,10 @@
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,7 +685,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -734,7 +718,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -767,7 +751,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -800,484 +784,746 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.418910433</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>22500963.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.569645035</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>22500967.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.695789952</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>22500961.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.316246289</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>22500962.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.394216924</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>22500964.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.418848648</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>22500965.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>LA Clippers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Chicago Bulls</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>LA Clippers</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E18" t="n">
         <v>0.730219433</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>LA Clippers</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>22500968.0</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
+    <row r="19">
+      <c r="A19" s="1" t="n">
         <v>46094</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.586101686</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>22500966.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.5777215957641602</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>22500975.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.4993022978305817</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>22500972.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.8574886322021484</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>22500971.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.6525467038154602</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>22500974.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8429240584373474</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>22500970.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.5775021314620972</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>22500969.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.6524375677108765</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>22500973.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.5038461685180664</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>22500985</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>Dallas Mavericks</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>0.418848648</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>22500965.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.7718399167060852</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>22500988</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.6628966331481934</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>22500986</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.222200021147728</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>22500984</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>Houston Rockets</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>0.394216924</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>22500964.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>0.586101686</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>22500966.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.4305817782878876</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>22500989</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.5851534008979797</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>22500990</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.5979579091072083</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>22500983</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Memphis Grizzlies</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>0.695789952</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>22500961.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>0.569645035</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>22500967.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Indiana Pacers</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>0.316246289</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>22500962.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>0.418910433</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>22500963.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Brooklyn Nets</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>0.5775021314620972</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>22500969</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Milwaukee Bucks</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>0.8429240584373474</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>22500970</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Charlotte Hornets</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>0.6524375677108765</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>22500973</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>0.8574886322021484</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>22500971</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>0.4993022978305817</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>22500972</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>0.6525467038154602</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>22500974</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Sacramento Kings</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>0.5777215957641602</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Sacramento Kings</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>22500975</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6791099905967712</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>22500987</v>
       </c>
     </row>
   </sheetData>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -789,30 +789,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.418910433</v>
+        <v>0.316246289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22500963.0</t>
+          <t>22500962.0</t>
         </is>
       </c>
     </row>
@@ -822,30 +822,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.569645035</v>
+        <v>0.695789952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>22500967.0</t>
+          <t>22500961.0</t>
         </is>
       </c>
     </row>
@@ -855,30 +855,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.695789952</v>
+        <v>0.418910433</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22500961.0</t>
+          <t>22500963.0</t>
         </is>
       </c>
     </row>
@@ -888,30 +888,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.316246289</v>
+        <v>0.569645035</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>22500962.0</t>
+          <t>22500967.0</t>
         </is>
       </c>
     </row>
@@ -921,30 +921,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.394216924</v>
+        <v>0.418848648</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22500964.0</t>
+          <t>22500965.0</t>
         </is>
       </c>
     </row>
@@ -954,30 +954,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.418848648</v>
+        <v>0.730219433</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22500965.0</t>
+          <t>22500968.0</t>
         </is>
       </c>
     </row>
@@ -987,30 +987,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.730219433</v>
+        <v>0.586101686</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>22500968.0</t>
+          <t>22500966.0</t>
         </is>
       </c>
     </row>
@@ -1020,30 +1020,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.586101686</v>
+        <v>0.394216924</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22500966.0</t>
+          <t>22500964.0</t>
         </is>
       </c>
     </row>
@@ -1053,30 +1053,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.5777215957641602</v>
+        <v>0.652546704</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>22500975.0</t>
+          <t>22500974.0</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.4993022978305817</v>
+        <v>0.499302298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.8574886322021484</v>
+        <v>0.857488632</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1152,30 +1152,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.6525467038154602</v>
+        <v>0.5777215959999999</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>22500974.0</t>
+          <t>22500975.0</t>
         </is>
       </c>
     </row>
@@ -1185,30 +1185,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.8429240584373474</v>
+        <v>0.652437568</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>22500970.0</t>
+          <t>22500973.0</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.5775021314620972</v>
+        <v>0.577502131</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1251,30 +1251,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.6524375677108765</v>
+        <v>0.842924058</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>22500973.0</t>
+          <t>22500970.0</t>
         </is>
       </c>
     </row>
@@ -1284,29 +1284,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.5038461685180664</v>
+        <v>0.1696883141994476</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>22500985</v>
+        <v>22500984</v>
       </c>
     </row>
     <row r="28">
@@ -1315,29 +1315,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.7718399167060852</v>
+        <v>0.3228119611740112</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>22500988</v>
+        <v>22500989</v>
       </c>
     </row>
     <row r="29">
@@ -1346,29 +1346,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.6628966331481934</v>
+        <v>0.4246545135974884</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>22500986</v>
+        <v>22500990</v>
       </c>
     </row>
     <row r="30">
@@ -1377,29 +1377,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.222200021147728</v>
+        <v>0.628429651260376</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>22500984</v>
+        <v>22500983</v>
       </c>
     </row>
     <row r="31">
@@ -1408,29 +1408,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.4305817782878876</v>
+        <v>0.2950863242149353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>22500989</v>
+        <v>22500985</v>
       </c>
     </row>
     <row r="32">
@@ -1439,29 +1439,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.5851534008979797</v>
+        <v>0.8141456246376038</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>22500990</v>
+        <v>22500988</v>
       </c>
     </row>
     <row r="33">
@@ -1470,29 +1470,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.5979579091072083</v>
+        <v>0.7310704588890076</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>22500983</v>
+        <v>22500986</v>
       </c>
     </row>
     <row r="34">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.6791099905967712</v>
+        <v>0.7086217999458313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,30 +789,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.316246289</v>
+        <v>0.569645035</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22500962.0</t>
+          <t>22500967.0</t>
         </is>
       </c>
     </row>
@@ -888,30 +888,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.569645035</v>
+        <v>0.316246289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>22500967.0</t>
+          <t>22500962.0</t>
         </is>
       </c>
     </row>
@@ -921,30 +921,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.418848648</v>
+        <v>0.394216924</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22500965.0</t>
+          <t>22500964.0</t>
         </is>
       </c>
     </row>
@@ -1020,30 +1020,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.394216924</v>
+        <v>0.418848648</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22500964.0</t>
+          <t>22500965.0</t>
         </is>
       </c>
     </row>
@@ -1086,30 +1086,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.499302298</v>
+        <v>0.5777215959999999</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22500972.0</t>
+          <t>22500975.0</t>
         </is>
       </c>
     </row>
@@ -1119,30 +1119,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.857488632</v>
+        <v>0.499302298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>22500971.0</t>
+          <t>22500972.0</t>
         </is>
       </c>
     </row>
@@ -1152,30 +1152,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.5777215959999999</v>
+        <v>0.652437568</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>22500975.0</t>
+          <t>22500973.0</t>
         </is>
       </c>
     </row>
@@ -1185,30 +1185,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.652437568</v>
+        <v>0.842924058</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>22500973.0</t>
+          <t>22500970.0</t>
         </is>
       </c>
     </row>
@@ -1251,30 +1251,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.842924058</v>
+        <v>0.857488632</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>22500970.0</t>
+          <t>22500971.0</t>
         </is>
       </c>
     </row>
@@ -1284,29 +1284,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.1696883141994476</v>
+        <v>0.814145625</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>22500984</v>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>22500988.0</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1315,29 +1317,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.3228119611740112</v>
+        <v>0.731070459</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>22500989</v>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>22500986.0</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -1346,29 +1350,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.4246545135974884</v>
+        <v>0.169688314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>22500990</v>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>22500984.0</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1377,29 +1383,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.628429651260376</v>
+        <v>0.322811961</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>22500983</v>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>22500989.0</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -1408,29 +1416,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.2950863242149353</v>
+        <v>0.424654514</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>22500985</v>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>22500990.0</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1439,29 +1449,31 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.8141456246376038</v>
+        <v>0.628429651</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>22500988</v>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>22500983.0</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1470,29 +1482,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.7310704588890076</v>
+        <v>0.295086324</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>22500986</v>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>22500985.0</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -1515,15 +1529,265 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.7086217999458313</v>
+        <v>0.7086218</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>Chicago Bulls</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>22500987</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>22500987.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.1621145457029343</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>22500993</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.5457360744476318</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>22500991</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7550305724143982</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>22500994</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.3026701211929321</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>22500998</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.3743271231651306</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>22500995</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.4343498349189758</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>22500996</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.2116377651691437</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>22500992</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6574461460113525</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>22500997</v>
       </c>
     </row>
   </sheetData>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -805,30 +805,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.316246289</v>
+        <v>0.569645035</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22500962</t>
+          <t>22500967</t>
         </is>
       </c>
     </row>
@@ -838,30 +838,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.695789952</v>
+        <v>0.316246289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>22500961</t>
+          <t>22500962</t>
         </is>
       </c>
     </row>
@@ -871,30 +871,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.418910433</v>
+        <v>0.695789952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22500963</t>
+          <t>22500961</t>
         </is>
       </c>
     </row>
@@ -904,30 +904,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.569645035</v>
+        <v>0.418910433</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>22500967</t>
+          <t>22500963</t>
         </is>
       </c>
     </row>
@@ -1333,30 +1333,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.295086324</v>
+        <v>0.424654514</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22500985</t>
+          <t>22500990</t>
         </is>
       </c>
     </row>
@@ -1366,30 +1366,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.424654514</v>
+        <v>0.628429651</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22500990</t>
+          <t>22500983</t>
         </is>
       </c>
     </row>
@@ -1399,30 +1399,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.628429651</v>
+        <v>0.295086324</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>22500983</t>
+          <t>22500985</t>
         </is>
       </c>
     </row>
@@ -1432,30 +1432,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.169688314</v>
+        <v>0.814145625</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>22500984</t>
+          <t>22500988</t>
         </is>
       </c>
     </row>
@@ -1465,30 +1465,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.731070459</v>
+        <v>0.322811961</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>22500986</t>
+          <t>22500989</t>
         </is>
       </c>
     </row>
@@ -1498,30 +1498,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.814145625</v>
+        <v>0.169688314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>22500988</t>
+          <t>22500984</t>
         </is>
       </c>
     </row>
@@ -1531,30 +1531,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.322811961</v>
+        <v>0.731070459</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>22500989</t>
+          <t>22500986</t>
         </is>
       </c>
     </row>
@@ -2083,6 +2083,468 @@
       <c r="G50" t="inlineStr">
         <is>
           <t>22501007</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46100.79166666666</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0.5466242432594299</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>22501008</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46100.79166666666</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0.156985729932785</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>22501009</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46100.83333333334</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.6886867880821228</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>22501012</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46100.83333333334</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.499740868806839</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>22501010</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46100.83333333334</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.462356299161911</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>22501011</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46100.83333333334</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.5898500084877014</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>22501013</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46100.875</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0.5481546521186829</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>22501014</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46100.91666666666</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.7287593483924866</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>22501015</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46101.8125</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.3670358955860138</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>22501016</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46101.8125</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.4748657643795013</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>22501017</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46101.83333333334</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.275350421667099</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>22501019</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>46101.83333333334</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0.336741179227829</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>22501020</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46101.83333333334</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0.2312954813241959</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>22501018</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46101.875</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.5892381072044373</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>22501021</t>
         </is>
       </c>
     </row>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,48 +417,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Actual Winner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>gameId</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +491,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -536,7 +524,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -569,7 +557,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +590,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,7 +623,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -661,14 +649,10 @@
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,7 +685,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -734,7 +718,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -767,7 +751,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -800,502 +784,502 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.586101686</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>22500966</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.730219433</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>22500968</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.418848648</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>22500965</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.394216924</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>22500964</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.695789952</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>22500961</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.316246289</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>22500962</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Utah Jazz</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E18" t="n">
         <v>0.569645035</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>22500967</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
+    <row r="19">
+      <c r="A19" s="1" t="n">
         <v>46094</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Indiana Pacers</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>0.316246289</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>22500962</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Memphis Grizzlies</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>0.695789952</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>22500961</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Toronto Raptors</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Phoenix Suns</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Phoenix Suns</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E19" t="n">
         <v>0.418910433</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Toronto Raptors</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>22500963</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>0.418848648</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>22500965</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B17" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.842924058</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>22500970</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.577502131</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>22500969</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.499302298</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>22500972</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.652437568</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>22500973</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.652546704</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>22500974</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>LA Clippers</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>LA Clippers</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>0.730219433</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>22500968</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>0.586101686</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>22500966</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>0.394216924</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>22500964</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="E25" t="n">
+        <v>0.5777215959999999</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>22500975</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
         <v>46095</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Sacramento Kings</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>0.5777215959999999</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Sacramento Kings</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>22500975</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>0.652546704</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>22500974</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Boston Celtics</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Washington Wizards</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Boston Celtics</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E26" t="n">
         <v>0.857488632</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Boston Celtics</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>22500971</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>0.499302298</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>22500972</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Brooklyn Nets</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>0.577502131</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>22500969</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Milwaukee Bucks</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>0.842924058</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>22500970</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Charlotte Hornets</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>0.652437568</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>22500973</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>46097</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1328,7 +1312,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>46097</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1361,7 +1345,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>46097</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -1394,7 +1378,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>46097</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -1427,7 +1411,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>46097</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -1460,7 +1444,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>46097</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -1493,7 +1477,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>46097</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -1526,7 +1510,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>46097</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -1559,106 +1543,106 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.657446146</v>
+        <v>0.266292274</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>22500997</t>
+          <t>22500995</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.513797641</v>
+        <v>0.5540216569999999</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>22500996</t>
+          <t>22500991</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.388431966</v>
+        <v>0.155862674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>22500998</t>
+          <t>22500993</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -1691,106 +1675,106 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.155862674</v>
+        <v>0.388431966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>22500993</t>
+          <t>22500998</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.266292274</v>
+        <v>0.513797641</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>22500995</t>
+          <t>22500996</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.5540216569999999</v>
+        <v>0.657446146</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>22500991</t>
+          <t>22500997</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>46099.79166666666</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -1823,7 +1807,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>46099.8125</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -1856,7 +1840,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>46099.8125</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -1889,7 +1873,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>46099.83333333334</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -1922,7 +1906,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>46099.83333333334</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -1955,7 +1939,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>46099.83333333334</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -1988,7 +1972,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>46099.85416666666</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -2021,7 +2005,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>46099.85416666666</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -2054,7 +2038,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>46099.89583333334</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -2087,7 +2071,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>46100.79166666666</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -2120,7 +2104,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>46100.79166666666</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -2153,139 +2137,139 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>46100.83333333334</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.462356299161911</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>22501011</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>46100.83333333334</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.5898500084877014</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>22501013</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>46100.83333333334</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>New Orleans Pelicans</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>LA Clippers</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>New Orleans Pelicans</t>
         </is>
       </c>
-      <c r="E53" t="n">
+      <c r="E55" t="n">
         <v>0.6886867880821228</v>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>New Orleans Pelicans</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>22501012</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
+    <row r="56">
+      <c r="A56" s="1" t="n">
         <v>46100.83333333334</v>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Miami Heat</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Los Angeles Lakers</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Los Angeles Lakers</t>
         </is>
       </c>
-      <c r="E54" t="n">
+      <c r="E56" t="n">
         <v>0.499740868806839</v>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Los Angeles Lakers</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>22501010</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>46100.83333333334</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>0.462356299161911</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>22501011</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>46100.83333333334</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>0.5898500084877014</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>22501013</t>
-        </is>
-      </c>
-    </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>46100.875</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -2318,7 +2302,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>46100.91666666666</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -2351,7 +2335,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>46101.8125</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -2384,7 +2368,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>46101.8125</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -2417,7 +2401,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>46101.83333333334</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -2450,7 +2434,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>46101.83333333334</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -2483,7 +2467,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>46101.83333333334</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -2516,7 +2500,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>46101.875</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -2545,6 +2529,336 @@
       <c r="G64" t="inlineStr">
         <is>
           <t>22501021</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>46102.70833333334</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0.3804706037044525</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>22501022</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>46102.79166666666</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.8523814678192139</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>22501023</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>46102.79166666666</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0.5733375549316406</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>22501024</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>46102.79166666666</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0.4314593970775604</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>22501025</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>46102.83333333334</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.8768197298049927</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>22501026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>46102.83333333334</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0.4926076531410217</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>22501027</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>46102.83333333334</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0.8616619110107422</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>22501028</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>46102.85416666666</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0.4836676120758057</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>22501029</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>46102.89583333334</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0.443777859210968</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>22501030</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>46102.91666666666</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0.7414435744285583</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>22501031</t>
         </is>
       </c>
     </row>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,30 +789,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.586101686</v>
+        <v>0.569645035</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22500966</t>
+          <t>22500967</t>
         </is>
       </c>
     </row>
@@ -822,30 +822,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.730219433</v>
+        <v>0.316246289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>22500968</t>
+          <t>22500962</t>
         </is>
       </c>
     </row>
@@ -855,30 +855,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.418848648</v>
+        <v>0.695789952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22500965</t>
+          <t>22500961</t>
         </is>
       </c>
     </row>
@@ -888,30 +888,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.394216924</v>
+        <v>0.418910433</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>22500964</t>
+          <t>22500963</t>
         </is>
       </c>
     </row>
@@ -921,30 +921,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.695789952</v>
+        <v>0.418848648</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22500961</t>
+          <t>22500965</t>
         </is>
       </c>
     </row>
@@ -954,30 +954,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.316246289</v>
+        <v>0.730219433</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22500962</t>
+          <t>22500968</t>
         </is>
       </c>
     </row>
@@ -987,30 +987,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.569645035</v>
+        <v>0.586101686</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>22500967</t>
+          <t>22500966</t>
         </is>
       </c>
     </row>
@@ -1020,30 +1020,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.418910433</v>
+        <v>0.394216924</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22500963</t>
+          <t>22500964</t>
         </is>
       </c>
     </row>
@@ -1053,30 +1053,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.842924058</v>
+        <v>0.5777215959999999</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>22500970</t>
+          <t>22500975</t>
         </is>
       </c>
     </row>
@@ -1086,30 +1086,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.577502131</v>
+        <v>0.652546704</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22500969</t>
+          <t>22500974</t>
         </is>
       </c>
     </row>
@@ -1119,30 +1119,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.499302298</v>
+        <v>0.652437568</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>22500972</t>
+          <t>22500973</t>
         </is>
       </c>
     </row>
@@ -1152,30 +1152,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.652437568</v>
+        <v>0.857488632</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>22500973</t>
+          <t>22500971</t>
         </is>
       </c>
     </row>
@@ -1185,30 +1185,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.652546704</v>
+        <v>0.577502131</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>22500974</t>
+          <t>22500969</t>
         </is>
       </c>
     </row>
@@ -1218,30 +1218,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.5777215959999999</v>
+        <v>0.842924058</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>22500975</t>
+          <t>22500970</t>
         </is>
       </c>
     </row>
@@ -1251,30 +1251,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.857488632</v>
+        <v>0.499302298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>22500971</t>
+          <t>22500972</t>
         </is>
       </c>
     </row>
@@ -1548,30 +1548,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.266292274</v>
+        <v>0.388431966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>22500995</t>
+          <t>22500998</t>
         </is>
       </c>
     </row>
@@ -1581,30 +1581,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.5540216569999999</v>
+        <v>0.657446146</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>22500991</t>
+          <t>22500997</t>
         </is>
       </c>
     </row>
@@ -1614,30 +1614,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.155862674</v>
+        <v>0.278542638</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>22500993</t>
+          <t>22500992</t>
         </is>
       </c>
     </row>
@@ -1647,30 +1647,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.278542638</v>
+        <v>0.513797641</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>22500992</t>
+          <t>22500996</t>
         </is>
       </c>
     </row>
@@ -1680,30 +1680,30 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.388431966</v>
+        <v>0.5540216569999999</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>22500998</t>
+          <t>22500991</t>
         </is>
       </c>
     </row>
@@ -1713,30 +1713,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.513797641</v>
+        <v>0.266292274</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>22500996</t>
+          <t>22500995</t>
         </is>
       </c>
     </row>
@@ -1746,30 +1746,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.657446146</v>
+        <v>0.155862674</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>22500997</t>
+          <t>22500993</t>
         </is>
       </c>
     </row>
@@ -1977,30 +1977,30 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.1570685207843781</v>
+        <v>0.494267612695694</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>22501006</t>
+          <t>22500651</t>
         </is>
       </c>
     </row>
@@ -2010,30 +2010,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.494267612695694</v>
+        <v>0.1570685207843781</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>22500651</t>
+          <t>22501006</t>
         </is>
       </c>
     </row>
@@ -2340,30 +2340,30 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.3670358955860138</v>
+        <v>0.4748657643795013</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>22501016</t>
+          <t>22501017</t>
         </is>
       </c>
     </row>
@@ -2373,30 +2373,30 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.4748657643795013</v>
+        <v>0.3670358955860138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>22501017</t>
+          <t>22501016</t>
         </is>
       </c>
     </row>
@@ -2670,30 +2670,30 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.8768197298049927</v>
+        <v>0.8616619110107422</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>22501026</t>
+          <t>22501028</t>
         </is>
       </c>
     </row>
@@ -2736,30 +2736,30 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.8616619110107422</v>
+        <v>0.8768197298049927</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>22501028</t>
+          <t>22501026</t>
         </is>
       </c>
     </row>
@@ -2859,6 +2859,171 @@
       <c r="G74" t="inlineStr">
         <is>
           <t>22501031</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>46103.70833333334</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0.6782870292663574</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>22501032</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>46103.75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0.6460906267166138</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>22501033</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>46103.8125</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0.8850165605545044</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>22501034</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>46103.83333333334</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0.7512719631195068</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>22501035</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>46103.875</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0.5605062246322632</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>22501036</t>
         </is>
       </c>
     </row>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -417,48 +429,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Actual Winner</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>gameId</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,7 +503,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -524,7 +536,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,7 +569,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -590,7 +602,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -623,7 +635,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -649,10 +661,14 @@
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -685,7 +701,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -718,7 +734,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -751,7 +767,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -784,370 +800,370 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.394216924</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>22500964</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.586101686</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>22500966</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.730219433</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>22500968</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.418848648</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>22500965</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Utah Jazz</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E16" t="n">
         <v>0.569645035</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>22500967</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
+    <row r="17">
+      <c r="A17" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.695789952</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>22500961</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>Indiana Pacers</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>New York Knicks</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>New York Knicks</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E18" t="n">
         <v>0.316246289</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>New York Knicks</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>22500962</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
+    <row r="19">
+      <c r="A19" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Memphis Grizzlies</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>0.695789952</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>22500961</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Toronto Raptors</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Phoenix Suns</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Phoenix Suns</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E19" t="n">
         <v>0.418910433</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Toronto Raptors</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>22500963</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>0.418848648</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>22500965</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>0.730219433</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>22500968</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>0.586101686</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>22500966</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>0.394216924</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>22500964</t>
-        </is>
-      </c>
-    </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>46095</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.5777215959999999</v>
+        <v>0.842924058</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>22500975</t>
+          <t>22500970</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>46095</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.652546704</v>
+        <v>0.499302298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22500974</t>
+          <t>22500972</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>46095</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.652437568</v>
+        <v>0.577502131</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>22500973</t>
+          <t>22500969</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46095</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1180,370 +1196,370 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46095</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.652437568</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>22500973</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.652546704</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>22500974</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.5777215959999999</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>22500975</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.169688314</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>22500984</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.322811961</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>22500989</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.814145625</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>22500988</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.731070459</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>22500986</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.628429651</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>22500983</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.424654514</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>22500990</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.7086218</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>22500987</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>Brooklyn Nets</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>0.577502131</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>22500969</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Milwaukee Bucks</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>0.842924058</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>22500970</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>0.499302298</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>22500972</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Memphis Grizzlies</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>0.7086218</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>22500987</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>0.424654514</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>22500990</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>0.628429651</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>22500983</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Brooklyn Nets</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="E34" t="n">
         <v>0.295086324</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>22500985</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>0.814145625</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>22500988</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>0.322811961</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>22500989</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>0.169688314</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>22500984</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>0.731070459</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>22500986</t>
-        </is>
-      </c>
-    </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>46098</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -1576,7 +1592,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>46098</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -1609,7 +1625,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>46098</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -1642,7 +1658,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>46098</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -1675,7 +1691,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>46098</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -1708,7 +1724,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>46098</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -1741,7 +1757,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>46098</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -1774,7 +1790,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>46099.79166666666</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -1807,172 +1823,172 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>46099.8125</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.2439689189195633</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>22501001</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46099.8125</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>Brooklyn Nets</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Oklahoma City Thunder</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Oklahoma City Thunder</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="E44" t="n">
         <v>0.2842900454998016</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Oklahoma City Thunder</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>22501000</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>46099.8125</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Indiana Pacers</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>0.2439689189195633</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>22501001</t>
-        </is>
-      </c>
-    </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>46099.83333333334</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.5324534177780151</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>22501005</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46099.83333333334</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>Chicago Bulls</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Toronto Raptors</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Chicago Bulls</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="E46" t="n">
         <v>0.5209299325942993</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Toronto Raptors</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>22501002</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
+    <row r="47">
+      <c r="A47" s="2" t="n">
         <v>46099.83333333334</v>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Minnesota Timberwolves</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Utah Jazz</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Minnesota Timberwolves</t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="E47" t="n">
         <v>0.6554064154624939</v>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Minnesota Timberwolves</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>22501004</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>46099.83333333334</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>0.5324534177780151</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>22501005</t>
-        </is>
-      </c>
-    </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>46099.85416666666</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -2005,7 +2021,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>46099.85416666666</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -2038,7 +2054,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>46099.89583333334</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -2071,7 +2087,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>46100.79166666666</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -2104,7 +2120,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>46100.79166666666</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -2137,139 +2153,139 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>46100.83333333334</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.6886867880821228</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>22501012</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46100.83333333334</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.499740868806839</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>22501010</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46100.83333333334</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>Chicago Bulls</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Cleveland Cavaliers</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Cleveland Cavaliers</t>
         </is>
       </c>
-      <c r="E53" t="n">
+      <c r="E55" t="n">
         <v>0.462356299161911</v>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Cleveland Cavaliers</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>22501011</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
+    <row r="56">
+      <c r="A56" s="2" t="n">
         <v>46100.83333333334</v>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Phoenix Suns</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="E54" t="n">
+      <c r="E56" t="n">
         <v>0.5898500084877014</v>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>22501013</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>46100.83333333334</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>0.6886867880821228</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>22501012</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>46100.83333333334</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>0.499740868806839</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>22501010</t>
-        </is>
-      </c>
-    </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>46100.875</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -2302,7 +2318,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>46100.91666666666</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -2335,7 +2351,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>46101.8125</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -2368,7 +2384,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>46101.8125</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -2401,7 +2417,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>46101.83333333334</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -2434,7 +2450,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>46101.83333333334</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -2467,7 +2483,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>46101.83333333334</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -2500,7 +2516,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>46101.875</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -2533,7 +2549,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>46102.70833333334</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -2566,40 +2582,40 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46102.79166666666</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.8523814678192139</v>
+        <v>0.4314593970775604</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>22501023</t>
+          <t>22501025</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46102.79166666666</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -2632,40 +2648,40 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46102.79166666666</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.4314593970775604</v>
+        <v>0.8523814678192139</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>22501025</t>
+          <t>22501023</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46102.83333333334</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -2698,7 +2714,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46102.83333333334</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -2731,7 +2747,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46102.83333333334</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -2764,7 +2780,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46102.85416666666</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -2797,7 +2813,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46102.89583333334</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -2830,7 +2846,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46102.91666666666</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -2863,7 +2879,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>46103.70833333334</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -2896,7 +2912,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>46103.75</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -2929,7 +2945,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>46103.8125</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -2962,7 +2978,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>46103.83333333334</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -2995,7 +3011,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>46103.875</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -3024,6 +3040,336 @@
       <c r="G79" t="inlineStr">
         <is>
           <t>22501036</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46104.79166666666</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0.6078159809112549</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>22501038</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46104.79166666666</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0.7137834429740906</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>22501039</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46104.79166666666</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0.2557961344718933</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>22501040</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46104.79166666666</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0.5200976729393005</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>22501041</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>46104.8125</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0.8431744575500488</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>22501037</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46104.83333333334</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0.5208929777145386</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>22501042</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46104.875</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0.3560488522052765</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>22501043</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46104.89583333334</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0.6753662824630737</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>22501044</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46104.91666666666</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0.7495328187942505</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>22501045</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46104.9375</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0.7013514041900635</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>22501046</t>
         </is>
       </c>
     </row>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,48 +417,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Actual Winner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>gameId</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +491,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -536,7 +524,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -569,7 +557,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +590,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,7 +623,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -661,14 +649,10 @@
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,7 +685,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -734,7 +718,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -767,7 +751,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -800,370 +784,370 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.418910433</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>22500963</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.316246289</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>22500962</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.695789952</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>22500961</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.569645035</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>22500967</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>Houston Rockets</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>New Orleans Pelicans</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>New Orleans Pelicans</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E16" t="n">
         <v>0.394216924</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Houston Rockets</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>22500964</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
+    <row r="17">
+      <c r="A17" s="1" t="n">
         <v>46094</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.730219433</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>22500968</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>Golden State Warriors</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Minnesota Timberwolves</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Golden State Warriors</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E18" t="n">
         <v>0.586101686</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Minnesota Timberwolves</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>22500966</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
+    <row r="19">
+      <c r="A19" s="1" t="n">
         <v>46094</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.418848648</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>22500965</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.652546704</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>22500974</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>LA Clippers</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>LA Clippers</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>0.730219433</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>22500968</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>0.418848648</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>22500965</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>0.569645035</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>22500967</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Memphis Grizzlies</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>0.695789952</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>22500961</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Indiana Pacers</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>0.316246289</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>22500962</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>0.418910433</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>22500963</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="E21" t="n">
+        <v>0.5777215959999999</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>22500975</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
         <v>46095</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Milwaukee Bucks</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>0.842924058</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>22500970</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>0.499302298</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>22500972</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>46095</v>
-      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.577502131</v>
+        <v>0.652437568</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>22500969</t>
+          <t>22500973</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>46095</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1196,370 +1180,370 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>46095</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.577502131</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>22500969</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.499302298</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>22500972</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.842924058</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>22500970</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.7086218</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>22500987</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Charlotte Hornets</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>0.652437568</v>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="E28" t="n">
+        <v>0.424654514</v>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>22500973</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B25" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>22500990</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.628429651</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>22500983</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.295086324</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>22500985</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.814145625</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>22500988</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>Los Angeles Lakers</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Los Angeles Lakers</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>0.652546704</v>
-      </c>
-      <c r="F25" t="inlineStr">
+      <c r="E32" t="n">
+        <v>0.322811961</v>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>Los Angeles Lakers</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>22500974</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Sacramento Kings</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>0.5777215959999999</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Sacramento Kings</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>22500975</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>22500989</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
         <v>46097</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Washington Wizards</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Golden State Warriors</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Golden State Warriors</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E33" t="n">
         <v>0.169688314</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Golden State Warriors</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>22500984</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
+    <row r="34">
+      <c r="A34" s="1" t="n">
         <v>46097</v>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>0.322811961</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>22500989</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>0.814145625</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>22500988</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B30" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Boston Celtics</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Phoenix Suns</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Boston Celtics</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="E34" t="n">
         <v>0.731070459</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Boston Celtics</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>22500986</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>0.628429651</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>22500983</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>0.424654514</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>22500990</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Memphis Grizzlies</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>0.7086218</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>22500987</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Brooklyn Nets</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>0.295086324</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>22500985</t>
-        </is>
-      </c>
-    </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -1592,7 +1576,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -1625,7 +1609,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -1658,7 +1642,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -1691,7 +1675,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -1724,7 +1708,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -1757,7 +1741,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -1790,7 +1774,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>46099.79166666666</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -1823,172 +1807,172 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>46099.8125</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.2842900454998016</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>22501000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>46099.8125</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>Indiana Pacers</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="E44" t="n">
         <v>0.2439689189195633</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>22501001</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>46099.8125</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Brooklyn Nets</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>0.2842900454998016</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>22501000</t>
-        </is>
-      </c>
-    </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>46099.83333333334</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.5209299325942993</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>22501002</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>46099.83333333334</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.6554064154624939</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>22501004</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46099.83333333334</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>New Orleans Pelicans</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>LA Clippers</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>New Orleans Pelicans</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="E47" t="n">
         <v>0.5324534177780151</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>New Orleans Pelicans</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>22501005</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>46099.83333333334</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>0.5209299325942993</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>22501002</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>46099.83333333334</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>0.6554064154624939</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>22501004</t>
-        </is>
-      </c>
-    </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>46099.85416666666</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -2021,7 +2005,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>46099.85416666666</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -2054,7 +2038,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>46099.89583333334</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -2087,7 +2071,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>46100.79166666666</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -2120,7 +2104,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>46100.79166666666</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -2153,7 +2137,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>46100.83333333334</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -2186,7 +2170,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>46100.83333333334</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -2219,7 +2203,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>46100.83333333334</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -2252,7 +2236,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>46100.83333333334</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -2285,7 +2269,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>46100.875</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -2318,7 +2302,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>46100.91666666666</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -2351,7 +2335,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>46101.8125</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -2384,7 +2368,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>46101.8125</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -2417,7 +2401,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>46101.83333333334</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -2450,7 +2434,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>46101.83333333334</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -2483,7 +2467,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>46101.83333333334</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -2516,7 +2500,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>46101.875</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -2549,7 +2533,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>46102.70833333334</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -2582,7 +2566,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>46102.79166666666</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -2615,7 +2599,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>46102.79166666666</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -2648,7 +2632,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>46102.79166666666</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -2681,40 +2665,40 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>46102.83333333334</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.8616619110107422</v>
+        <v>0.8768197298049927</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>22501028</t>
+          <t>22501026</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>46102.83333333334</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -2747,40 +2731,40 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>46102.83333333334</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.8768197298049927</v>
+        <v>0.8616619110107422</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>22501026</t>
+          <t>22501028</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>46102.85416666666</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -2813,7 +2797,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>46102.89583333334</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -2846,7 +2830,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>46102.91666666666</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -2879,7 +2863,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>46103.70833333334</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -2912,7 +2896,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>46103.75</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -2945,7 +2929,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>46103.8125</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -2978,7 +2962,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>46103.83333333334</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -3011,7 +2995,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>46103.875</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -3044,139 +3028,139 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>46104.79166666666</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0.5200976729393005</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>22501041</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>46104.79166666666</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0.2557961344718933</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>22501040</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46104.79166666666</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0.7137834429740906</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>22501039</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>46104.79166666666</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Los Angeles Lakers</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="E80" t="n">
+      <c r="E83" t="n">
         <v>0.6078159809112549</v>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>22501038</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
-        <v>46104.79166666666</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Indiana Pacers</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>0.7137834429740906</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Indiana Pacers</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>22501039</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
-        <v>46104.79166666666</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>0.2557961344718933</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>22501040</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
-        <v>46104.79166666666</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>0.5200976729393005</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>22501041</t>
-        </is>
-      </c>
-    </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>46104.8125</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -3209,7 +3193,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>46104.83333333334</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -3242,7 +3226,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>46104.875</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -3275,7 +3259,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>46104.89583333334</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -3308,7 +3292,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>46104.91666666666</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -3341,7 +3325,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>46104.9375</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -3370,6 +3354,138 @@
       <c r="G89" t="inlineStr">
         <is>
           <t>22501046</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>46105.79166666666</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0.7356671094894409</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>22501047</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>46105.8125</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>0.7157652378082275</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>22501048</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>46105.83333333334</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0.7073813676834106</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>22501049</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>46105.95833333334</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0.4800166189670563</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>22501050</t>
         </is>
       </c>
     </row>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,30 +789,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.418910433</v>
+        <v>0.418848648</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22500963</t>
+          <t>22500965</t>
         </is>
       </c>
     </row>
@@ -822,30 +822,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.316246289</v>
+        <v>0.586101686</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>22500962</t>
+          <t>22500966</t>
         </is>
       </c>
     </row>
@@ -855,30 +855,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.695789952</v>
+        <v>0.730219433</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22500961</t>
+          <t>22500968</t>
         </is>
       </c>
     </row>
@@ -888,30 +888,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.569645035</v>
+        <v>0.394216924</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>22500967</t>
+          <t>22500964</t>
         </is>
       </c>
     </row>
@@ -921,30 +921,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.394216924</v>
+        <v>0.695789952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22500964</t>
+          <t>22500961</t>
         </is>
       </c>
     </row>
@@ -954,30 +954,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.730219433</v>
+        <v>0.316246289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22500968</t>
+          <t>22500962</t>
         </is>
       </c>
     </row>
@@ -987,30 +987,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.586101686</v>
+        <v>0.418910433</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>22500966</t>
+          <t>22500963</t>
         </is>
       </c>
     </row>
@@ -1020,30 +1020,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.418848648</v>
+        <v>0.569645035</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22500965</t>
+          <t>22500967</t>
         </is>
       </c>
     </row>
@@ -1284,30 +1284,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.7086218</v>
+        <v>0.322811961</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>22500987</t>
+          <t>22500989</t>
         </is>
       </c>
     </row>
@@ -1317,30 +1317,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.424654514</v>
+        <v>0.731070459</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22500990</t>
+          <t>22500986</t>
         </is>
       </c>
     </row>
@@ -1350,30 +1350,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.628429651</v>
+        <v>0.169688314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22500983</t>
+          <t>22500984</t>
         </is>
       </c>
     </row>
@@ -1383,30 +1383,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.295086324</v>
+        <v>0.814145625</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>22500985</t>
+          <t>22500988</t>
         </is>
       </c>
     </row>
@@ -1416,30 +1416,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.814145625</v>
+        <v>0.424654514</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>22500988</t>
+          <t>22500990</t>
         </is>
       </c>
     </row>
@@ -1449,30 +1449,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.322811961</v>
+        <v>0.628429651</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>22500989</t>
+          <t>22500983</t>
         </is>
       </c>
     </row>
@@ -1482,30 +1482,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.169688314</v>
+        <v>0.7086218</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>22500984</t>
+          <t>22500987</t>
         </is>
       </c>
     </row>
@@ -1515,30 +1515,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.731070459</v>
+        <v>0.295086324</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>22500986</t>
+          <t>22500985</t>
         </is>
       </c>
     </row>
@@ -1812,30 +1812,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.2842900454998016</v>
+        <v>0.2439689189195633</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>22501000</t>
+          <t>22501001</t>
         </is>
       </c>
     </row>
@@ -1845,30 +1845,30 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.2439689189195633</v>
+        <v>0.2842900454998016</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>22501001</t>
+          <t>22501000</t>
         </is>
       </c>
     </row>
@@ -2142,30 +2142,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.6886867880821228</v>
+        <v>0.5898500084877014</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>22501012</t>
+          <t>22501013</t>
         </is>
       </c>
     </row>
@@ -2175,30 +2175,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.499740868806839</v>
+        <v>0.462356299161911</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>22501010</t>
+          <t>22501011</t>
         </is>
       </c>
     </row>
@@ -2208,30 +2208,30 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.462356299161911</v>
+        <v>0.6886867880821228</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>22501011</t>
+          <t>22501012</t>
         </is>
       </c>
     </row>
@@ -2241,30 +2241,30 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.5898500084877014</v>
+        <v>0.499740868806839</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>22501013</t>
+          <t>22501010</t>
         </is>
       </c>
     </row>
@@ -2571,30 +2571,30 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.4314593970775604</v>
+        <v>0.8523814678192139</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>22501025</t>
+          <t>22501023</t>
         </is>
       </c>
     </row>
@@ -2637,30 +2637,30 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.8523814678192139</v>
+        <v>0.4314593970775604</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>22501023</t>
+          <t>22501025</t>
         </is>
       </c>
     </row>
@@ -3033,30 +3033,30 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.5200976729393005</v>
+        <v>0.6078159809112549</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>22501041</t>
+          <t>22501038</t>
         </is>
       </c>
     </row>
@@ -3066,30 +3066,30 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.2557961344718933</v>
+        <v>0.7137834429740906</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>22501040</t>
+          <t>22501039</t>
         </is>
       </c>
     </row>
@@ -3099,30 +3099,30 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.7137834429740906</v>
+        <v>0.5200976729393005</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>22501039</t>
+          <t>22501041</t>
         </is>
       </c>
     </row>
@@ -3132,30 +3132,30 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.6078159809112549</v>
+        <v>0.2557961344718933</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>22501038</t>
+          <t>22501040</t>
         </is>
       </c>
     </row>
@@ -3486,6 +3486,402 @@
       <c r="G93" t="inlineStr">
         <is>
           <t>22501050</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>46106.79166666666</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0.5882400870323181</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>22501051</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>46106.79166666666</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0.3540230095386505</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>22501052</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>46106.79166666666</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>0.7345883250236511</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>22501053</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>46106.8125</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>0.5735021829605103</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>22501054</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>46106.8125</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0.6663347482681274</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>22501055</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>46106.83333333334</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0.3558185696601868</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>22501056</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>46106.875</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>0.7327764630317688</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>22501057</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>46106.89583333334</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>0.7012732028961182</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>22501058</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>46106.91666666666</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>0.8636989593505859</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>22501060</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>46106.91666666666</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0.6992468237876892</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>22501061</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>46106.91666666666</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0.7136558294296265</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>22501059</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>46106.9375</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0.4335979521274567</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>22501062</t>
         </is>
       </c>
     </row>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,30 +789,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.418848648</v>
+        <v>0.569645035</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22500965</t>
+          <t>22500967</t>
         </is>
       </c>
     </row>
@@ -822,30 +822,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.586101686</v>
+        <v>0.418910433</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>22500966</t>
+          <t>22500963</t>
         </is>
       </c>
     </row>
@@ -855,30 +855,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.730219433</v>
+        <v>0.316246289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22500968</t>
+          <t>22500962</t>
         </is>
       </c>
     </row>
@@ -888,30 +888,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.394216924</v>
+        <v>0.695789952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>22500964</t>
+          <t>22500961</t>
         </is>
       </c>
     </row>
@@ -921,30 +921,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.695789952</v>
+        <v>0.730219433</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22500961</t>
+          <t>22500968</t>
         </is>
       </c>
     </row>
@@ -954,30 +954,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.316246289</v>
+        <v>0.586101686</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22500962</t>
+          <t>22500966</t>
         </is>
       </c>
     </row>
@@ -987,30 +987,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.418910433</v>
+        <v>0.418848648</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>22500963</t>
+          <t>22500965</t>
         </is>
       </c>
     </row>
@@ -1020,30 +1020,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.569645035</v>
+        <v>0.394216924</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22500967</t>
+          <t>22500964</t>
         </is>
       </c>
     </row>
@@ -1284,30 +1284,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.322811961</v>
+        <v>0.628429651</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>22500989</t>
+          <t>22500983</t>
         </is>
       </c>
     </row>
@@ -1317,30 +1317,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.731070459</v>
+        <v>0.295086324</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22500986</t>
+          <t>22500985</t>
         </is>
       </c>
     </row>
@@ -1350,30 +1350,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.169688314</v>
+        <v>0.7086218</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22500984</t>
+          <t>22500987</t>
         </is>
       </c>
     </row>
@@ -1383,30 +1383,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.814145625</v>
+        <v>0.424654514</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>22500988</t>
+          <t>22500990</t>
         </is>
       </c>
     </row>
@@ -1416,30 +1416,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.424654514</v>
+        <v>0.169688314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>22500990</t>
+          <t>22500984</t>
         </is>
       </c>
     </row>
@@ -1449,30 +1449,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.628429651</v>
+        <v>0.731070459</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>22500983</t>
+          <t>22500986</t>
         </is>
       </c>
     </row>
@@ -1482,30 +1482,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.7086218</v>
+        <v>0.322811961</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>22500987</t>
+          <t>22500989</t>
         </is>
       </c>
     </row>
@@ -1515,30 +1515,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.295086324</v>
+        <v>0.814145625</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>22500985</t>
+          <t>22500988</t>
         </is>
       </c>
     </row>
@@ -1812,30 +1812,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.2439689189195633</v>
+        <v>0.2842900454998016</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>22501001</t>
+          <t>22501000</t>
         </is>
       </c>
     </row>
@@ -1845,30 +1845,30 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.2842900454998016</v>
+        <v>0.2439689189195633</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>22501000</t>
+          <t>22501001</t>
         </is>
       </c>
     </row>
@@ -2076,30 +2076,30 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.5466242432594299</v>
+        <v>0.156985729932785</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>22501008</t>
+          <t>22501009</t>
         </is>
       </c>
     </row>
@@ -2109,30 +2109,30 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.156985729932785</v>
+        <v>0.5466242432594299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>22501009</t>
+          <t>22501008</t>
         </is>
       </c>
     </row>
@@ -2142,30 +2142,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.5898500084877014</v>
+        <v>0.6886867880821228</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>22501013</t>
+          <t>22501012</t>
         </is>
       </c>
     </row>
@@ -2175,30 +2175,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.462356299161911</v>
+        <v>0.499740868806839</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>22501011</t>
+          <t>22501010</t>
         </is>
       </c>
     </row>
@@ -2208,30 +2208,30 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.6886867880821228</v>
+        <v>0.5898500084877014</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>22501012</t>
+          <t>22501013</t>
         </is>
       </c>
     </row>
@@ -2241,30 +2241,30 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.499740868806839</v>
+        <v>0.462356299161911</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>22501010</t>
+          <t>22501011</t>
         </is>
       </c>
     </row>
@@ -3882,6 +3882,336 @@
       <c r="G105" t="inlineStr">
         <is>
           <t>22501062</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>46108.79166666666</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0.3163451850414276</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>22501066</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>46108.8125</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0.6011347770690918</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>22501067</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>46108.8125</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0.7299258708953857</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>22501068</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>46108.83333333334</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0.3269562125205994</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>22501069</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>46108.83333333334</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0.8295520544052124</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>22501070</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>46108.85416666666</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0.6670945882797241</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>22501071</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>46108.875</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0.8279622793197632</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>22501072</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>46108.91666666666</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0.7257824540138245</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>22501073</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>46108.91666666666</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0.7883844375610352</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>22501074</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>46108.9375</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>0.8457854390144348</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>22501075</t>
         </is>
       </c>
     </row>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,30 +789,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.569645035</v>
+        <v>0.394216924</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22500967</t>
+          <t>22500964</t>
         </is>
       </c>
     </row>
@@ -822,30 +822,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.418910433</v>
+        <v>0.418848648</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>22500963</t>
+          <t>22500965</t>
         </is>
       </c>
     </row>
@@ -855,30 +855,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.316246289</v>
+        <v>0.586101686</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22500962</t>
+          <t>22500966</t>
         </is>
       </c>
     </row>
@@ -888,30 +888,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.695789952</v>
+        <v>0.730219433</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>22500961</t>
+          <t>22500968</t>
         </is>
       </c>
     </row>
@@ -921,30 +921,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.730219433</v>
+        <v>0.695789952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22500968</t>
+          <t>22500961</t>
         </is>
       </c>
     </row>
@@ -954,30 +954,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.586101686</v>
+        <v>0.316246289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22500966</t>
+          <t>22500962</t>
         </is>
       </c>
     </row>
@@ -987,30 +987,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.418848648</v>
+        <v>0.418910433</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>22500965</t>
+          <t>22500963</t>
         </is>
       </c>
     </row>
@@ -1020,30 +1020,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.394216924</v>
+        <v>0.569645035</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22500964</t>
+          <t>22500967</t>
         </is>
       </c>
     </row>
@@ -1284,30 +1284,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.628429651</v>
+        <v>0.814145625</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>22500983</t>
+          <t>22500988</t>
         </is>
       </c>
     </row>
@@ -1317,30 +1317,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.295086324</v>
+        <v>0.322811961</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22500985</t>
+          <t>22500989</t>
         </is>
       </c>
     </row>
@@ -1350,30 +1350,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.7086218</v>
+        <v>0.731070459</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22500987</t>
+          <t>22500986</t>
         </is>
       </c>
     </row>
@@ -1383,30 +1383,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.424654514</v>
+        <v>0.169688314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>22500990</t>
+          <t>22500984</t>
         </is>
       </c>
     </row>
@@ -1416,30 +1416,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.169688314</v>
+        <v>0.7086218</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>22500984</t>
+          <t>22500987</t>
         </is>
       </c>
     </row>
@@ -1449,30 +1449,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.731070459</v>
+        <v>0.295086324</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>22500986</t>
+          <t>22500985</t>
         </is>
       </c>
     </row>
@@ -1482,30 +1482,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.322811961</v>
+        <v>0.628429651</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>22500989</t>
+          <t>22500983</t>
         </is>
       </c>
     </row>
@@ -1515,30 +1515,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.814145625</v>
+        <v>0.424654514</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>22500988</t>
+          <t>22500990</t>
         </is>
       </c>
     </row>
@@ -1812,30 +1812,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.2842900454998016</v>
+        <v>0.2439689189195633</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>22501000</t>
+          <t>22501001</t>
         </is>
       </c>
     </row>
@@ -1845,30 +1845,30 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.2439689189195633</v>
+        <v>0.2842900454998016</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>22501001</t>
+          <t>22501000</t>
         </is>
       </c>
     </row>
@@ -1878,30 +1878,30 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.5209299325942993</v>
+        <v>0.5324534177780151</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>22501002</t>
+          <t>22501005</t>
         </is>
       </c>
     </row>
@@ -1944,30 +1944,30 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.5324534177780151</v>
+        <v>0.5209299325942993</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>22501005</t>
+          <t>22501002</t>
         </is>
       </c>
     </row>
@@ -2340,30 +2340,30 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.4748657643795013</v>
+        <v>0.3670358955860138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>22501017</t>
+          <t>22501016</t>
         </is>
       </c>
     </row>
@@ -2373,30 +2373,30 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.3670358955860138</v>
+        <v>0.4748657643795013</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>22501016</t>
+          <t>22501017</t>
         </is>
       </c>
     </row>
@@ -2406,30 +2406,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.275350421667099</v>
+        <v>0.2312954813241959</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>22501019</t>
+          <t>22501018</t>
         </is>
       </c>
     </row>
@@ -2439,30 +2439,30 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.336741179227829</v>
+        <v>0.275350421667099</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>22501020</t>
+          <t>22501019</t>
         </is>
       </c>
     </row>
@@ -2472,30 +2472,30 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.2312954813241959</v>
+        <v>0.336741179227829</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>22501018</t>
+          <t>22501020</t>
         </is>
       </c>
     </row>
@@ -4212,6 +4212,204 @@
       <c r="G115" t="inlineStr">
         <is>
           <t>22501075</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>46109.625</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>0.3542602062225342</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>22501076</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>46109.72916666666</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0.4755303859710693</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>22501080</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>46109.75</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>0.6064226627349854</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>22501077</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>46109.8125</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>0.7755086421966553</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>22501078</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>46109.83333333334</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0.3101013600826263</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>22501079</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>46109.91666666666</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>0.8269034624099731</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>22501081</t>
         </is>
       </c>
     </row>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,30 +789,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.394216924</v>
+        <v>0.569645035</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22500964</t>
+          <t>22500967</t>
         </is>
       </c>
     </row>
@@ -822,30 +822,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.418848648</v>
+        <v>0.418910433</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>22500965</t>
+          <t>22500963</t>
         </is>
       </c>
     </row>
@@ -855,30 +855,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.586101686</v>
+        <v>0.316246289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22500966</t>
+          <t>22500962</t>
         </is>
       </c>
     </row>
@@ -888,30 +888,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.730219433</v>
+        <v>0.695789952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>22500968</t>
+          <t>22500961</t>
         </is>
       </c>
     </row>
@@ -921,30 +921,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.695789952</v>
+        <v>0.730219433</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22500961</t>
+          <t>22500968</t>
         </is>
       </c>
     </row>
@@ -954,30 +954,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.316246289</v>
+        <v>0.586101686</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22500962</t>
+          <t>22500966</t>
         </is>
       </c>
     </row>
@@ -987,30 +987,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.418910433</v>
+        <v>0.418848648</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>22500963</t>
+          <t>22500965</t>
         </is>
       </c>
     </row>
@@ -1020,30 +1020,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.569645035</v>
+        <v>0.394216924</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22500967</t>
+          <t>22500964</t>
         </is>
       </c>
     </row>
@@ -1284,30 +1284,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.814145625</v>
+        <v>0.424654514</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>22500988</t>
+          <t>22500990</t>
         </is>
       </c>
     </row>
@@ -1317,30 +1317,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.322811961</v>
+        <v>0.295086324</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22500989</t>
+          <t>22500985</t>
         </is>
       </c>
     </row>
@@ -1350,30 +1350,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.731070459</v>
+        <v>0.7086218</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22500986</t>
+          <t>22500987</t>
         </is>
       </c>
     </row>
@@ -1383,30 +1383,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.169688314</v>
+        <v>0.628429651</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>22500984</t>
+          <t>22500983</t>
         </is>
       </c>
     </row>
@@ -1416,30 +1416,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.7086218</v>
+        <v>0.731070459</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>22500987</t>
+          <t>22500986</t>
         </is>
       </c>
     </row>
@@ -1449,30 +1449,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.295086324</v>
+        <v>0.322811961</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>22500985</t>
+          <t>22500989</t>
         </is>
       </c>
     </row>
@@ -1482,30 +1482,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.628429651</v>
+        <v>0.169688314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>22500983</t>
+          <t>22500984</t>
         </is>
       </c>
     </row>
@@ -1515,30 +1515,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.424654514</v>
+        <v>0.814145625</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>22500990</t>
+          <t>22500988</t>
         </is>
       </c>
     </row>
@@ -1878,30 +1878,30 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.5324534177780151</v>
+        <v>0.6554064154624939</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>22501005</t>
+          <t>22501004</t>
         </is>
       </c>
     </row>
@@ -1911,30 +1911,30 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.6554064154624939</v>
+        <v>0.5209299325942993</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>22501004</t>
+          <t>22501002</t>
         </is>
       </c>
     </row>
@@ -1944,30 +1944,30 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.5209299325942993</v>
+        <v>0.5324534177780151</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>22501002</t>
+          <t>22501005</t>
         </is>
       </c>
     </row>
@@ -2142,30 +2142,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.6886867880821228</v>
+        <v>0.5898500084877014</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>22501012</t>
+          <t>22501013</t>
         </is>
       </c>
     </row>
@@ -2175,30 +2175,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.499740868806839</v>
+        <v>0.6886867880821228</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>22501010</t>
+          <t>22501012</t>
         </is>
       </c>
     </row>
@@ -2208,30 +2208,30 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.5898500084877014</v>
+        <v>0.499740868806839</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>22501013</t>
+          <t>22501010</t>
         </is>
       </c>
     </row>
@@ -2406,30 +2406,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.2312954813241959</v>
+        <v>0.275350421667099</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>22501018</t>
+          <t>22501019</t>
         </is>
       </c>
     </row>
@@ -2439,30 +2439,30 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.275350421667099</v>
+        <v>0.336741179227829</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>22501019</t>
+          <t>22501020</t>
         </is>
       </c>
     </row>
@@ -2472,30 +2472,30 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.336741179227829</v>
+        <v>0.2312954813241959</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>22501020</t>
+          <t>22501018</t>
         </is>
       </c>
     </row>
@@ -3033,30 +3033,30 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.6078159809112549</v>
+        <v>0.2557961344718933</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>22501038</t>
+          <t>22501040</t>
         </is>
       </c>
     </row>
@@ -3066,30 +3066,30 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.7137834429740906</v>
+        <v>0.5200976729393005</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>22501039</t>
+          <t>22501041</t>
         </is>
       </c>
     </row>
@@ -3099,30 +3099,30 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.5200976729393005</v>
+        <v>0.7137834429740906</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>22501041</t>
+          <t>22501039</t>
         </is>
       </c>
     </row>
@@ -3132,30 +3132,30 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.2557961344718933</v>
+        <v>0.6078159809112549</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>22501040</t>
+          <t>22501038</t>
         </is>
       </c>
     </row>
@@ -3594,30 +3594,30 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.5735021829605103</v>
+        <v>0.6663347482681274</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>22501054</t>
+          <t>22501055</t>
         </is>
       </c>
     </row>
@@ -3627,30 +3627,30 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.6663347482681274</v>
+        <v>0.5735021829605103</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>22501055</t>
+          <t>22501054</t>
         </is>
       </c>
     </row>
@@ -4122,30 +4122,30 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.7257824540138245</v>
+        <v>0.7883844375610352</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>22501073</t>
+          <t>22501074</t>
         </is>
       </c>
     </row>
@@ -4155,30 +4155,30 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.7883844375610352</v>
+        <v>0.7257824540138245</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>22501074</t>
+          <t>22501073</t>
         </is>
       </c>
     </row>
@@ -4410,6 +4410,270 @@
       <c r="G121" t="inlineStr">
         <is>
           <t>22501081</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>46111.79166666666</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>0.4759908616542816</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>22501091</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>46111.8125</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>0.3622306883335114</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>22501092</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>46111.83333333334</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0.1846820116043091</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>22501093</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>46111.83333333334</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>0.7859463095664978</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>22501094</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>46111.85416666666</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0.2331387102603912</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>22501095</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>46111.875</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3524667322635651</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>22501096</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>46111.89583333334</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>0.607979416847229</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>22501097</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>46111.91666666666</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>0.7356448173522949</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>22501098</t>
         </is>
       </c>
     </row>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,30 +789,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.569645035</v>
+        <v>0.418848648</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22500967</t>
+          <t>22500965</t>
         </is>
       </c>
     </row>
@@ -822,30 +822,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.418910433</v>
+        <v>0.586101686</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>22500963</t>
+          <t>22500966</t>
         </is>
       </c>
     </row>
@@ -855,30 +855,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.316246289</v>
+        <v>0.730219433</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22500962</t>
+          <t>22500968</t>
         </is>
       </c>
     </row>
@@ -888,30 +888,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.695789952</v>
+        <v>0.394216924</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>22500961</t>
+          <t>22500964</t>
         </is>
       </c>
     </row>
@@ -921,30 +921,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.730219433</v>
+        <v>0.316246289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22500968</t>
+          <t>22500962</t>
         </is>
       </c>
     </row>
@@ -954,30 +954,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.586101686</v>
+        <v>0.418910433</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22500966</t>
+          <t>22500963</t>
         </is>
       </c>
     </row>
@@ -987,30 +987,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.418848648</v>
+        <v>0.569645035</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>22500965</t>
+          <t>22500967</t>
         </is>
       </c>
     </row>
@@ -1020,30 +1020,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.394216924</v>
+        <v>0.695789952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22500964</t>
+          <t>22500961</t>
         </is>
       </c>
     </row>
@@ -1053,30 +1053,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.652546704</v>
+        <v>0.499302298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>22500974</t>
+          <t>22500972</t>
         </is>
       </c>
     </row>
@@ -1086,30 +1086,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.5777215959999999</v>
+        <v>0.577502131</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22500975</t>
+          <t>22500969</t>
         </is>
       </c>
     </row>
@@ -1119,30 +1119,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.652437568</v>
+        <v>0.857488632</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>22500973</t>
+          <t>22500971</t>
         </is>
       </c>
     </row>
@@ -1152,30 +1152,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.857488632</v>
+        <v>0.842924058</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>22500971</t>
+          <t>22500970</t>
         </is>
       </c>
     </row>
@@ -1185,30 +1185,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.577502131</v>
+        <v>0.5777215959999999</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>22500969</t>
+          <t>22500975</t>
         </is>
       </c>
     </row>
@@ -1218,30 +1218,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.499302298</v>
+        <v>0.652546704</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>22500972</t>
+          <t>22500974</t>
         </is>
       </c>
     </row>
@@ -1251,30 +1251,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.842924058</v>
+        <v>0.652437568</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>22500970</t>
+          <t>22500973</t>
         </is>
       </c>
     </row>
@@ -1548,30 +1548,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.388431966</v>
+        <v>0.266292274</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>22500998</t>
+          <t>22500995</t>
         </is>
       </c>
     </row>
@@ -1581,30 +1581,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.657446146</v>
+        <v>0.155862674</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>22500997</t>
+          <t>22500993</t>
         </is>
       </c>
     </row>
@@ -1614,30 +1614,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.278542638</v>
+        <v>0.5540216569999999</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>22500992</t>
+          <t>22500991</t>
         </is>
       </c>
     </row>
@@ -1647,30 +1647,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.513797641</v>
+        <v>0.388431966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>22500996</t>
+          <t>22500998</t>
         </is>
       </c>
     </row>
@@ -1680,30 +1680,30 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.5540216569999999</v>
+        <v>0.278542638</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>22500991</t>
+          <t>22500992</t>
         </is>
       </c>
     </row>
@@ -1713,30 +1713,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.266292274</v>
+        <v>0.657446146</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>22500995</t>
+          <t>22500997</t>
         </is>
       </c>
     </row>
@@ -1746,30 +1746,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.155862674</v>
+        <v>0.513797641</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>22500993</t>
+          <t>22500996</t>
         </is>
       </c>
     </row>
@@ -2142,30 +2142,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.5898500084877014</v>
+        <v>0.462356299161911</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>22501013</t>
+          <t>22501011</t>
         </is>
       </c>
     </row>
@@ -2175,30 +2175,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.6886867880821228</v>
+        <v>0.499740868806839</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>22501012</t>
+          <t>22501010</t>
         </is>
       </c>
     </row>
@@ -2208,30 +2208,30 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.499740868806839</v>
+        <v>0.6886867880821228</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>22501010</t>
+          <t>22501012</t>
         </is>
       </c>
     </row>
@@ -2241,30 +2241,30 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.462356299161911</v>
+        <v>0.5898500084877014</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>22501011</t>
+          <t>22501013</t>
         </is>
       </c>
     </row>
@@ -2571,30 +2571,30 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.8523814678192139</v>
+        <v>0.4314593970775604</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>22501023</t>
+          <t>22501025</t>
         </is>
       </c>
     </row>
@@ -2604,30 +2604,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.5733375549316406</v>
+        <v>0.8523814678192139</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>22501024</t>
+          <t>22501023</t>
         </is>
       </c>
     </row>
@@ -2637,30 +2637,30 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.4314593970775604</v>
+        <v>0.5733375549316406</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>22501025</t>
+          <t>22501024</t>
         </is>
       </c>
     </row>
@@ -2670,30 +2670,30 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.8768197298049927</v>
+        <v>0.8616619110107422</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>22501026</t>
+          <t>22501028</t>
         </is>
       </c>
     </row>
@@ -2703,30 +2703,30 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.4926076531410217</v>
+        <v>0.8768197298049927</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>22501027</t>
+          <t>22501026</t>
         </is>
       </c>
     </row>
@@ -2736,30 +2736,30 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.8616619110107422</v>
+        <v>0.4926076531410217</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>22501028</t>
+          <t>22501027</t>
         </is>
       </c>
     </row>
@@ -3759,30 +3759,30 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.8636989593505859</v>
+        <v>0.7136558294296265</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>22501060</t>
+          <t>22501059</t>
         </is>
       </c>
     </row>
@@ -3825,30 +3825,30 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.7136558294296265</v>
+        <v>0.8636989593505859</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>22501059</t>
+          <t>22501060</t>
         </is>
       </c>
     </row>
@@ -4674,6 +4674,237 @@
       <c r="G129" t="inlineStr">
         <is>
           <t>22501098</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>46112.79166666666</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>0.4455626606941223</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>22501099</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>46112.8125</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3104596138000488</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>22501100</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>46112.83333333334</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>0.5768108367919922</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>22500652</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>46112.83333333334</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>0.629755437374115</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>22501101</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>46112.83333333334</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>0.3904860615730286</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>22501102</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>46112.9375</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>0.6365575194358826</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>22501103</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>46112.95833333334</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>0.5477316975593567</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>22501104</t>
         </is>
       </c>
     </row>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G136"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,30 +789,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.418848648</v>
+        <v>0.569645035</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22500965</t>
+          <t>22500967</t>
         </is>
       </c>
     </row>
@@ -822,30 +822,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.586101686</v>
+        <v>0.418910433</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>22500966</t>
+          <t>22500963</t>
         </is>
       </c>
     </row>
@@ -855,30 +855,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.730219433</v>
+        <v>0.316246289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22500968</t>
+          <t>22500962</t>
         </is>
       </c>
     </row>
@@ -888,30 +888,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.394216924</v>
+        <v>0.695789952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>22500964</t>
+          <t>22500961</t>
         </is>
       </c>
     </row>
@@ -921,30 +921,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.316246289</v>
+        <v>0.730219433</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22500962</t>
+          <t>22500968</t>
         </is>
       </c>
     </row>
@@ -954,30 +954,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.418910433</v>
+        <v>0.586101686</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22500963</t>
+          <t>22500966</t>
         </is>
       </c>
     </row>
@@ -987,30 +987,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.569645035</v>
+        <v>0.418848648</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>22500967</t>
+          <t>22500965</t>
         </is>
       </c>
     </row>
@@ -1020,30 +1020,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.695789952</v>
+        <v>0.394216924</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22500961</t>
+          <t>22500964</t>
         </is>
       </c>
     </row>
@@ -1053,30 +1053,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.499302298</v>
+        <v>0.652546704</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>22500972</t>
+          <t>22500974</t>
         </is>
       </c>
     </row>
@@ -1086,30 +1086,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.577502131</v>
+        <v>0.5777215959999999</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22500969</t>
+          <t>22500975</t>
         </is>
       </c>
     </row>
@@ -1119,30 +1119,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.857488632</v>
+        <v>0.842924058</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>22500971</t>
+          <t>22500970</t>
         </is>
       </c>
     </row>
@@ -1152,30 +1152,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.842924058</v>
+        <v>0.652437568</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>22500970</t>
+          <t>22500973</t>
         </is>
       </c>
     </row>
@@ -1185,30 +1185,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.5777215959999999</v>
+        <v>0.577502131</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>22500975</t>
+          <t>22500969</t>
         </is>
       </c>
     </row>
@@ -1218,30 +1218,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.652546704</v>
+        <v>0.499302298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>22500974</t>
+          <t>22500972</t>
         </is>
       </c>
     </row>
@@ -1251,30 +1251,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.652437568</v>
+        <v>0.857488632</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>22500973</t>
+          <t>22500971</t>
         </is>
       </c>
     </row>
@@ -1548,30 +1548,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.266292274</v>
+        <v>0.657446146</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>22500995</t>
+          <t>22500997</t>
         </is>
       </c>
     </row>
@@ -1581,30 +1581,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.155862674</v>
+        <v>0.513797641</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>22500993</t>
+          <t>22500996</t>
         </is>
       </c>
     </row>
@@ -1614,30 +1614,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.5540216569999999</v>
+        <v>0.278542638</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>22500991</t>
+          <t>22500992</t>
         </is>
       </c>
     </row>
@@ -1647,30 +1647,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.388431966</v>
+        <v>0.5540216569999999</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>22500998</t>
+          <t>22500991</t>
         </is>
       </c>
     </row>
@@ -1680,30 +1680,30 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.278542638</v>
+        <v>0.155862674</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>22500992</t>
+          <t>22500993</t>
         </is>
       </c>
     </row>
@@ -1713,30 +1713,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.657446146</v>
+        <v>0.266292274</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>22500997</t>
+          <t>22500995</t>
         </is>
       </c>
     </row>
@@ -1746,30 +1746,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.513797641</v>
+        <v>0.388431966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>22500996</t>
+          <t>22500998</t>
         </is>
       </c>
     </row>
@@ -2142,30 +2142,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.462356299161911</v>
+        <v>0.6886867880821228</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>22501011</t>
+          <t>22501012</t>
         </is>
       </c>
     </row>
@@ -2175,30 +2175,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.499740868806839</v>
+        <v>0.5898500084877014</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>22501010</t>
+          <t>22501013</t>
         </is>
       </c>
     </row>
@@ -2208,30 +2208,30 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.6886867880821228</v>
+        <v>0.499740868806839</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>22501012</t>
+          <t>22501010</t>
         </is>
       </c>
     </row>
@@ -2241,30 +2241,30 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.5898500084877014</v>
+        <v>0.462356299161911</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>22501013</t>
+          <t>22501011</t>
         </is>
       </c>
     </row>
@@ -2670,30 +2670,30 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.8616619110107422</v>
+        <v>0.8768197298049927</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>22501028</t>
+          <t>22501026</t>
         </is>
       </c>
     </row>
@@ -2703,30 +2703,30 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.8768197298049927</v>
+        <v>0.4926076531410217</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>22501026</t>
+          <t>22501027</t>
         </is>
       </c>
     </row>
@@ -2736,30 +2736,30 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.4926076531410217</v>
+        <v>0.8616619110107422</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>22501027</t>
+          <t>22501028</t>
         </is>
       </c>
     </row>
@@ -3033,30 +3033,30 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.2557961344718933</v>
+        <v>0.6078159809112549</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>22501040</t>
+          <t>22501038</t>
         </is>
       </c>
     </row>
@@ -3066,30 +3066,30 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.5200976729393005</v>
+        <v>0.7137834429740906</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>22501041</t>
+          <t>22501039</t>
         </is>
       </c>
     </row>
@@ -3099,30 +3099,30 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.7137834429740906</v>
+        <v>0.2557961344718933</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>22501039</t>
+          <t>22501040</t>
         </is>
       </c>
     </row>
@@ -3132,30 +3132,30 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.6078159809112549</v>
+        <v>0.5200976729393005</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>22501038</t>
+          <t>22501041</t>
         </is>
       </c>
     </row>
@@ -3990,30 +3990,30 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.3269562125205994</v>
+        <v>0.8295520544052124</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>22501069</t>
+          <t>22501070</t>
         </is>
       </c>
     </row>
@@ -4023,30 +4023,30 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.8295520544052124</v>
+        <v>0.3269562125205994</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>22501070</t>
+          <t>22501069</t>
         </is>
       </c>
     </row>
@@ -4905,6 +4905,303 @@
       <c r="G136" t="inlineStr">
         <is>
           <t>22501104</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>46113.79166666666</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>0.3167918026447296</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>22501105</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>46113.8125</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>0.4533692002296448</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>22501106</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>46113.8125</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>0.3006761372089386</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>22501107</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>46113.83333333334</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>0.334742397069931</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>22501003</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>46113.83333333334</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>0.7200018763542175</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>22501108</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>46113.83333333334</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>0.6811369657516479</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>22501109</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>46113.83333333334</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>0.7958841919898987</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>22501110</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>46113.875</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>0.3026004433631897</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>22501112</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>46113.91666666666</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>0.3299661874771118</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>22501113</t>
         </is>
       </c>
     </row>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -417,48 +429,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Actual Winner</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>gameId</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,7 +503,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -524,7 +536,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,7 +569,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -590,7 +602,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -623,7 +635,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -649,10 +661,14 @@
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -685,7 +701,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -718,7 +734,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -751,7 +767,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -784,502 +800,502 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.418848648</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>22500965</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.586101686</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>22500966</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.730219433</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>22500968</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.394216924</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>22500964</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.316246289</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>22500962</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.418910433</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>22500963</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Utah Jazz</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E18" t="n">
         <v>0.569645035</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>22500967</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
+    <row r="19">
+      <c r="A19" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>0.418910433</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>22500963</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Indiana Pacers</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>0.316246289</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>22500962</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Memphis Grizzlies</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E19" t="n">
         <v>0.695789952</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>22500961</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B16" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.499302298</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>22500972</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.577502131</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>22500969</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.652437568</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>22500973</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.857488632</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>22500971</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>LA Clippers</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>LA Clippers</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>0.730219433</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>22500968</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>0.586101686</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>22500966</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>0.418848648</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>22500965</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>0.394216924</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>22500964</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="E24" t="n">
+        <v>0.5777215959999999</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>22500975</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Los Angeles Lakers</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Denver Nuggets</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Los Angeles Lakers</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E25" t="n">
         <v>0.652546704</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Los Angeles Lakers</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>22500974</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
+    <row r="26">
+      <c r="A26" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Sacramento Kings</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>0.5777215959999999</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Sacramento Kings</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>22500975</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Atlanta Hawks</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Milwaukee Bucks</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Atlanta Hawks</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E26" t="n">
         <v>0.842924058</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Atlanta Hawks</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>22500970</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Charlotte Hornets</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>0.652437568</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>22500973</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Brooklyn Nets</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>0.577502131</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>22500969</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>0.499302298</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>22500972</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>0.857488632</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>22500971</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1312,7 +1328,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1345,7 +1361,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -1378,7 +1394,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -1411,7 +1427,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -1444,7 +1460,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -1477,7 +1493,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -1510,7 +1526,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -1543,238 +1559,238 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>46098</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.266292274</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>22500995</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.388431966</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>22500998</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.5540216569999999</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>22500991</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.155862674</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>22500993</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.278542638</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>22500992</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.513797641</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>22500996</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>Denver Nuggets</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Philadelphia 76ers</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Denver Nuggets</t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="E41" t="n">
         <v>0.657446146</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Denver Nuggets</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>22500997</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>0.513797641</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>22500996</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>0.278542638</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>22500992</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Charlotte Hornets</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Charlotte Hornets</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>0.5540216569999999</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Charlotte Hornets</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>22500991</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>0.155862674</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>22500993</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Milwaukee Bucks</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>0.266292274</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>22500995</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Sacramento Kings</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>0.388431966</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>22500998</t>
-        </is>
-      </c>
-    </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>46099.79166666666</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -1807,7 +1823,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>46099.8125</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -1840,7 +1856,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>46099.8125</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -1873,7 +1889,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>46099.83333333334</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -1906,7 +1922,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>46099.83333333334</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -1939,7 +1955,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>46099.83333333334</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -1972,73 +1988,73 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>46099.85416666666</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.1570685207843781</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>22501006</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46099.85416666666</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>Memphis Grizzlies</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Denver Nuggets</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Denver Nuggets</t>
         </is>
       </c>
-      <c r="E48" t="n">
+      <c r="E49" t="n">
         <v>0.494267612695694</v>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Memphis Grizzlies</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>22500651</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>46099.85416666666</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>0.1570685207843781</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>22501006</t>
-        </is>
-      </c>
-    </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>46099.89583333334</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -2071,7 +2087,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>46100.79166666666</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -2104,7 +2120,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>46100.79166666666</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -2137,7 +2153,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>46100.83333333334</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -2170,7 +2186,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>46100.83333333334</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -2203,7 +2219,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>46100.83333333334</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -2236,7 +2252,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>46100.83333333334</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -2269,7 +2285,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>46100.875</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -2302,7 +2318,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>46100.91666666666</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -2335,7 +2351,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>46101.8125</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -2368,7 +2384,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>46101.8125</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -2401,7 +2417,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>46101.83333333334</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -2434,7 +2450,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>46101.83333333334</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -2467,7 +2483,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>46101.83333333334</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -2500,7 +2516,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>46101.875</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -2533,7 +2549,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>46102.70833333334</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -2566,40 +2582,40 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46102.79166666666</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.4314593970775604</v>
+        <v>0.5733375549316406</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>22501025</t>
+          <t>22501024</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46102.79166666666</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -2632,40 +2648,40 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46102.79166666666</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.5733375549316406</v>
+        <v>0.4314593970775604</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>22501024</t>
+          <t>22501025</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46102.83333333334</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -2698,7 +2714,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46102.83333333334</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -2731,7 +2747,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46102.83333333334</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -2764,7 +2780,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46102.85416666666</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -2797,7 +2813,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46102.89583333334</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -2830,7 +2846,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46102.91666666666</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -2863,7 +2879,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>46103.70833333334</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -2896,7 +2912,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>46103.75</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -2929,7 +2945,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>46103.8125</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -2962,7 +2978,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>46103.83333333334</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -2995,7 +3011,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>46103.875</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -3028,7 +3044,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>46104.79166666666</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -3061,7 +3077,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>46104.79166666666</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -3094,7 +3110,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>46104.79166666666</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -3127,7 +3143,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>46104.79166666666</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -3160,7 +3176,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>46104.8125</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -3193,7 +3209,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>46104.83333333334</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -3226,7 +3242,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>46104.875</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -3259,7 +3275,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>46104.89583333334</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -3292,7 +3308,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>46104.91666666666</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -3325,7 +3341,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>46104.9375</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -3358,7 +3374,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>46105.79166666666</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -3391,7 +3407,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>46105.8125</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -3424,7 +3440,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>46105.83333333334</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -3457,7 +3473,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>46105.95833333334</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -3490,7 +3506,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>46106.79166666666</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -3523,7 +3539,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>46106.79166666666</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -3556,7 +3572,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>46106.79166666666</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -3589,73 +3605,73 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>46106.8125</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>0.5735021829605103</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>22501054</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>46106.8125</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
           <t>Cleveland Cavaliers</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Miami Heat</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>Cleveland Cavaliers</t>
         </is>
       </c>
-      <c r="E97" t="n">
+      <c r="E98" t="n">
         <v>0.6663347482681274</v>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>Miami Heat</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>22501055</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="1" t="n">
-        <v>46106.8125</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
-        <v>0.5735021829605103</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>22501054</t>
-        </is>
-      </c>
-    </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>46106.83333333334</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -3688,7 +3704,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>46106.875</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -3721,7 +3737,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>46106.89583333334</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -3754,7 +3770,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>46106.91666666666</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -3787,7 +3803,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>46106.91666666666</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -3820,7 +3836,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>46106.91666666666</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -3853,7 +3869,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>46106.9375</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -3886,7 +3902,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>46108.79166666666</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -3919,73 +3935,73 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>46108.8125</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0.7299258708953857</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>22501068</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>46108.8125</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
           <t>Boston Celtics</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>Atlanta Hawks</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>Boston Celtics</t>
         </is>
       </c>
-      <c r="E107" t="n">
+      <c r="E108" t="n">
         <v>0.6011347770690918</v>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>Boston Celtics</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t>22501067</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="1" t="n">
-        <v>46108.8125</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="E108" t="n">
-        <v>0.7299258708953857</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>22501068</t>
-        </is>
-      </c>
-    </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>46108.83333333334</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -4018,7 +4034,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>46108.83333333334</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -4051,7 +4067,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>46108.85416666666</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -4084,7 +4100,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>46108.875</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -4117,7 +4133,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>46108.91666666666</v>
       </c>
       <c r="B113" t="inlineStr">
@@ -4150,7 +4166,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>46108.91666666666</v>
       </c>
       <c r="B114" t="inlineStr">
@@ -4183,7 +4199,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>46108.9375</v>
       </c>
       <c r="B115" t="inlineStr">
@@ -4216,7 +4232,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>46109.625</v>
       </c>
       <c r="B116" t="inlineStr">
@@ -4249,7 +4265,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>46109.72916666666</v>
       </c>
       <c r="B117" t="inlineStr">
@@ -4282,7 +4298,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>46109.75</v>
       </c>
       <c r="B118" t="inlineStr">
@@ -4315,7 +4331,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>46109.8125</v>
       </c>
       <c r="B119" t="inlineStr">
@@ -4348,7 +4364,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>46109.83333333334</v>
       </c>
       <c r="B120" t="inlineStr">
@@ -4381,7 +4397,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>46109.91666666666</v>
       </c>
       <c r="B121" t="inlineStr">
@@ -4414,7 +4430,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>46111.79166666666</v>
       </c>
       <c r="B122" t="inlineStr">
@@ -4447,7 +4463,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>46111.8125</v>
       </c>
       <c r="B123" t="inlineStr">
@@ -4480,73 +4496,73 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>46111.83333333334</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0.7859463095664978</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>22501094</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46111.83333333334</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
           <t>Memphis Grizzlies</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>Phoenix Suns</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>Phoenix Suns</t>
         </is>
       </c>
-      <c r="E124" t="n">
+      <c r="E125" t="n">
         <v>0.1846820116043091</v>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>Phoenix Suns</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t>22501093</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="1" t="n">
-        <v>46111.83333333334</v>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="E125" t="n">
-        <v>0.7859463095664978</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>22501094</t>
-        </is>
-      </c>
-    </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>46111.85416666666</v>
       </c>
       <c r="B126" t="inlineStr">
@@ -4579,7 +4595,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>46111.875</v>
       </c>
       <c r="B127" t="inlineStr">
@@ -4612,7 +4628,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>46111.89583333334</v>
       </c>
       <c r="B128" t="inlineStr">
@@ -4645,7 +4661,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>46111.91666666666</v>
       </c>
       <c r="B129" t="inlineStr">
@@ -4678,7 +4694,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>46112.79166666666</v>
       </c>
       <c r="B130" t="inlineStr">
@@ -4711,7 +4727,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>46112.8125</v>
       </c>
       <c r="B131" t="inlineStr">
@@ -4744,73 +4760,73 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>46112.83333333334</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>0.629755437374115</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>22501101</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46112.83333333334</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
           <t>Milwaukee Bucks</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>Dallas Mavericks</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>Milwaukee Bucks</t>
         </is>
       </c>
-      <c r="E132" t="n">
+      <c r="E133" t="n">
         <v>0.5768108367919922</v>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>Milwaukee Bucks</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>22500652</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="1" t="n">
-        <v>46112.83333333334</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="E133" t="n">
-        <v>0.629755437374115</v>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>22501101</t>
-        </is>
-      </c>
-    </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>46112.83333333334</v>
       </c>
       <c r="B134" t="inlineStr">
@@ -4843,7 +4859,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>46112.9375</v>
       </c>
       <c r="B135" t="inlineStr">
@@ -4876,7 +4892,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>46112.95833333334</v>
       </c>
       <c r="B136" t="inlineStr">
@@ -4909,7 +4925,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>46113.79166666666</v>
       </c>
       <c r="B137" t="inlineStr">
@@ -4942,7 +4958,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>46113.8125</v>
       </c>
       <c r="B138" t="inlineStr">
@@ -4975,7 +4991,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>46113.8125</v>
       </c>
       <c r="B139" t="inlineStr">
@@ -5008,7 +5024,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>46113.83333333334</v>
       </c>
       <c r="B140" t="inlineStr">
@@ -5041,7 +5057,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>46113.83333333334</v>
       </c>
       <c r="B141" t="inlineStr">
@@ -5074,7 +5090,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>46113.83333333334</v>
       </c>
       <c r="B142" t="inlineStr">
@@ -5107,7 +5123,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>46113.83333333334</v>
       </c>
       <c r="B143" t="inlineStr">
@@ -5140,7 +5156,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>46113.875</v>
       </c>
       <c r="B144" t="inlineStr">
@@ -5173,7 +5189,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>46113.91666666666</v>
       </c>
       <c r="B145" t="inlineStr">
@@ -5202,6 +5218,303 @@
       <c r="G145" t="inlineStr">
         <is>
           <t>22501113</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>46115.79166666666</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>0.7051196098327637</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>22501120</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>46115.79166666666</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>0.5093315839767456</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>22501121</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>46115.8125</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>0.313143253326416</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>22501122</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>46115.8125</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>0.869844377040863</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>22501123</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>46115.83333333334</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>0.8550282120704651</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>22501124</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>46115.83333333334</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>0.236572340130806</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>22501125</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>46115.83333333334</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>0.3213936686515808</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>22501126</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>46115.85416666666</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>0.4103548228740692</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>22501127</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>46115.91666666666</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>0.7199352979660034</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>22501128</t>
         </is>
       </c>
     </row>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G154"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -805,30 +805,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.418848648</v>
+        <v>0.569645035</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22500965</t>
+          <t>22500967</t>
         </is>
       </c>
     </row>
@@ -838,30 +838,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.586101686</v>
+        <v>0.418910433</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>22500966</t>
+          <t>22500963</t>
         </is>
       </c>
     </row>
@@ -871,30 +871,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.730219433</v>
+        <v>0.316246289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22500968</t>
+          <t>22500962</t>
         </is>
       </c>
     </row>
@@ -904,30 +904,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.394216924</v>
+        <v>0.695789952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>22500964</t>
+          <t>22500961</t>
         </is>
       </c>
     </row>
@@ -937,30 +937,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.316246289</v>
+        <v>0.730219433</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22500962</t>
+          <t>22500968</t>
         </is>
       </c>
     </row>
@@ -970,30 +970,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.418910433</v>
+        <v>0.586101686</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22500963</t>
+          <t>22500966</t>
         </is>
       </c>
     </row>
@@ -1003,30 +1003,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.569645035</v>
+        <v>0.418848648</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>22500967</t>
+          <t>22500965</t>
         </is>
       </c>
     </row>
@@ -1036,30 +1036,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.695789952</v>
+        <v>0.394216924</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22500961</t>
+          <t>22500964</t>
         </is>
       </c>
     </row>
@@ -1069,30 +1069,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.499302298</v>
+        <v>0.652546704</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>22500972</t>
+          <t>22500974</t>
         </is>
       </c>
     </row>
@@ -1102,30 +1102,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.577502131</v>
+        <v>0.5777215959999999</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22500969</t>
+          <t>22500975</t>
         </is>
       </c>
     </row>
@@ -1135,30 +1135,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.652437568</v>
+        <v>0.857488632</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>22500973</t>
+          <t>22500971</t>
         </is>
       </c>
     </row>
@@ -1168,30 +1168,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.857488632</v>
+        <v>0.842924058</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>22500971</t>
+          <t>22500970</t>
         </is>
       </c>
     </row>
@@ -1201,30 +1201,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.5777215959999999</v>
+        <v>0.577502131</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>22500975</t>
+          <t>22500969</t>
         </is>
       </c>
     </row>
@@ -1234,30 +1234,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.652546704</v>
+        <v>0.499302298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>22500974</t>
+          <t>22500972</t>
         </is>
       </c>
     </row>
@@ -1267,30 +1267,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.842924058</v>
+        <v>0.652437568</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>22500970</t>
+          <t>22500973</t>
         </is>
       </c>
     </row>
@@ -1564,30 +1564,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.266292274</v>
+        <v>0.278542638</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>22500995</t>
+          <t>22500992</t>
         </is>
       </c>
     </row>
@@ -1597,30 +1597,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.388431966</v>
+        <v>0.657446146</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>22500998</t>
+          <t>22500997</t>
         </is>
       </c>
     </row>
@@ -1630,30 +1630,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.5540216569999999</v>
+        <v>0.155862674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>22500991</t>
+          <t>22500993</t>
         </is>
       </c>
     </row>
@@ -1663,30 +1663,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.155862674</v>
+        <v>0.513797641</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>22500993</t>
+          <t>22500996</t>
         </is>
       </c>
     </row>
@@ -1696,30 +1696,30 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.278542638</v>
+        <v>0.388431966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>22500992</t>
+          <t>22500998</t>
         </is>
       </c>
     </row>
@@ -1729,30 +1729,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.513797641</v>
+        <v>0.5540216569999999</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>22500996</t>
+          <t>22500991</t>
         </is>
       </c>
     </row>
@@ -1762,30 +1762,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.657446146</v>
+        <v>0.266292274</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>22500997</t>
+          <t>22500995</t>
         </is>
       </c>
     </row>
@@ -1993,30 +1993,30 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.1570685207843781</v>
+        <v>0.494267612695694</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>22501006</t>
+          <t>22500651</t>
         </is>
       </c>
     </row>
@@ -2026,30 +2026,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.494267612695694</v>
+        <v>0.1570685207843781</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>22500651</t>
+          <t>22501006</t>
         </is>
       </c>
     </row>
@@ -2587,30 +2587,30 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.5733375549316406</v>
+        <v>0.8523814678192139</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>22501024</t>
+          <t>22501023</t>
         </is>
       </c>
     </row>
@@ -2620,30 +2620,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.8523814678192139</v>
+        <v>0.4314593970775604</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>22501023</t>
+          <t>22501025</t>
         </is>
       </c>
     </row>
@@ -2653,30 +2653,30 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.4314593970775604</v>
+        <v>0.5733375549316406</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>22501025</t>
+          <t>22501024</t>
         </is>
       </c>
     </row>
@@ -3610,30 +3610,30 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.5735021829605103</v>
+        <v>0.6663347482681274</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>22501054</t>
+          <t>22501055</t>
         </is>
       </c>
     </row>
@@ -3643,30 +3643,30 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.6663347482681274</v>
+        <v>0.5735021829605103</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>22501055</t>
+          <t>22501054</t>
         </is>
       </c>
     </row>
@@ -3940,30 +3940,30 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.7299258708953857</v>
+        <v>0.6011347770690918</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>22501068</t>
+          <t>22501067</t>
         </is>
       </c>
     </row>
@@ -3973,30 +3973,30 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.6011347770690918</v>
+        <v>0.7299258708953857</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>22501067</t>
+          <t>22501068</t>
         </is>
       </c>
     </row>
@@ -4963,30 +4963,30 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.4533692002296448</v>
+        <v>0.3006761372089386</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>22501106</t>
+          <t>22501107</t>
         </is>
       </c>
     </row>
@@ -4996,30 +4996,30 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.3006761372089386</v>
+        <v>0.4533692002296448</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>22501107</t>
+          <t>22501106</t>
         </is>
       </c>
     </row>
@@ -5293,30 +5293,30 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.313143253326416</v>
+        <v>0.869844377040863</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>22501122</t>
+          <t>22501123</t>
         </is>
       </c>
     </row>
@@ -5326,30 +5326,30 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.869844377040863</v>
+        <v>0.313143253326416</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>22501123</t>
+          <t>22501122</t>
         </is>
       </c>
     </row>
@@ -5515,6 +5515,105 @@
       <c r="G154" t="inlineStr">
         <is>
           <t>22501128</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>46116.625</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>0.6822111010551453</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>22501129</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>46116.625</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>0.6619012355804443</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>22501130</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>46116.79166666666</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>0.5364096760749817</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>22501131</t>
         </is>
       </c>
     </row>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G157"/>
+  <dimension ref="A1:G168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -805,30 +805,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.569645035</v>
+        <v>0.394216924</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22500967</t>
+          <t>22500964</t>
         </is>
       </c>
     </row>
@@ -838,30 +838,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.418910433</v>
+        <v>0.418848648</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>22500963</t>
+          <t>22500965</t>
         </is>
       </c>
     </row>
@@ -871,30 +871,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.316246289</v>
+        <v>0.586101686</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22500962</t>
+          <t>22500966</t>
         </is>
       </c>
     </row>
@@ -904,30 +904,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.695789952</v>
+        <v>0.730219433</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>22500961</t>
+          <t>22500968</t>
         </is>
       </c>
     </row>
@@ -937,30 +937,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.730219433</v>
+        <v>0.569645035</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22500968</t>
+          <t>22500967</t>
         </is>
       </c>
     </row>
@@ -970,30 +970,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.586101686</v>
+        <v>0.316246289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22500966</t>
+          <t>22500962</t>
         </is>
       </c>
     </row>
@@ -1003,30 +1003,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.418848648</v>
+        <v>0.418910433</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>22500965</t>
+          <t>22500963</t>
         </is>
       </c>
     </row>
@@ -1036,30 +1036,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.394216924</v>
+        <v>0.695789952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22500964</t>
+          <t>22500961</t>
         </is>
       </c>
     </row>
@@ -1069,30 +1069,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.652546704</v>
+        <v>0.499302298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>22500974</t>
+          <t>22500972</t>
         </is>
       </c>
     </row>
@@ -1102,30 +1102,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.5777215959999999</v>
+        <v>0.652437568</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22500975</t>
+          <t>22500973</t>
         </is>
       </c>
     </row>
@@ -1135,30 +1135,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.857488632</v>
+        <v>0.577502131</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>22500971</t>
+          <t>22500969</t>
         </is>
       </c>
     </row>
@@ -1168,30 +1168,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.842924058</v>
+        <v>0.857488632</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>22500970</t>
+          <t>22500971</t>
         </is>
       </c>
     </row>
@@ -1201,30 +1201,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.577502131</v>
+        <v>0.5777215959999999</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>22500969</t>
+          <t>22500975</t>
         </is>
       </c>
     </row>
@@ -1234,30 +1234,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.499302298</v>
+        <v>0.652546704</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>22500972</t>
+          <t>22500974</t>
         </is>
       </c>
     </row>
@@ -1267,30 +1267,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.652437568</v>
+        <v>0.842924058</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>22500973</t>
+          <t>22500970</t>
         </is>
       </c>
     </row>
@@ -1300,30 +1300,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.424654514</v>
+        <v>0.169688314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>22500990</t>
+          <t>22500984</t>
         </is>
       </c>
     </row>
@@ -1333,30 +1333,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.295086324</v>
+        <v>0.814145625</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22500985</t>
+          <t>22500988</t>
         </is>
       </c>
     </row>
@@ -1366,30 +1366,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.7086218</v>
+        <v>0.731070459</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22500987</t>
+          <t>22500986</t>
         </is>
       </c>
     </row>
@@ -1399,30 +1399,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.628429651</v>
+        <v>0.322811961</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>22500983</t>
+          <t>22500989</t>
         </is>
       </c>
     </row>
@@ -1432,30 +1432,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.731070459</v>
+        <v>0.7086218</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>22500986</t>
+          <t>22500987</t>
         </is>
       </c>
     </row>
@@ -1465,30 +1465,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.322811961</v>
+        <v>0.295086324</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>22500989</t>
+          <t>22500985</t>
         </is>
       </c>
     </row>
@@ -1498,30 +1498,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.169688314</v>
+        <v>0.424654514</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>22500984</t>
+          <t>22500990</t>
         </is>
       </c>
     </row>
@@ -1531,30 +1531,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.814145625</v>
+        <v>0.628429651</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>22500988</t>
+          <t>22500983</t>
         </is>
       </c>
     </row>
@@ -1564,30 +1564,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.278542638</v>
+        <v>0.5540216569999999</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>22500992</t>
+          <t>22500991</t>
         </is>
       </c>
     </row>
@@ -1597,30 +1597,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.657446146</v>
+        <v>0.278542638</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>22500997</t>
+          <t>22500992</t>
         </is>
       </c>
     </row>
@@ -1630,30 +1630,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.155862674</v>
+        <v>0.657446146</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>22500993</t>
+          <t>22500997</t>
         </is>
       </c>
     </row>
@@ -1663,30 +1663,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.513797641</v>
+        <v>0.155862674</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>22500996</t>
+          <t>22500993</t>
         </is>
       </c>
     </row>
@@ -1696,30 +1696,30 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.388431966</v>
+        <v>0.513797641</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>22500998</t>
+          <t>22500996</t>
         </is>
       </c>
     </row>
@@ -1729,30 +1729,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.5540216569999999</v>
+        <v>0.388431966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>22500991</t>
+          <t>22500998</t>
         </is>
       </c>
     </row>
@@ -1828,30 +1828,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.2439689189195633</v>
+        <v>0.2842900454998016</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>22501001</t>
+          <t>22501000</t>
         </is>
       </c>
     </row>
@@ -1861,30 +1861,30 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.2842900454998016</v>
+        <v>0.2439689189195633</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>22501000</t>
+          <t>22501001</t>
         </is>
       </c>
     </row>
@@ -2158,30 +2158,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.6886867880821228</v>
+        <v>0.462356299161911</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>22501012</t>
+          <t>22501011</t>
         </is>
       </c>
     </row>
@@ -2191,30 +2191,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.5898500084877014</v>
+        <v>0.499740868806839</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>22501013</t>
+          <t>22501010</t>
         </is>
       </c>
     </row>
@@ -2224,30 +2224,30 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.499740868806839</v>
+        <v>0.5898500084877014</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>22501010</t>
+          <t>22501013</t>
         </is>
       </c>
     </row>
@@ -2257,30 +2257,30 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.462356299161911</v>
+        <v>0.6886867880821228</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>22501011</t>
+          <t>22501012</t>
         </is>
       </c>
     </row>
@@ -3511,30 +3511,30 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.5882400870323181</v>
+        <v>0.7345883250236511</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>22501051</t>
+          <t>22501053</t>
         </is>
       </c>
     </row>
@@ -3577,30 +3577,30 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.7345883250236511</v>
+        <v>0.5882400870323181</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>22501053</t>
+          <t>22501051</t>
         </is>
       </c>
     </row>
@@ -4963,30 +4963,30 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.3006761372089386</v>
+        <v>0.4533692002296448</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>22501107</t>
+          <t>22501106</t>
         </is>
       </c>
     </row>
@@ -4996,30 +4996,30 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.4533692002296448</v>
+        <v>0.3006761372089386</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>22501106</t>
+          <t>22501107</t>
         </is>
       </c>
     </row>
@@ -5293,30 +5293,30 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.869844377040863</v>
+        <v>0.313143253326416</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>22501123</t>
+          <t>22501122</t>
         </is>
       </c>
     </row>
@@ -5326,30 +5326,30 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.313143253326416</v>
+        <v>0.869844377040863</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>22501122</t>
+          <t>22501123</t>
         </is>
       </c>
     </row>
@@ -5614,6 +5614,369 @@
       <c r="G157" t="inlineStr">
         <is>
           <t>22501131</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>46117.64583333334</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>0.6839718818664551</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>22501135</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>46117.64583333334</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>0.209761306643486</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>22501134</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>46117.64583333334</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>0.4391545355319977</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>22501133</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>46117.64583333334</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>0.6894626617431641</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>22501132</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>46117.75</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>0.5989465713500977</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>22501136</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>46117.79166666666</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>0.6429611444473267</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>22501137</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>46117.79166666666</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>0.5532301664352417</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>22501138</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>46117.79166666666</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>0.8973514437675476</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>22501139</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>46117.8125</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>0.3314782083034515</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>22501140</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>46117.875</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>0.2489812076091766</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>22501141</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>46117.91666666666</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>0.4032554924488068</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>22501142</t>
         </is>
       </c>
     </row>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G168"/>
+  <dimension ref="A1:G183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -805,30 +805,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.394216924</v>
+        <v>0.730219433</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22500964</t>
+          <t>22500968</t>
         </is>
       </c>
     </row>
@@ -904,30 +904,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.730219433</v>
+        <v>0.394216924</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>22500968</t>
+          <t>22500964</t>
         </is>
       </c>
     </row>
@@ -937,30 +937,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.569645035</v>
+        <v>0.695789952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22500967</t>
+          <t>22500961</t>
         </is>
       </c>
     </row>
@@ -1036,30 +1036,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.695789952</v>
+        <v>0.569645035</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22500961</t>
+          <t>22500967</t>
         </is>
       </c>
     </row>
@@ -1102,30 +1102,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.652437568</v>
+        <v>0.857488632</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22500973</t>
+          <t>22500971</t>
         </is>
       </c>
     </row>
@@ -1135,30 +1135,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.577502131</v>
+        <v>0.652437568</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>22500969</t>
+          <t>22500973</t>
         </is>
       </c>
     </row>
@@ -1168,30 +1168,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.857488632</v>
+        <v>0.577502131</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>22500971</t>
+          <t>22500969</t>
         </is>
       </c>
     </row>
@@ -1234,30 +1234,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.652546704</v>
+        <v>0.842924058</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>22500974</t>
+          <t>22500970</t>
         </is>
       </c>
     </row>
@@ -1267,30 +1267,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.842924058</v>
+        <v>0.652546704</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>22500970</t>
+          <t>22500974</t>
         </is>
       </c>
     </row>
@@ -1300,30 +1300,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.169688314</v>
+        <v>0.295086324</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>22500984</t>
+          <t>22500985</t>
         </is>
       </c>
     </row>
@@ -1333,30 +1333,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.814145625</v>
+        <v>0.7086218</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22500988</t>
+          <t>22500987</t>
         </is>
       </c>
     </row>
@@ -1366,30 +1366,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.731070459</v>
+        <v>0.322811961</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22500986</t>
+          <t>22500989</t>
         </is>
       </c>
     </row>
@@ -1399,30 +1399,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.322811961</v>
+        <v>0.628429651</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>22500989</t>
+          <t>22500983</t>
         </is>
       </c>
     </row>
@@ -1432,30 +1432,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.7086218</v>
+        <v>0.814145625</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>22500987</t>
+          <t>22500988</t>
         </is>
       </c>
     </row>
@@ -1465,30 +1465,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.295086324</v>
+        <v>0.169688314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>22500985</t>
+          <t>22500984</t>
         </is>
       </c>
     </row>
@@ -1531,30 +1531,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.628429651</v>
+        <v>0.731070459</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>22500983</t>
+          <t>22500986</t>
         </is>
       </c>
     </row>
@@ -1564,30 +1564,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.5540216569999999</v>
+        <v>0.388431966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>22500991</t>
+          <t>22500998</t>
         </is>
       </c>
     </row>
@@ -1597,30 +1597,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.278542638</v>
+        <v>0.513797641</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>22500992</t>
+          <t>22500996</t>
         </is>
       </c>
     </row>
@@ -1630,30 +1630,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.657446146</v>
+        <v>0.155862674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>22500997</t>
+          <t>22500993</t>
         </is>
       </c>
     </row>
@@ -1663,30 +1663,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.155862674</v>
+        <v>0.266292274</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>22500993</t>
+          <t>22500995</t>
         </is>
       </c>
     </row>
@@ -1696,30 +1696,30 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.513797641</v>
+        <v>0.278542638</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>22500996</t>
+          <t>22500992</t>
         </is>
       </c>
     </row>
@@ -1729,30 +1729,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.388431966</v>
+        <v>0.5540216569999999</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>22500998</t>
+          <t>22500991</t>
         </is>
       </c>
     </row>
@@ -1762,30 +1762,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.266292274</v>
+        <v>0.657446146</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>22500995</t>
+          <t>22500997</t>
         </is>
       </c>
     </row>
@@ -1894,30 +1894,30 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.6554064154624939</v>
+        <v>0.5324534177780151</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>22501004</t>
+          <t>22501005</t>
         </is>
       </c>
     </row>
@@ -1960,30 +1960,30 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.5324534177780151</v>
+        <v>0.6554064154624939</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>22501005</t>
+          <t>22501004</t>
         </is>
       </c>
     </row>
@@ -2158,30 +2158,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.462356299161911</v>
+        <v>0.6886867880821228</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>22501011</t>
+          <t>22501012</t>
         </is>
       </c>
     </row>
@@ -2191,30 +2191,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.499740868806839</v>
+        <v>0.5898500084877014</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>22501010</t>
+          <t>22501013</t>
         </is>
       </c>
     </row>
@@ -2224,30 +2224,30 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.5898500084877014</v>
+        <v>0.499740868806839</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>22501013</t>
+          <t>22501010</t>
         </is>
       </c>
     </row>
@@ -2257,30 +2257,30 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.6886867880821228</v>
+        <v>0.462356299161911</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>22501012</t>
+          <t>22501011</t>
         </is>
       </c>
     </row>
@@ -2686,30 +2686,30 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.8768197298049927</v>
+        <v>0.8616619110107422</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>22501026</t>
+          <t>22501028</t>
         </is>
       </c>
     </row>
@@ -2719,30 +2719,30 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.4926076531410217</v>
+        <v>0.8768197298049927</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>22501027</t>
+          <t>22501026</t>
         </is>
       </c>
     </row>
@@ -2752,30 +2752,30 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.8616619110107422</v>
+        <v>0.4926076531410217</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>22501028</t>
+          <t>22501027</t>
         </is>
       </c>
     </row>
@@ -3049,30 +3049,30 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.6078159809112549</v>
+        <v>0.7137834429740906</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>22501038</t>
+          <t>22501039</t>
         </is>
       </c>
     </row>
@@ -3082,30 +3082,30 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.7137834429740906</v>
+        <v>0.5200976729393005</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>22501039</t>
+          <t>22501041</t>
         </is>
       </c>
     </row>
@@ -3115,30 +3115,30 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.2557961344718933</v>
+        <v>0.6078159809112549</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>22501040</t>
+          <t>22501038</t>
         </is>
       </c>
     </row>
@@ -3148,30 +3148,30 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.5200976729393005</v>
+        <v>0.2557961344718933</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>22501041</t>
+          <t>22501040</t>
         </is>
       </c>
     </row>
@@ -3610,30 +3610,30 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.6663347482681274</v>
+        <v>0.5735021829605103</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>22501055</t>
+          <t>22501054</t>
         </is>
       </c>
     </row>
@@ -3643,30 +3643,30 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.5735021829605103</v>
+        <v>0.6663347482681274</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>22501054</t>
+          <t>22501055</t>
         </is>
       </c>
     </row>
@@ -3775,30 +3775,30 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.7136558294296265</v>
+        <v>0.8636989593505859</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>22501059</t>
+          <t>22501060</t>
         </is>
       </c>
     </row>
@@ -3841,30 +3841,30 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.8636989593505859</v>
+        <v>0.7136558294296265</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>22501060</t>
+          <t>22501059</t>
         </is>
       </c>
     </row>
@@ -3940,30 +3940,30 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.6011347770690918</v>
+        <v>0.7299258708953857</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>22501067</t>
+          <t>22501068</t>
         </is>
       </c>
     </row>
@@ -3973,30 +3973,30 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.7299258708953857</v>
+        <v>0.6011347770690918</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>22501068</t>
+          <t>22501067</t>
         </is>
       </c>
     </row>
@@ -4963,30 +4963,30 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.4533692002296448</v>
+        <v>0.3006761372089386</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>22501106</t>
+          <t>22501107</t>
         </is>
       </c>
     </row>
@@ -4996,30 +4996,30 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.3006761372089386</v>
+        <v>0.4533692002296448</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>22501107</t>
+          <t>22501106</t>
         </is>
       </c>
     </row>
@@ -5029,30 +5029,30 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.334742397069931</v>
+        <v>0.7958841919898987</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>22501003</t>
+          <t>22501110</t>
         </is>
       </c>
     </row>
@@ -5062,30 +5062,30 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.7200018763542175</v>
+        <v>0.6811369657516479</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>22501108</t>
+          <t>22501109</t>
         </is>
       </c>
     </row>
@@ -5095,30 +5095,30 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.6811369657516479</v>
+        <v>0.334742397069931</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>22501109</t>
+          <t>22501003</t>
         </is>
       </c>
     </row>
@@ -5128,30 +5128,30 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.7958841919898987</v>
+        <v>0.7200018763542175</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>22501110</t>
+          <t>22501108</t>
         </is>
       </c>
     </row>
@@ -5359,30 +5359,30 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.8550282120704651</v>
+        <v>0.236572340130806</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>22501124</t>
+          <t>22501125</t>
         </is>
       </c>
     </row>
@@ -5392,30 +5392,30 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.236572340130806</v>
+        <v>0.3213936686515808</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>22501125</t>
+          <t>22501126</t>
         </is>
       </c>
     </row>
@@ -5425,30 +5425,30 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.3213936686515808</v>
+        <v>0.8550282120704651</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>22501126</t>
+          <t>22501124</t>
         </is>
       </c>
     </row>
@@ -5623,30 +5623,30 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.6839718818664551</v>
+        <v>0.209761306643486</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>22501135</t>
+          <t>22501134</t>
         </is>
       </c>
     </row>
@@ -5656,30 +5656,30 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.209761306643486</v>
+        <v>0.4391545355319977</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>22501134</t>
+          <t>22501133</t>
         </is>
       </c>
     </row>
@@ -5689,30 +5689,30 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.4391545355319977</v>
+        <v>0.6894626617431641</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>22501133</t>
+          <t>22501132</t>
         </is>
       </c>
     </row>
@@ -5722,30 +5722,30 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.6894626617431641</v>
+        <v>0.6839718818664551</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>22501132</t>
+          <t>22501135</t>
         </is>
       </c>
     </row>
@@ -5977,6 +5977,501 @@
       <c r="G168" t="inlineStr">
         <is>
           <t>22501142</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>46118.79166666666</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>0.5972306132316589</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>22501143</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>46118.79166666666</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>0.2161738723516464</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>22501144</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>46118.83333333334</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>0.3576884865760803</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>22501145</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>46118.83333333334</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>0.6878817677497864</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>22501146</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>46118.875</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>0.5550410151481628</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>22501147</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>46119.79166666666</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>0.3282864689826965</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>22501148</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>46119.8125</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>0.6930505633354187</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>22501149</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>46119.8125</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>0.5698964595794678</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>22501150</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>46119.8125</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>0.8373758792877197</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>22501151</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>46119.83333333334</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>0.6395388245582581</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>22501152</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>46119.83333333334</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>0.4932611286640167</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>22501153</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>46119.91666666666</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>0.6486186981201172</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>22501154</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>46119.9375</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>0.484617680311203</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>22501155</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>46119.9375</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>0.8861657381057739</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>22501156</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>46119.95833333334</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>0.4802132546901703</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>22501157</t>
         </is>
       </c>
     </row>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,48 +417,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G183"/>
+  <dimension ref="A1:G190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Actual Winner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>gameId</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +491,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -536,7 +524,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -569,7 +557,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +590,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,7 +623,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -661,14 +649,10 @@
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,7 +685,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -734,7 +718,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -767,7 +751,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -800,502 +784,502 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.569645035</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>22500967</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.418910433</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>22500963</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.316246289</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>22500962</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.695789952</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>22500961</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>LA Clippers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Chicago Bulls</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>LA Clippers</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E16" t="n">
         <v>0.730219433</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>LA Clippers</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>22500968</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
+    <row r="17">
+      <c r="A17" s="1" t="n">
         <v>46094</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.586101686</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>22500966</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>Dallas Mavericks</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Cleveland Cavaliers</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Cleveland Cavaliers</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E18" t="n">
         <v>0.418848648</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Cleveland Cavaliers</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>22500965</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
+    <row r="19">
+      <c r="A19" s="1" t="n">
         <v>46094</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>0.586101686</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>22500966</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Houston Rockets</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>New Orleans Pelicans</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>New Orleans Pelicans</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E19" t="n">
         <v>0.394216924</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Houston Rockets</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>22500964</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Memphis Grizzlies</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>0.695789952</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>22500961</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Indiana Pacers</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>0.316246289</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>22500962</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>0.418910433</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>22500963</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>0.569645035</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>22500967</t>
-        </is>
-      </c>
-    </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>46095</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.5777215959999999</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>22500975</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.652546704</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>22500974</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.577502131</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>22500969</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.842924058</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>22500970</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.857488632</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>22500971</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>Miami Heat</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Orlando Magic</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Orlando Magic</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E25" t="n">
         <v>0.499302298</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Orlando Magic</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>22500972</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
+    <row r="26">
+      <c r="A26" s="1" t="n">
         <v>46095</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>0.857488632</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>22500971</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Charlotte Hornets</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E26" t="n">
         <v>0.652437568</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>22500973</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Brooklyn Nets</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>0.577502131</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>22500969</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Sacramento Kings</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>0.5777215959999999</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Sacramento Kings</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>22500975</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Milwaukee Bucks</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>0.842924058</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>22500970</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>0.652546704</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>22500974</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>46097</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1328,7 +1312,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>46097</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1361,7 +1345,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>46097</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -1394,7 +1378,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>46097</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -1427,7 +1411,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>46097</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -1460,7 +1444,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>46097</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -1493,7 +1477,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>46097</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -1526,7 +1510,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>46097</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -1559,238 +1543,238 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.657446146</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>22500997</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.5540216569999999</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>22500991</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.278542638</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>22500992</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.513797641</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>22500996</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.155862674</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>22500993</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>Sacramento Kings</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="E40" t="n">
         <v>0.388431966</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>22500998</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
+    <row r="41">
+      <c r="A41" s="1" t="n">
         <v>46098</v>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>0.513797641</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>22500996</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>0.155862674</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>22500993</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B38" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Milwaukee Bucks</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Cleveland Cavaliers</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Cleveland Cavaliers</t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="E41" t="n">
         <v>0.266292274</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Cleveland Cavaliers</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>22500995</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>0.278542638</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>22500992</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Charlotte Hornets</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Charlotte Hornets</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>0.5540216569999999</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Charlotte Hornets</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>22500991</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>0.657446146</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>22500997</t>
-        </is>
-      </c>
-    </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>46099.79166666666</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -1823,7 +1807,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>46099.8125</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -1856,7 +1840,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>46099.8125</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -1889,172 +1873,172 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>46099.83333333334</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.6554064154624939</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>22501004</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>46099.83333333334</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>New Orleans Pelicans</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>LA Clippers</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>New Orleans Pelicans</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="E46" t="n">
         <v>0.5324534177780151</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>New Orleans Pelicans</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>22501005</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
+    <row r="47">
+      <c r="A47" s="1" t="n">
         <v>46099.83333333334</v>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Chicago Bulls</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Toronto Raptors</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Chicago Bulls</t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="E47" t="n">
         <v>0.5209299325942993</v>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Toronto Raptors</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>22501002</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>46099.83333333334</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>0.6554064154624939</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>22501004</t>
-        </is>
-      </c>
-    </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>46099.85416666666</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.1570685207843781</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>22501006</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>46099.85416666666</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>Memphis Grizzlies</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Denver Nuggets</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Denver Nuggets</t>
         </is>
       </c>
-      <c r="E48" t="n">
+      <c r="E49" t="n">
         <v>0.494267612695694</v>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Memphis Grizzlies</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>22500651</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>46099.85416666666</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>0.1570685207843781</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>22501006</t>
-        </is>
-      </c>
-    </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>46099.89583333334</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -2087,7 +2071,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>46100.79166666666</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -2120,7 +2104,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>46100.79166666666</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -2153,7 +2137,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>46100.83333333334</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -2186,7 +2170,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>46100.83333333334</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -2219,7 +2203,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>46100.83333333334</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -2252,7 +2236,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>46100.83333333334</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -2285,7 +2269,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>46100.875</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -2318,7 +2302,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>46100.91666666666</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -2351,73 +2335,73 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>46101.8125</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.4748657643795013</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>22501017</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>46101.8125</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>Brooklyn Nets</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>New York Knicks</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>New York Knicks</t>
         </is>
       </c>
-      <c r="E59" t="n">
+      <c r="E60" t="n">
         <v>0.3670358955860138</v>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>New York Knicks</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>22501016</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>46101.8125</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>0.4748657643795013</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>22501017</t>
-        </is>
-      </c>
-    </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>46101.83333333334</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -2450,7 +2434,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>46101.83333333334</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -2483,7 +2467,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>46101.83333333334</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -2516,7 +2500,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>46101.875</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -2549,7 +2533,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>46102.70833333334</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -2582,7 +2566,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>46102.79166666666</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -2615,7 +2599,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>46102.79166666666</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -2648,7 +2632,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>46102.79166666666</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -2681,73 +2665,73 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>46102.83333333334</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.8768197298049927</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>22501026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>46102.83333333334</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Indiana Pacers</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="E69" t="n">
+      <c r="E70" t="n">
         <v>0.8616619110107422</v>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>22501028</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="n">
-        <v>46102.83333333334</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>0.8768197298049927</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>22501026</t>
-        </is>
-      </c>
-    </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>46102.83333333334</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -2780,7 +2764,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>46102.85416666666</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -2813,7 +2797,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>46102.89583333334</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -2846,7 +2830,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>46102.91666666666</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -2879,7 +2863,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>46103.70833333334</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -2912,7 +2896,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>46103.75</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -2945,7 +2929,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>46103.8125</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -2978,7 +2962,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>46103.83333333334</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -3011,7 +2995,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>46103.875</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -3044,139 +3028,139 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>46104.79166666666</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0.6078159809112549</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>22501038</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>46104.79166666666</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0.2557961344718933</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>22501040</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46104.79166666666</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
           <t>Orlando Magic</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Indiana Pacers</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>Orlando Magic</t>
         </is>
       </c>
-      <c r="E80" t="n">
+      <c r="E82" t="n">
         <v>0.7137834429740906</v>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Indiana Pacers</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>22501039</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
+    <row r="83">
+      <c r="A83" s="1" t="n">
         <v>46104.79166666666</v>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>Miami Heat</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>Miami Heat</t>
         </is>
       </c>
-      <c r="E81" t="n">
+      <c r="E83" t="n">
         <v>0.5200976729393005</v>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>22501041</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
-        <v>46104.79166666666</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>0.6078159809112549</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>22501038</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
-        <v>46104.79166666666</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>0.2557961344718933</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>22501040</t>
-        </is>
-      </c>
-    </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>46104.8125</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -3209,7 +3193,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>46104.83333333334</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -3242,7 +3226,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>46104.875</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -3275,7 +3259,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>46104.89583333334</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -3308,7 +3292,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>46104.91666666666</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -3341,7 +3325,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>46104.9375</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -3374,7 +3358,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>46105.79166666666</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -3407,7 +3391,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>46105.8125</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -3440,7 +3424,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>46105.83333333334</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -3473,7 +3457,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>46105.95833333334</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -3506,106 +3490,106 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>46106.79166666666</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0.3540230095386505</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>22501052</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>46106.79166666666</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0.5882400870323181</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>22501051</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>46106.79166666666</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
           <t>Philadelphia 76ers</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Chicago Bulls</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>Philadelphia 76ers</t>
         </is>
       </c>
-      <c r="E94" t="n">
+      <c r="E96" t="n">
         <v>0.7345883250236511</v>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>Philadelphia 76ers</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>22501053</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="n">
-        <v>46106.79166666666</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Indiana Pacers</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>0.3540230095386505</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>22501052</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="n">
-        <v>46106.79166666666</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>0.5882400870323181</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>22501051</t>
-        </is>
-      </c>
-    </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>46106.8125</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -3638,7 +3622,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>46106.8125</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -3671,7 +3655,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>46106.83333333334</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -3704,7 +3688,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>46106.875</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -3737,7 +3721,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>46106.89583333334</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -3770,7 +3754,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>46106.91666666666</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -3803,7 +3787,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>46106.91666666666</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -3836,7 +3820,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>46106.91666666666</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -3869,7 +3853,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>46106.9375</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -3902,7 +3886,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>46108.79166666666</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -3935,7 +3919,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>46108.8125</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -3968,7 +3952,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>46108.8125</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -4001,7 +3985,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>46108.83333333334</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -4034,7 +4018,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>46108.83333333334</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -4067,7 +4051,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>46108.85416666666</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -4100,7 +4084,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>46108.875</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -4133,7 +4117,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>46108.91666666666</v>
       </c>
       <c r="B113" t="inlineStr">
@@ -4166,7 +4150,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>46108.91666666666</v>
       </c>
       <c r="B114" t="inlineStr">
@@ -4199,7 +4183,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>46108.9375</v>
       </c>
       <c r="B115" t="inlineStr">
@@ -4232,7 +4216,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>46109.625</v>
       </c>
       <c r="B116" t="inlineStr">
@@ -4265,7 +4249,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>46109.72916666666</v>
       </c>
       <c r="B117" t="inlineStr">
@@ -4298,7 +4282,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>46109.75</v>
       </c>
       <c r="B118" t="inlineStr">
@@ -4331,7 +4315,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>46109.8125</v>
       </c>
       <c r="B119" t="inlineStr">
@@ -4364,7 +4348,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>46109.83333333334</v>
       </c>
       <c r="B120" t="inlineStr">
@@ -4397,7 +4381,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>46109.91666666666</v>
       </c>
       <c r="B121" t="inlineStr">
@@ -4430,7 +4414,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>46111.79166666666</v>
       </c>
       <c r="B122" t="inlineStr">
@@ -4463,7 +4447,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>46111.8125</v>
       </c>
       <c r="B123" t="inlineStr">
@@ -4496,7 +4480,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>46111.83333333334</v>
       </c>
       <c r="B124" t="inlineStr">
@@ -4529,7 +4513,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>46111.83333333334</v>
       </c>
       <c r="B125" t="inlineStr">
@@ -4562,7 +4546,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>46111.85416666666</v>
       </c>
       <c r="B126" t="inlineStr">
@@ -4595,7 +4579,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>46111.875</v>
       </c>
       <c r="B127" t="inlineStr">
@@ -4628,7 +4612,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>46111.89583333334</v>
       </c>
       <c r="B128" t="inlineStr">
@@ -4661,7 +4645,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>46111.91666666666</v>
       </c>
       <c r="B129" t="inlineStr">
@@ -4694,7 +4678,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>46112.79166666666</v>
       </c>
       <c r="B130" t="inlineStr">
@@ -4727,7 +4711,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>46112.8125</v>
       </c>
       <c r="B131" t="inlineStr">
@@ -4760,7 +4744,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>46112.83333333334</v>
       </c>
       <c r="B132" t="inlineStr">
@@ -4793,7 +4777,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>46112.83333333334</v>
       </c>
       <c r="B133" t="inlineStr">
@@ -4826,7 +4810,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>46112.83333333334</v>
       </c>
       <c r="B134" t="inlineStr">
@@ -4859,7 +4843,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>46112.9375</v>
       </c>
       <c r="B135" t="inlineStr">
@@ -4892,7 +4876,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>46112.95833333334</v>
       </c>
       <c r="B136" t="inlineStr">
@@ -4925,7 +4909,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>46113.79166666666</v>
       </c>
       <c r="B137" t="inlineStr">
@@ -4958,7 +4942,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>46113.8125</v>
       </c>
       <c r="B138" t="inlineStr">
@@ -4991,7 +4975,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>46113.8125</v>
       </c>
       <c r="B139" t="inlineStr">
@@ -5024,139 +5008,139 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>46113.83333333334</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>0.7200018763542175</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>22501108</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>46113.83333333334</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>0.334742397069931</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>22501003</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>46113.83333333334</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>0.6811369657516479</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>22501109</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>46113.83333333334</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
           <t>Houston Rockets</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>Milwaukee Bucks</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>Houston Rockets</t>
         </is>
       </c>
-      <c r="E140" t="n">
+      <c r="E143" t="n">
         <v>0.7958841919898987</v>
       </c>
-      <c r="F140" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>Houston Rockets</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t>22501110</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="n">
-        <v>46113.83333333334</v>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Indiana Pacers</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="E141" t="n">
-        <v>0.6811369657516479</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Indiana Pacers</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>22501109</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="n">
-        <v>46113.83333333334</v>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Memphis Grizzlies</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="E142" t="n">
-        <v>0.334742397069931</v>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>22501003</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="n">
-        <v>46113.83333333334</v>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Sacramento Kings</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="E143" t="n">
-        <v>0.7200018763542175</v>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>Sacramento Kings</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>22501108</t>
-        </is>
-      </c>
-    </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>46113.875</v>
       </c>
       <c r="B144" t="inlineStr">
@@ -5189,7 +5173,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>46113.91666666666</v>
       </c>
       <c r="B145" t="inlineStr">
@@ -5222,7 +5206,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>46115.79166666666</v>
       </c>
       <c r="B146" t="inlineStr">
@@ -5255,7 +5239,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>46115.79166666666</v>
       </c>
       <c r="B147" t="inlineStr">
@@ -5288,7 +5272,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>46115.8125</v>
       </c>
       <c r="B148" t="inlineStr">
@@ -5321,7 +5305,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>46115.8125</v>
       </c>
       <c r="B149" t="inlineStr">
@@ -5354,106 +5338,106 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>46115.83333333334</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>0.3213936686515808</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>22501126</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>46115.83333333334</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>0.8550282120704651</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>22501124</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>46115.83333333334</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
           <t>Memphis Grizzlies</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
+      <c r="C152" t="inlineStr">
         <is>
           <t>Toronto Raptors</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D152" t="inlineStr">
         <is>
           <t>Toronto Raptors</t>
         </is>
       </c>
-      <c r="E150" t="n">
+      <c r="E152" t="n">
         <v>0.236572340130806</v>
       </c>
-      <c r="F150" t="inlineStr">
+      <c r="F152" t="inlineStr">
         <is>
           <t>Toronto Raptors</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="G152" t="inlineStr">
         <is>
           <t>22501125</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="n">
-        <v>46115.83333333334</v>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Milwaukee Bucks</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="E151" t="n">
-        <v>0.3213936686515808</v>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>22501126</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="n">
-        <v>46115.83333333334</v>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="E152" t="n">
-        <v>0.8550282120704651</v>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>22501124</t>
-        </is>
-      </c>
-    </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>46115.85416666666</v>
       </c>
       <c r="B153" t="inlineStr">
@@ -5486,7 +5470,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>46115.91666666666</v>
       </c>
       <c r="B154" t="inlineStr">
@@ -5519,7 +5503,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>46116.625</v>
       </c>
       <c r="B155" t="inlineStr">
@@ -5552,7 +5536,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>46116.625</v>
       </c>
       <c r="B156" t="inlineStr">
@@ -5585,7 +5569,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>46116.79166666666</v>
       </c>
       <c r="B157" t="inlineStr">
@@ -5618,7 +5602,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>46117.64583333334</v>
       </c>
       <c r="B158" t="inlineStr">
@@ -5651,7 +5635,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>46117.64583333334</v>
       </c>
       <c r="B159" t="inlineStr">
@@ -5684,7 +5668,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>46117.64583333334</v>
       </c>
       <c r="B160" t="inlineStr">
@@ -5717,7 +5701,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>46117.64583333334</v>
       </c>
       <c r="B161" t="inlineStr">
@@ -5750,7 +5734,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>46117.75</v>
       </c>
       <c r="B162" t="inlineStr">
@@ -5783,40 +5767,40 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>46117.79166666666</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.6429611444473267</v>
+        <v>0.8973514437675476</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>22501137</t>
+          <t>22501139</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>46117.79166666666</v>
       </c>
       <c r="B164" t="inlineStr">
@@ -5849,40 +5833,40 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>46117.79166666666</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.8973514437675476</v>
+        <v>0.6429611444473267</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>22501139</t>
+          <t>22501137</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>46117.8125</v>
       </c>
       <c r="B166" t="inlineStr">
@@ -5915,7 +5899,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>46117.875</v>
       </c>
       <c r="B167" t="inlineStr">
@@ -5948,7 +5932,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>46117.91666666666</v>
       </c>
       <c r="B168" t="inlineStr">
@@ -5981,7 +5965,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>46118.79166666666</v>
       </c>
       <c r="B169" t="inlineStr">
@@ -6014,7 +5998,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>46118.79166666666</v>
       </c>
       <c r="B170" t="inlineStr">
@@ -6047,7 +6031,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>46118.83333333334</v>
       </c>
       <c r="B171" t="inlineStr">
@@ -6080,7 +6064,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>46118.83333333334</v>
       </c>
       <c r="B172" t="inlineStr">
@@ -6113,7 +6097,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>46118.875</v>
       </c>
       <c r="B173" t="inlineStr">
@@ -6146,7 +6130,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>46119.79166666666</v>
       </c>
       <c r="B174" t="inlineStr">
@@ -6179,106 +6163,106 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>46119.8125</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>0.8373758792877197</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>22501151</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>46119.8125</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
           <t>Boston Celtics</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>Charlotte Hornets</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
+      <c r="D176" t="inlineStr">
         <is>
           <t>Boston Celtics</t>
         </is>
       </c>
-      <c r="E175" t="n">
+      <c r="E176" t="n">
         <v>0.6930505633354187</v>
       </c>
-      <c r="F175" t="inlineStr">
+      <c r="F176" t="inlineStr">
         <is>
           <t>Boston Celtics</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
+      <c r="G176" t="inlineStr">
         <is>
           <t>22501149</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="n">
+    <row r="177">
+      <c r="A177" s="1" t="n">
         <v>46119.8125</v>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B177" t="inlineStr">
         <is>
           <t>Brooklyn Nets</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
+      <c r="C177" t="inlineStr">
         <is>
           <t>Milwaukee Bucks</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
+      <c r="D177" t="inlineStr">
         <is>
           <t>Brooklyn Nets</t>
         </is>
       </c>
-      <c r="E176" t="n">
+      <c r="E177" t="n">
         <v>0.5698964595794678</v>
       </c>
-      <c r="F176" t="inlineStr">
+      <c r="F177" t="inlineStr">
         <is>
           <t>Brooklyn Nets</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
+      <c r="G177" t="inlineStr">
         <is>
           <t>22501150</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="n">
-        <v>46119.8125</v>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="E177" t="n">
-        <v>0.8373758792877197</v>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>22501151</t>
-        </is>
-      </c>
-    </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>46119.83333333334</v>
       </c>
       <c r="B178" t="inlineStr">
@@ -6311,7 +6295,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>46119.83333333334</v>
       </c>
       <c r="B179" t="inlineStr">
@@ -6344,7 +6328,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>46119.91666666666</v>
       </c>
       <c r="B180" t="inlineStr">
@@ -6377,7 +6361,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>46119.9375</v>
       </c>
       <c r="B181" t="inlineStr">
@@ -6410,7 +6394,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>46119.9375</v>
       </c>
       <c r="B182" t="inlineStr">
@@ -6443,7 +6427,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>46119.95833333334</v>
       </c>
       <c r="B183" t="inlineStr">
@@ -6472,6 +6456,237 @@
       <c r="G183" t="inlineStr">
         <is>
           <t>22501157</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>46120.79166666666</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>0.4664558172225952</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>22501159</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>46120.79166666666</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>0.5356937646865845</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>22501158</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>46120.79166666666</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>0.6002041697502136</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>22501160</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>46120.875</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>0.8839766979217529</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>22501162</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>46120.89583333334</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>0.5398016571998596</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>22501161</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>46120.91666666666</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>0.3676699697971344</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>22501163</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>46120.91666666666</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>0.73008793592453</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>22501164</t>
         </is>
       </c>
     </row>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -417,48 +429,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G190"/>
+  <dimension ref="A1:G196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Actual Winner</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>gameId</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,7 +503,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -524,7 +536,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -557,7 +569,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -590,7 +602,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -623,7 +635,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -649,10 +661,14 @@
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -685,7 +701,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -718,7 +734,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -751,7 +767,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>46093</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -784,502 +800,502 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.394216924</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>22500964</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.418848648</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>22500965</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.586101686</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>22500966</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.730219433</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>22500968</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Utah Jazz</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E16" t="n">
         <v>0.569645035</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>22500967</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
+    <row r="17">
+      <c r="A17" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.316246289</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>22500962</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>Toronto Raptors</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Phoenix Suns</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Phoenix Suns</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E18" t="n">
         <v>0.418910433</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Toronto Raptors</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>22500963</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
+    <row r="19">
+      <c r="A19" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Indiana Pacers</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>0.316246289</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>22500962</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Memphis Grizzlies</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E19" t="n">
         <v>0.695789952</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>22500961</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B16" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.857488632</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>22500971</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.652437568</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>22500973</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.842924058</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>22500970</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.499302298</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>22500972</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.652546704</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>22500974</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>LA Clippers</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>LA Clippers</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>0.730219433</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>22500968</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>0.586101686</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>22500966</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>0.418848648</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>22500965</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>0.394216924</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>22500964</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="E25" t="n">
+        <v>0.5777215959999999</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>22500975</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Sacramento Kings</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>0.5777215959999999</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Sacramento Kings</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>22500975</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>0.652546704</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>22500974</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Philadelphia 76ers</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Brooklyn Nets</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Philadelphia 76ers</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E26" t="n">
         <v>0.577502131</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Philadelphia 76ers</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>22500969</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Milwaukee Bucks</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>0.842924058</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>22500970</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>0.857488632</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>22500971</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>0.499302298</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>22500972</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Charlotte Hornets</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>0.652437568</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>22500973</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1312,7 +1328,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1345,7 +1361,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -1378,7 +1394,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -1411,7 +1427,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -1444,7 +1460,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -1477,7 +1493,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -1510,7 +1526,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -1543,238 +1559,238 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>46098</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.266292274</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>22500995</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.388431966</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>22500998</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.155862674</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>22500993</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.5540216569999999</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>22500991</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.278542638</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>22500992</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>Denver Nuggets</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Philadelphia 76ers</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Denver Nuggets</t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="E40" t="n">
         <v>0.657446146</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Denver Nuggets</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>22500997</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
+    <row r="41">
+      <c r="A41" s="2" t="n">
         <v>46098</v>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Charlotte Hornets</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Charlotte Hornets</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>0.5540216569999999</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Charlotte Hornets</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>22500991</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>0.278542638</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>22500992</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B38" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Minnesota Timberwolves</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Phoenix Suns</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Minnesota Timberwolves</t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="E41" t="n">
         <v>0.513797641</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Minnesota Timberwolves</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>22500996</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>0.155862674</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>22500993</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Sacramento Kings</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>0.388431966</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>22500998</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Milwaukee Bucks</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>0.266292274</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>22500995</t>
-        </is>
-      </c>
-    </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>46099.79166666666</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -1807,7 +1823,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>46099.8125</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -1840,7 +1856,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>46099.8125</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -1873,7 +1889,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>46099.83333333334</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -1906,7 +1922,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>46099.83333333334</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -1939,7 +1955,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>46099.83333333334</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -1972,7 +1988,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>46099.85416666666</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -2005,7 +2021,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>46099.85416666666</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -2038,7 +2054,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>46099.89583333334</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -2071,7 +2087,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>46100.79166666666</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -2104,7 +2120,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>46100.79166666666</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -2137,7 +2153,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>46100.83333333334</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -2170,7 +2186,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>46100.83333333334</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -2203,7 +2219,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>46100.83333333334</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -2236,7 +2252,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>46100.83333333334</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -2269,7 +2285,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>46100.875</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -2302,7 +2318,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>46100.91666666666</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -2335,7 +2351,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>46101.8125</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -2368,7 +2384,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>46101.8125</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -2401,40 +2417,40 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>46101.83333333334</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.275350421667099</v>
+        <v>0.2312954813241959</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>22501019</t>
+          <t>22501018</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>46101.83333333334</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -2467,40 +2483,40 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>46101.83333333334</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.2312954813241959</v>
+        <v>0.275350421667099</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>22501018</t>
+          <t>22501019</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>46101.875</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -2533,7 +2549,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>46102.70833333334</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -2566,7 +2582,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46102.79166666666</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -2599,7 +2615,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46102.79166666666</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -2632,7 +2648,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46102.79166666666</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -2665,7 +2681,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46102.83333333334</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -2698,7 +2714,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46102.83333333334</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -2731,7 +2747,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46102.83333333334</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -2764,7 +2780,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46102.85416666666</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -2797,7 +2813,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46102.89583333334</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -2830,7 +2846,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46102.91666666666</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -2863,7 +2879,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>46103.70833333334</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -2896,7 +2912,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>46103.75</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -2929,7 +2945,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>46103.8125</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -2962,7 +2978,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>46103.83333333334</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -2995,7 +3011,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>46103.875</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -3028,7 +3044,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>46104.79166666666</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -3061,7 +3077,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>46104.79166666666</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -3094,7 +3110,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>46104.79166666666</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -3127,7 +3143,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>46104.79166666666</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -3160,7 +3176,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>46104.8125</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -3193,7 +3209,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>46104.83333333334</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -3226,7 +3242,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>46104.875</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -3259,7 +3275,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>46104.89583333334</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -3292,7 +3308,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>46104.91666666666</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -3325,7 +3341,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>46104.9375</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -3358,7 +3374,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>46105.79166666666</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -3391,7 +3407,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>46105.8125</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -3424,7 +3440,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>46105.83333333334</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -3457,7 +3473,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>46105.95833333334</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -3490,7 +3506,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>46106.79166666666</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -3523,7 +3539,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>46106.79166666666</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -3556,7 +3572,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>46106.79166666666</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -3589,7 +3605,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>46106.8125</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -3622,7 +3638,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>46106.8125</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -3655,7 +3671,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>46106.83333333334</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -3688,7 +3704,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>46106.875</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -3721,7 +3737,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>46106.89583333334</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -3754,7 +3770,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>46106.91666666666</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -3787,7 +3803,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>46106.91666666666</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -3820,7 +3836,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>46106.91666666666</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -3853,7 +3869,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>46106.9375</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -3886,7 +3902,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>46108.79166666666</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -3919,7 +3935,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>46108.8125</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -3952,7 +3968,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>46108.8125</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -3985,7 +4001,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>46108.83333333334</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -4018,7 +4034,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>46108.83333333334</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -4051,7 +4067,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>46108.85416666666</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -4084,7 +4100,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>46108.875</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -4117,7 +4133,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>46108.91666666666</v>
       </c>
       <c r="B113" t="inlineStr">
@@ -4150,7 +4166,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>46108.91666666666</v>
       </c>
       <c r="B114" t="inlineStr">
@@ -4183,7 +4199,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>46108.9375</v>
       </c>
       <c r="B115" t="inlineStr">
@@ -4216,7 +4232,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>46109.625</v>
       </c>
       <c r="B116" t="inlineStr">
@@ -4249,7 +4265,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>46109.72916666666</v>
       </c>
       <c r="B117" t="inlineStr">
@@ -4282,7 +4298,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>46109.75</v>
       </c>
       <c r="B118" t="inlineStr">
@@ -4315,7 +4331,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>46109.8125</v>
       </c>
       <c r="B119" t="inlineStr">
@@ -4348,7 +4364,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>46109.83333333334</v>
       </c>
       <c r="B120" t="inlineStr">
@@ -4381,7 +4397,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>46109.91666666666</v>
       </c>
       <c r="B121" t="inlineStr">
@@ -4414,7 +4430,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>46111.79166666666</v>
       </c>
       <c r="B122" t="inlineStr">
@@ -4447,7 +4463,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>46111.8125</v>
       </c>
       <c r="B123" t="inlineStr">
@@ -4480,73 +4496,73 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>46111.83333333334</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0.1846820116043091</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>22501093</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46111.83333333334</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>Chicago Bulls</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="E124" t="n">
+      <c r="E125" t="n">
         <v>0.7859463095664978</v>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t>22501094</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="1" t="n">
-        <v>46111.83333333334</v>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Memphis Grizzlies</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="E125" t="n">
-        <v>0.1846820116043091</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>22501093</t>
-        </is>
-      </c>
-    </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>46111.85416666666</v>
       </c>
       <c r="B126" t="inlineStr">
@@ -4579,7 +4595,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>46111.875</v>
       </c>
       <c r="B127" t="inlineStr">
@@ -4612,7 +4628,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>46111.89583333334</v>
       </c>
       <c r="B128" t="inlineStr">
@@ -4645,7 +4661,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>46111.91666666666</v>
       </c>
       <c r="B129" t="inlineStr">
@@ -4678,7 +4694,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>46112.79166666666</v>
       </c>
       <c r="B130" t="inlineStr">
@@ -4711,7 +4727,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>46112.8125</v>
       </c>
       <c r="B131" t="inlineStr">
@@ -4744,7 +4760,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>46112.83333333334</v>
       </c>
       <c r="B132" t="inlineStr">
@@ -4777,7 +4793,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>46112.83333333334</v>
       </c>
       <c r="B133" t="inlineStr">
@@ -4810,7 +4826,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>46112.83333333334</v>
       </c>
       <c r="B134" t="inlineStr">
@@ -4843,7 +4859,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>46112.9375</v>
       </c>
       <c r="B135" t="inlineStr">
@@ -4876,7 +4892,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>46112.95833333334</v>
       </c>
       <c r="B136" t="inlineStr">
@@ -4909,7 +4925,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>46113.79166666666</v>
       </c>
       <c r="B137" t="inlineStr">
@@ -4942,7 +4958,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>46113.8125</v>
       </c>
       <c r="B138" t="inlineStr">
@@ -4975,7 +4991,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>46113.8125</v>
       </c>
       <c r="B139" t="inlineStr">
@@ -5008,7 +5024,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>46113.83333333334</v>
       </c>
       <c r="B140" t="inlineStr">
@@ -5041,7 +5057,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>46113.83333333334</v>
       </c>
       <c r="B141" t="inlineStr">
@@ -5074,7 +5090,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>46113.83333333334</v>
       </c>
       <c r="B142" t="inlineStr">
@@ -5107,7 +5123,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>46113.83333333334</v>
       </c>
       <c r="B143" t="inlineStr">
@@ -5140,7 +5156,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>46113.875</v>
       </c>
       <c r="B144" t="inlineStr">
@@ -5173,7 +5189,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>46113.91666666666</v>
       </c>
       <c r="B145" t="inlineStr">
@@ -5206,7 +5222,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>46115.79166666666</v>
       </c>
       <c r="B146" t="inlineStr">
@@ -5239,7 +5255,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>46115.79166666666</v>
       </c>
       <c r="B147" t="inlineStr">
@@ -5272,73 +5288,73 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>46115.8125</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>0.869844377040863</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>22501123</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>46115.8125</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
           <t>Brooklyn Nets</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>Atlanta Hawks</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="D149" t="inlineStr">
         <is>
           <t>Atlanta Hawks</t>
         </is>
       </c>
-      <c r="E148" t="n">
+      <c r="E149" t="n">
         <v>0.313143253326416</v>
       </c>
-      <c r="F148" t="inlineStr">
+      <c r="F149" t="inlineStr">
         <is>
           <t>Atlanta Hawks</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
+      <c r="G149" t="inlineStr">
         <is>
           <t>22501122</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="1" t="n">
-        <v>46115.8125</v>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="E149" t="n">
-        <v>0.869844377040863</v>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>22501123</t>
-        </is>
-      </c>
-    </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>46115.83333333334</v>
       </c>
       <c r="B150" t="inlineStr">
@@ -5371,7 +5387,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>46115.83333333334</v>
       </c>
       <c r="B151" t="inlineStr">
@@ -5404,7 +5420,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>46115.83333333334</v>
       </c>
       <c r="B152" t="inlineStr">
@@ -5437,7 +5453,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>46115.85416666666</v>
       </c>
       <c r="B153" t="inlineStr">
@@ -5470,7 +5486,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>46115.91666666666</v>
       </c>
       <c r="B154" t="inlineStr">
@@ -5503,7 +5519,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>46116.625</v>
       </c>
       <c r="B155" t="inlineStr">
@@ -5536,7 +5552,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>46116.625</v>
       </c>
       <c r="B156" t="inlineStr">
@@ -5569,7 +5585,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>46116.79166666666</v>
       </c>
       <c r="B157" t="inlineStr">
@@ -5602,139 +5618,139 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>46117.64583333334</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>0.6894626617431641</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>22501132</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>46117.64583333334</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>0.6839718818664551</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>22501135</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>46117.64583333334</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
           <t>Chicago Bulls</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
+      <c r="C160" t="inlineStr">
         <is>
           <t>Phoenix Suns</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
+      <c r="D160" t="inlineStr">
         <is>
           <t>Phoenix Suns</t>
         </is>
       </c>
-      <c r="E158" t="n">
+      <c r="E160" t="n">
         <v>0.209761306643486</v>
       </c>
-      <c r="F158" t="inlineStr">
+      <c r="F160" t="inlineStr">
         <is>
           <t>Phoenix Suns</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
+      <c r="G160" t="inlineStr">
         <is>
           <t>22501134</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="1" t="n">
+    <row r="161">
+      <c r="A161" s="2" t="n">
         <v>46117.64583333334</v>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>Brooklyn Nets</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>Washington Wizards</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>Washington Wizards</t>
         </is>
       </c>
-      <c r="E159" t="n">
+      <c r="E161" t="n">
         <v>0.4391545355319977</v>
       </c>
-      <c r="F159" t="inlineStr">
+      <c r="F161" t="inlineStr">
         <is>
           <t>Brooklyn Nets</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
+      <c r="G161" t="inlineStr">
         <is>
           <t>22501133</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="1" t="n">
-        <v>46117.64583333334</v>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="E160" t="n">
-        <v>0.6894626617431641</v>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>22501132</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="1" t="n">
-        <v>46117.64583333334</v>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Milwaukee Bucks</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Memphis Grizzlies</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Milwaukee Bucks</t>
-        </is>
-      </c>
-      <c r="E161" t="n">
-        <v>0.6839718818664551</v>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Milwaukee Bucks</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>22501135</t>
-        </is>
-      </c>
-    </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>46117.75</v>
       </c>
       <c r="B162" t="inlineStr">
@@ -5767,7 +5783,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>46117.79166666666</v>
       </c>
       <c r="B163" t="inlineStr">
@@ -5800,7 +5816,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>46117.79166666666</v>
       </c>
       <c r="B164" t="inlineStr">
@@ -5833,7 +5849,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>46117.79166666666</v>
       </c>
       <c r="B165" t="inlineStr">
@@ -5866,7 +5882,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>46117.8125</v>
       </c>
       <c r="B166" t="inlineStr">
@@ -5899,7 +5915,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>46117.875</v>
       </c>
       <c r="B167" t="inlineStr">
@@ -5932,7 +5948,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>46117.91666666666</v>
       </c>
       <c r="B168" t="inlineStr">
@@ -5965,7 +5981,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>46118.79166666666</v>
       </c>
       <c r="B169" t="inlineStr">
@@ -5998,7 +6014,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>46118.79166666666</v>
       </c>
       <c r="B170" t="inlineStr">
@@ -6031,7 +6047,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>46118.83333333334</v>
       </c>
       <c r="B171" t="inlineStr">
@@ -6064,7 +6080,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>46118.83333333334</v>
       </c>
       <c r="B172" t="inlineStr">
@@ -6097,7 +6113,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>46118.875</v>
       </c>
       <c r="B173" t="inlineStr">
@@ -6130,7 +6146,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>46119.79166666666</v>
       </c>
       <c r="B174" t="inlineStr">
@@ -6163,7 +6179,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>46119.8125</v>
       </c>
       <c r="B175" t="inlineStr">
@@ -6196,7 +6212,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>46119.8125</v>
       </c>
       <c r="B176" t="inlineStr">
@@ -6229,7 +6245,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>46119.8125</v>
       </c>
       <c r="B177" t="inlineStr">
@@ -6262,7 +6278,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>46119.83333333334</v>
       </c>
       <c r="B178" t="inlineStr">
@@ -6295,7 +6311,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>46119.83333333334</v>
       </c>
       <c r="B179" t="inlineStr">
@@ -6328,7 +6344,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>46119.91666666666</v>
       </c>
       <c r="B180" t="inlineStr">
@@ -6361,7 +6377,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>46119.9375</v>
       </c>
       <c r="B181" t="inlineStr">
@@ -6394,7 +6410,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>46119.9375</v>
       </c>
       <c r="B182" t="inlineStr">
@@ -6427,7 +6443,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>46119.95833333334</v>
       </c>
       <c r="B183" t="inlineStr">
@@ -6460,40 +6476,40 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>46120.79166666666</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>0.4664558172225952</v>
+        <v>0.6002041697502136</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>22501159</t>
+          <t>22501160</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>46120.79166666666</v>
       </c>
       <c r="B185" t="inlineStr">
@@ -6526,40 +6542,40 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>46120.79166666666</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>0.6002041697502136</v>
+        <v>0.4664558172225952</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>22501160</t>
+          <t>22501159</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>46120.875</v>
       </c>
       <c r="B187" t="inlineStr">
@@ -6592,7 +6608,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>46120.89583333334</v>
       </c>
       <c r="B188" t="inlineStr">
@@ -6625,7 +6641,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>46120.91666666666</v>
       </c>
       <c r="B189" t="inlineStr">
@@ -6658,7 +6674,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>46120.91666666666</v>
       </c>
       <c r="B190" t="inlineStr">
@@ -6687,6 +6703,204 @@
       <c r="G190" t="inlineStr">
         <is>
           <t>22501164</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>46121.79166666666</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>0.7684751152992249</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>22501165</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>46121.79166666666</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>0.2770043313503265</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>22501166</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>46121.8125</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>0.4195958077907562</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>22501167</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>46121.8125</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>0.3564230799674988</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>22501168</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>46121.83333333334</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>0.6835659146308899</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>22501169</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>46121.91666666666</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>0.3815212249755859</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>22501170</t>
         </is>
       </c>
     </row>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,48 +417,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G196"/>
+  <dimension ref="A1:G211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Actual Winner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>gameId</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +491,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -536,7 +524,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -569,7 +557,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -602,7 +590,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,7 +623,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -661,14 +649,10 @@
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,7 +685,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -734,7 +718,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -767,7 +751,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -800,271 +784,271 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.695789952</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>22500961</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.418910433</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>22500963</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.316246289</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>22500962</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.569645035</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>22500967</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.586101686</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>22500966</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.418848648</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>22500965</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>Houston Rockets</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>New Orleans Pelicans</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>New Orleans Pelicans</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E18" t="n">
         <v>0.394216924</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Houston Rockets</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>22500964</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
+    <row r="19">
+      <c r="A19" s="1" t="n">
         <v>46094</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>0.418848648</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>22500965</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>0.586101686</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>22500966</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>LA Clippers</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Chicago Bulls</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>LA Clippers</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E19" t="n">
         <v>0.730219433</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>LA Clippers</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>22500968</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Utah Jazz</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>0.569645035</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>22500967</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Indiana Pacers</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>0.316246289</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>New York Knicks</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>22500962</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>0.418910433</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Toronto Raptors</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>22500963</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Memphis Grizzlies</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>0.695789952</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>22500961</t>
-        </is>
-      </c>
-    </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>46095</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1097,7 +1081,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>46095</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1130,7 +1114,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>46095</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1163,7 +1147,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>46095</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1196,7 +1180,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>46095</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1229,7 +1213,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>46095</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1262,7 +1246,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>46095</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1295,271 +1279,271 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>46097</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.169688314</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>22500984</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.731070459</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>22500986</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.424654514</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>22500990</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.814145625</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>22500988</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7086218</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>22500987</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.322811961</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>22500989</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>Brooklyn Nets</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E33" t="n">
         <v>0.295086324</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>22500985</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
+    <row r="34">
+      <c r="A34" s="1" t="n">
         <v>46097</v>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Memphis Grizzlies</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>0.7086218</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>22500987</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Houston Rockets</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>0.322811961</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>22500989</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B30" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Atlanta Hawks</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Orlando Magic</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Atlanta Hawks</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="E34" t="n">
         <v>0.628429651</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Atlanta Hawks</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>22500983</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>0.814145625</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>New Orleans Pelicans</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>22500988</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>0.169688314</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>22500984</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>LA Clippers</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>0.424654514</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>22500990</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>0.731070459</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Boston Celtics</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>22500986</t>
-        </is>
-      </c>
-    </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -1592,7 +1576,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -1625,7 +1609,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -1658,7 +1642,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -1691,7 +1675,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -1724,7 +1708,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -1757,7 +1741,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -1790,7 +1774,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>46099.79166666666</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -1823,73 +1807,73 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>46099.8125</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.2439689189195633</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>22501001</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>46099.8125</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>Brooklyn Nets</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Oklahoma City Thunder</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Oklahoma City Thunder</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="E44" t="n">
         <v>0.2842900454998016</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Oklahoma City Thunder</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>22501000</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>46099.8125</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Indiana Pacers</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>0.2439689189195633</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>22501001</t>
-        </is>
-      </c>
-    </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>46099.83333333334</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -1922,7 +1906,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>46099.83333333334</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -1955,7 +1939,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>46099.83333333334</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -1988,7 +1972,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>46099.85416666666</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -2021,7 +2005,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>46099.85416666666</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -2054,7 +2038,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>46099.89583333334</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -2087,7 +2071,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>46100.79166666666</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -2120,7 +2104,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>46100.79166666666</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -2153,139 +2137,139 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>46100.83333333334</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.462356299161911</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>22501011</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>46100.83333333334</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.499740868806839</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>22501010</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>46100.83333333334</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>New Orleans Pelicans</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>LA Clippers</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>New Orleans Pelicans</t>
         </is>
       </c>
-      <c r="E53" t="n">
+      <c r="E55" t="n">
         <v>0.6886867880821228</v>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>New Orleans Pelicans</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>22501012</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
+    <row r="56">
+      <c r="A56" s="1" t="n">
         <v>46100.83333333334</v>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Phoenix Suns</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="E54" t="n">
+      <c r="E56" t="n">
         <v>0.5898500084877014</v>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>22501013</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>46100.83333333334</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>0.499740868806839</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Los Angeles Lakers</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>22501010</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>46100.83333333334</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>0.462356299161911</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>22501011</t>
-        </is>
-      </c>
-    </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>46100.875</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -2318,7 +2302,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>46100.91666666666</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -2351,7 +2335,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>46101.8125</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -2384,7 +2368,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>46101.8125</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -2417,7 +2401,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>46101.83333333334</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -2450,7 +2434,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>46101.83333333334</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -2483,7 +2467,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>46101.83333333334</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -2516,7 +2500,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>46101.875</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -2549,7 +2533,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>46102.70833333334</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -2582,40 +2566,40 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>46102.79166666666</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.8523814678192139</v>
+        <v>0.5733375549316406</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>22501023</t>
+          <t>22501024</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>46102.79166666666</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -2648,40 +2632,40 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>46102.79166666666</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.5733375549316406</v>
+        <v>0.8523814678192139</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>22501024</t>
+          <t>22501023</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>46102.83333333334</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -2714,7 +2698,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>46102.83333333334</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -2747,7 +2731,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>46102.83333333334</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -2780,7 +2764,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>46102.85416666666</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -2813,7 +2797,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>46102.89583333334</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -2846,7 +2830,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>46102.91666666666</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -2879,7 +2863,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>46103.70833333334</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -2912,7 +2896,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>46103.75</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -2945,7 +2929,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>46103.8125</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -2978,7 +2962,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>46103.83333333334</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -3011,7 +2995,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>46103.875</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -3044,139 +3028,139 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>46104.79166666666</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0.5200976729393005</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>22501041</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>46104.79166666666</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0.7137834429740906</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>22501039</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46104.79166666666</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Los Angeles Lakers</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="E80" t="n">
+      <c r="E82" t="n">
         <v>0.6078159809112549</v>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>22501038</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
+    <row r="83">
+      <c r="A83" s="1" t="n">
         <v>46104.79166666666</v>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>Philadelphia 76ers</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Oklahoma City Thunder</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>Oklahoma City Thunder</t>
         </is>
       </c>
-      <c r="E81" t="n">
+      <c r="E83" t="n">
         <v>0.2557961344718933</v>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Oklahoma City Thunder</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>22501040</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
-        <v>46104.79166666666</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Indiana Pacers</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>0.7137834429740906</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Indiana Pacers</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>22501039</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
-        <v>46104.79166666666</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>0.5200976729393005</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>22501041</t>
-        </is>
-      </c>
-    </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>46104.8125</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -3209,7 +3193,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>46104.83333333334</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -3242,7 +3226,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>46104.875</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -3275,7 +3259,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>46104.89583333334</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -3308,7 +3292,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>46104.91666666666</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -3341,7 +3325,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>46104.9375</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -3374,7 +3358,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>46105.79166666666</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -3407,7 +3391,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>46105.8125</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -3440,7 +3424,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>46105.83333333334</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -3473,7 +3457,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>46105.95833333334</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -3506,7 +3490,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>46106.79166666666</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -3539,7 +3523,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>46106.79166666666</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -3572,7 +3556,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>46106.79166666666</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -3605,7 +3589,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>46106.8125</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -3638,7 +3622,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>46106.8125</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -3671,7 +3655,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>46106.83333333334</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -3704,7 +3688,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>46106.875</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -3737,7 +3721,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>46106.89583333334</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -3770,106 +3754,106 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>46106.91666666666</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>0.6992468237876892</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>22501061</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>46106.91666666666</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0.7136558294296265</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>22501059</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>46106.91666666666</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
           <t>Golden State Warriors</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>Brooklyn Nets</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>Golden State Warriors</t>
         </is>
       </c>
-      <c r="E102" t="n">
+      <c r="E104" t="n">
         <v>0.8636989593505859</v>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>Golden State Warriors</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>22501060</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="n">
-        <v>46106.91666666666</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Milwaukee Bucks</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="E103" t="n">
-        <v>0.6992468237876892</v>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>22501061</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="n">
-        <v>46106.91666666666</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
-      <c r="E104" t="n">
-        <v>0.7136558294296265</v>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Denver Nuggets</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>22501059</t>
-        </is>
-      </c>
-    </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>46106.9375</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -3902,7 +3886,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>46108.79166666666</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -3935,7 +3919,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>46108.8125</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -3968,7 +3952,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>46108.8125</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -4001,7 +3985,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>46108.83333333334</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -4034,7 +4018,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>46108.83333333334</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -4067,7 +4051,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>46108.85416666666</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -4100,7 +4084,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>46108.875</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -4133,7 +4117,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>46108.91666666666</v>
       </c>
       <c r="B113" t="inlineStr">
@@ -4166,7 +4150,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>46108.91666666666</v>
       </c>
       <c r="B114" t="inlineStr">
@@ -4199,7 +4183,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>46108.9375</v>
       </c>
       <c r="B115" t="inlineStr">
@@ -4232,7 +4216,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>46109.625</v>
       </c>
       <c r="B116" t="inlineStr">
@@ -4265,7 +4249,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>46109.72916666666</v>
       </c>
       <c r="B117" t="inlineStr">
@@ -4298,7 +4282,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>46109.75</v>
       </c>
       <c r="B118" t="inlineStr">
@@ -4331,7 +4315,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>46109.8125</v>
       </c>
       <c r="B119" t="inlineStr">
@@ -4364,7 +4348,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>46109.83333333334</v>
       </c>
       <c r="B120" t="inlineStr">
@@ -4397,7 +4381,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>46109.91666666666</v>
       </c>
       <c r="B121" t="inlineStr">
@@ -4430,7 +4414,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>46111.79166666666</v>
       </c>
       <c r="B122" t="inlineStr">
@@ -4463,7 +4447,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>46111.8125</v>
       </c>
       <c r="B123" t="inlineStr">
@@ -4496,7 +4480,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>46111.83333333334</v>
       </c>
       <c r="B124" t="inlineStr">
@@ -4529,7 +4513,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>46111.83333333334</v>
       </c>
       <c r="B125" t="inlineStr">
@@ -4562,7 +4546,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>46111.85416666666</v>
       </c>
       <c r="B126" t="inlineStr">
@@ -4595,7 +4579,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>46111.875</v>
       </c>
       <c r="B127" t="inlineStr">
@@ -4628,7 +4612,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>46111.89583333334</v>
       </c>
       <c r="B128" t="inlineStr">
@@ -4661,7 +4645,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>46111.91666666666</v>
       </c>
       <c r="B129" t="inlineStr">
@@ -4694,7 +4678,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>46112.79166666666</v>
       </c>
       <c r="B130" t="inlineStr">
@@ -4727,7 +4711,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>46112.8125</v>
       </c>
       <c r="B131" t="inlineStr">
@@ -4760,40 +4744,40 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>46112.83333333334</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.629755437374115</v>
+        <v>0.3904860615730286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>22501101</t>
+          <t>22501102</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>46112.83333333334</v>
       </c>
       <c r="B133" t="inlineStr">
@@ -4826,40 +4810,40 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>46112.83333333334</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.3904860615730286</v>
+        <v>0.629755437374115</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>22501102</t>
+          <t>22501101</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>46112.9375</v>
       </c>
       <c r="B135" t="inlineStr">
@@ -4892,7 +4876,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>46112.95833333334</v>
       </c>
       <c r="B136" t="inlineStr">
@@ -4925,7 +4909,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>46113.79166666666</v>
       </c>
       <c r="B137" t="inlineStr">
@@ -4958,7 +4942,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>46113.8125</v>
       </c>
       <c r="B138" t="inlineStr">
@@ -4991,7 +4975,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>46113.8125</v>
       </c>
       <c r="B139" t="inlineStr">
@@ -5024,7 +5008,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>46113.83333333334</v>
       </c>
       <c r="B140" t="inlineStr">
@@ -5057,7 +5041,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>46113.83333333334</v>
       </c>
       <c r="B141" t="inlineStr">
@@ -5090,7 +5074,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>46113.83333333334</v>
       </c>
       <c r="B142" t="inlineStr">
@@ -5123,7 +5107,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>46113.83333333334</v>
       </c>
       <c r="B143" t="inlineStr">
@@ -5156,7 +5140,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>46113.875</v>
       </c>
       <c r="B144" t="inlineStr">
@@ -5189,7 +5173,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>46113.91666666666</v>
       </c>
       <c r="B145" t="inlineStr">
@@ -5222,73 +5206,73 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>46115.79166666666</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>0.5093315839767456</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>22501121</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>46115.79166666666</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
           <t>Charlotte Hornets</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
+      <c r="C147" t="inlineStr">
         <is>
           <t>Indiana Pacers</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="D147" t="inlineStr">
         <is>
           <t>Charlotte Hornets</t>
         </is>
       </c>
-      <c r="E146" t="n">
+      <c r="E147" t="n">
         <v>0.7051196098327637</v>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="F147" t="inlineStr">
         <is>
           <t>Charlotte Hornets</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="G147" t="inlineStr">
         <is>
           <t>22501120</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="n">
-        <v>46115.79166666666</v>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="E147" t="n">
-        <v>0.5093315839767456</v>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>22501121</t>
-        </is>
-      </c>
-    </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>46115.8125</v>
       </c>
       <c r="B148" t="inlineStr">
@@ -5321,7 +5305,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>46115.8125</v>
       </c>
       <c r="B149" t="inlineStr">
@@ -5354,7 +5338,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>46115.83333333334</v>
       </c>
       <c r="B150" t="inlineStr">
@@ -5387,7 +5371,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>46115.83333333334</v>
       </c>
       <c r="B151" t="inlineStr">
@@ -5420,7 +5404,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>46115.83333333334</v>
       </c>
       <c r="B152" t="inlineStr">
@@ -5453,7 +5437,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>46115.85416666666</v>
       </c>
       <c r="B153" t="inlineStr">
@@ -5486,7 +5470,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>46115.91666666666</v>
       </c>
       <c r="B154" t="inlineStr">
@@ -5519,7 +5503,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>46116.625</v>
       </c>
       <c r="B155" t="inlineStr">
@@ -5552,7 +5536,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>46116.625</v>
       </c>
       <c r="B156" t="inlineStr">
@@ -5585,7 +5569,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>46116.79166666666</v>
       </c>
       <c r="B157" t="inlineStr">
@@ -5618,139 +5602,139 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>46117.64583333334</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>0.4391545355319977</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>22501133</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>46117.64583333334</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>0.209761306643486</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>22501134</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>46117.64583333334</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>0.6839718818664551</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>22501135</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>46117.64583333334</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
           <t>Boston Celtics</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>Toronto Raptors</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>Boston Celtics</t>
         </is>
       </c>
-      <c r="E158" t="n">
+      <c r="E161" t="n">
         <v>0.6894626617431641</v>
       </c>
-      <c r="F158" t="inlineStr">
+      <c r="F161" t="inlineStr">
         <is>
           <t>Boston Celtics</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
+      <c r="G161" t="inlineStr">
         <is>
           <t>22501132</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="n">
-        <v>46117.64583333334</v>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Milwaukee Bucks</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Memphis Grizzlies</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Milwaukee Bucks</t>
-        </is>
-      </c>
-      <c r="E159" t="n">
-        <v>0.6839718818664551</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Milwaukee Bucks</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>22501135</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="n">
-        <v>46117.64583333334</v>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Chicago Bulls</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="E160" t="n">
-        <v>0.209761306643486</v>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>22501134</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="n">
-        <v>46117.64583333334</v>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Brooklyn Nets</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Washington Wizards</t>
-        </is>
-      </c>
-      <c r="E161" t="n">
-        <v>0.4391545355319977</v>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Brooklyn Nets</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>22501133</t>
-        </is>
-      </c>
-    </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>46117.75</v>
       </c>
       <c r="B162" t="inlineStr">
@@ -5783,7 +5767,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>46117.79166666666</v>
       </c>
       <c r="B163" t="inlineStr">
@@ -5816,7 +5800,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>46117.79166666666</v>
       </c>
       <c r="B164" t="inlineStr">
@@ -5849,7 +5833,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>46117.79166666666</v>
       </c>
       <c r="B165" t="inlineStr">
@@ -5882,7 +5866,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>46117.8125</v>
       </c>
       <c r="B166" t="inlineStr">
@@ -5915,7 +5899,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>46117.875</v>
       </c>
       <c r="B167" t="inlineStr">
@@ -5948,7 +5932,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>46117.91666666666</v>
       </c>
       <c r="B168" t="inlineStr">
@@ -5981,7 +5965,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>46118.79166666666</v>
       </c>
       <c r="B169" t="inlineStr">
@@ -6014,7 +5998,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>46118.79166666666</v>
       </c>
       <c r="B170" t="inlineStr">
@@ -6047,73 +6031,73 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>46118.83333333334</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>0.6878817677497864</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>22501146</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>46118.83333333334</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
           <t>Memphis Grizzlies</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
+      <c r="C172" t="inlineStr">
         <is>
           <t>Cleveland Cavaliers</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
+      <c r="D172" t="inlineStr">
         <is>
           <t>Cleveland Cavaliers</t>
         </is>
       </c>
-      <c r="E171" t="n">
+      <c r="E172" t="n">
         <v>0.3576884865760803</v>
       </c>
-      <c r="F171" t="inlineStr">
+      <c r="F172" t="inlineStr">
         <is>
           <t>Cleveland Cavaliers</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
+      <c r="G172" t="inlineStr">
         <is>
           <t>22501145</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="n">
-        <v>46118.83333333334</v>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Philadelphia 76ers</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="E172" t="n">
-        <v>0.6878817677497864</v>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>San Antonio Spurs</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>22501146</t>
-        </is>
-      </c>
-    </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>46118.875</v>
       </c>
       <c r="B173" t="inlineStr">
@@ -6146,7 +6130,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>46119.79166666666</v>
       </c>
       <c r="B174" t="inlineStr">
@@ -6179,7 +6163,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>46119.8125</v>
       </c>
       <c r="B175" t="inlineStr">
@@ -6212,7 +6196,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>46119.8125</v>
       </c>
       <c r="B176" t="inlineStr">
@@ -6245,7 +6229,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>46119.8125</v>
       </c>
       <c r="B177" t="inlineStr">
@@ -6278,7 +6262,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>46119.83333333334</v>
       </c>
       <c r="B178" t="inlineStr">
@@ -6311,7 +6295,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>46119.83333333334</v>
       </c>
       <c r="B179" t="inlineStr">
@@ -6344,7 +6328,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>46119.91666666666</v>
       </c>
       <c r="B180" t="inlineStr">
@@ -6377,7 +6361,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>46119.9375</v>
       </c>
       <c r="B181" t="inlineStr">
@@ -6410,7 +6394,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>46119.9375</v>
       </c>
       <c r="B182" t="inlineStr">
@@ -6443,7 +6427,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>46119.95833333334</v>
       </c>
       <c r="B183" t="inlineStr">
@@ -6476,106 +6460,106 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>46120.79166666666</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>0.5356937646865845</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>22501158</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>46120.79166666666</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>0.4664558172225952</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>22501159</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>46120.79166666666</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
+      <c r="C186" t="inlineStr">
         <is>
           <t>Milwaukee Bucks</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
+      <c r="D186" t="inlineStr">
         <is>
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="E184" t="n">
+      <c r="E186" t="n">
         <v>0.6002041697502136</v>
       </c>
-      <c r="F184" t="inlineStr">
+      <c r="F186" t="inlineStr">
         <is>
           <t>Detroit Pistons</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
+      <c r="G186" t="inlineStr">
         <is>
           <t>22501160</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="n">
-        <v>46120.79166666666</v>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="E185" t="n">
-        <v>0.5356937646865845</v>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>Cleveland Cavaliers</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>22501158</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="n">
-        <v>46120.79166666666</v>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="E186" t="n">
-        <v>0.4664558172225952</v>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>22501159</t>
-        </is>
-      </c>
-    </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>46120.875</v>
       </c>
       <c r="B187" t="inlineStr">
@@ -6608,7 +6592,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>46120.89583333334</v>
       </c>
       <c r="B188" t="inlineStr">
@@ -6641,7 +6625,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>46120.91666666666</v>
       </c>
       <c r="B189" t="inlineStr">
@@ -6674,7 +6658,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>46120.91666666666</v>
       </c>
       <c r="B190" t="inlineStr">
@@ -6707,7 +6691,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>46121.79166666666</v>
       </c>
       <c r="B191" t="inlineStr">
@@ -6740,7 +6724,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>46121.79166666666</v>
       </c>
       <c r="B192" t="inlineStr">
@@ -6773,7 +6757,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>46121.8125</v>
       </c>
       <c r="B193" t="inlineStr">
@@ -6806,7 +6790,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>46121.8125</v>
       </c>
       <c r="B194" t="inlineStr">
@@ -6839,7 +6823,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>46121.83333333334</v>
       </c>
       <c r="B195" t="inlineStr">
@@ -6872,7 +6856,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>46121.91666666666</v>
       </c>
       <c r="B196" t="inlineStr">
@@ -6901,6 +6885,501 @@
       <c r="G196" t="inlineStr">
         <is>
           <t>22501170</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>46122.79166666666</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>0.4738925993442535</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>22501172</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>46122.79166666666</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>0.672922670841217</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>22501173</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>46122.79166666666</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>0.5150246024131775</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>22501171</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>46122.8125</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>0.9048323035240173</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>22501174</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>46122.8125</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>0.535803496837616</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>22501175</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>46122.8125</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>0.5096167325973511</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>22501176</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>46122.83333333334</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>0.111219123005867</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>22501177</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>46122.83333333334</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>0.7083379030227661</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>22501179</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>46122.83333333334</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>0.8614312410354614</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>22501180</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>46122.875</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>0.6415862441062927</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>22501182</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>46122.89583333334</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>0.6991291046142578</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>22501178</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>46122.89583333334</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>0.3756789565086365</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>22501181</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>46122.91666666666</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>0.4845962822437286</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>22501184</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>46122.91666666666</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>0.6735097765922546</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>22501183</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>46122.9375</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>0.5701608061790466</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>22501185</t>
         </is>
       </c>
     </row>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G211"/>
+  <dimension ref="A1:G216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,166 +459,146 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46093</v>
+        <v>45932.5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.859049225</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
+        <v>0.6360629200935364</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22500957</t>
+          <t>12500008</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46093</v>
+        <v>45933.91666666666</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.631213677</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Oklahoma City Thunder</t>
-        </is>
-      </c>
+        <v>0.4915966987609863</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22500959</t>
+          <t>12500001</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46093</v>
+        <v>45934.45833333334</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.641633512</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Dallas Mavericks</t>
-        </is>
-      </c>
+        <v>0.6432452797889709</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22501111</t>
+          <t>12500010</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46093</v>
+        <v>45934.83333333334</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.654368185</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
+        <v>0.5113423466682434</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22500953</t>
+          <t>12500027</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46093</v>
+        <v>45934.875</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8596300650000001</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Atlanta Hawks</t>
-        </is>
-      </c>
+        <v>0.8339630365371704</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>22500956</t>
+          <t>12500028</t>
         </is>
       </c>
     </row>
@@ -628,28 +608,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.654368189</v>
+        <v>0.297013835</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>22500954</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -657,30 +641,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.847037727</v>
+        <v>0.749628073</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>22500955</t>
+          <t>22500958</t>
         </is>
       </c>
     </row>
@@ -690,30 +674,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.646850802</v>
+        <v>0.859049225</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>22500960</t>
+          <t>22500957</t>
         </is>
       </c>
     </row>
@@ -723,30 +707,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.749628073</v>
+        <v>0.847037727</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>22500958</t>
+          <t>22500955</t>
         </is>
       </c>
     </row>
@@ -756,197 +740,193 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.297013835</v>
+        <v>0.641633512</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>22500954</t>
+          <t>22501111</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.695789952</v>
+        <v>0.631213677</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22500961</t>
+          <t>22500959</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.418910433</v>
+        <v>0.8596300650000001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>22500963</t>
+          <t>22500956</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.316246289</v>
+        <v>0.654368185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22500962</t>
+          <t>22500953</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.569645035</v>
+        <v>0.646850802</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>22500967</t>
+          <t>22500960</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.586101686</v>
+        <v>0.654368189</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>22500966</t>
-        </is>
-      </c>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -954,30 +934,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.418848648</v>
+        <v>0.586101686</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22500965</t>
+          <t>22500966</t>
         </is>
       </c>
     </row>
@@ -987,30 +967,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.394216924</v>
+        <v>0.695789952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>22500964</t>
+          <t>22500961</t>
         </is>
       </c>
     </row>
@@ -1020,195 +1000,195 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.730219433</v>
+        <v>0.316246289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22500968</t>
+          <t>22500962</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.857488632</v>
+        <v>0.569645035</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>22500971</t>
+          <t>22500967</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.652437568</v>
+        <v>0.418910433</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22500973</t>
+          <t>22500963</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.842924058</v>
+        <v>0.730219433</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>22500970</t>
+          <t>22500968</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.499302298</v>
+        <v>0.394216924</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>22500972</t>
+          <t>22500964</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.652546704</v>
+        <v>0.418848648</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>22500974</t>
+          <t>22500965</t>
         </is>
       </c>
     </row>
@@ -1218,30 +1198,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.5777215959999999</v>
+        <v>0.842924058</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>22500975</t>
+          <t>22500970</t>
         </is>
       </c>
     </row>
@@ -1251,102 +1231,102 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.577502131</v>
+        <v>0.652437568</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>22500969</t>
+          <t>22500973</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46097</v>
+        <v>46095</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>Washington Wizards</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Golden State Warriors</t>
-        </is>
-      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.169688314</v>
+        <v>0.857488632</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>22500984</t>
+          <t>22500971</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46097</v>
+        <v>46095</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.731070459</v>
+        <v>0.577502131</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22500986</t>
+          <t>22500969</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46097</v>
+        <v>46095</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1355,91 +1335,91 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.424654514</v>
+        <v>0.5777215959999999</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22500990</t>
+          <t>22500975</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46097</v>
+        <v>46095</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.814145625</v>
+        <v>0.652546704</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>22500988</t>
+          <t>22500974</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46097</v>
+        <v>46095</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.7086218</v>
+        <v>0.499302298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>22500987</t>
+          <t>22500972</t>
         </is>
       </c>
     </row>
@@ -1449,30 +1429,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.322811961</v>
+        <v>0.731070459</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>22500989</t>
+          <t>22500986</t>
         </is>
       </c>
     </row>
@@ -1482,30 +1462,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.295086324</v>
+        <v>0.424654514</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>22500985</t>
+          <t>22500990</t>
         </is>
       </c>
     </row>
@@ -1515,195 +1495,195 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.628429651</v>
+        <v>0.814145625</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>22500983</t>
+          <t>22500988</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.266292274</v>
+        <v>0.322811961</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>22500995</t>
+          <t>22500989</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.388431966</v>
+        <v>0.295086324</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>22500998</t>
+          <t>22500985</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.155862674</v>
+        <v>0.628429651</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>22500993</t>
+          <t>22500983</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.5540216569999999</v>
+        <v>0.169688314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>22500991</t>
+          <t>22500984</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.278542638</v>
+        <v>0.7086218</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>22500992</t>
+          <t>22500987</t>
         </is>
       </c>
     </row>
@@ -1713,30 +1693,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.657446146</v>
+        <v>0.513797641</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>22500997</t>
+          <t>22500996</t>
         </is>
       </c>
     </row>
@@ -1746,1257 +1726,1257 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.513797641</v>
+        <v>0.657446146</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>22500996</t>
+          <t>22500997</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46099.79166666666</v>
+        <v>46098</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.7294707894325256</v>
+        <v>0.5540216569999999</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>22500999</t>
+          <t>22500991</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46099.8125</v>
+        <v>46098</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.2439689189195633</v>
+        <v>0.266292274</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>22501001</t>
+          <t>22500995</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46099.8125</v>
+        <v>46098</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.2842900454998016</v>
+        <v>0.388431966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>22501000</t>
+          <t>22500998</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46099.83333333334</v>
+        <v>46098</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.6554064154624939</v>
+        <v>0.155862674</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>22501004</t>
+          <t>22500993</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46099.83333333334</v>
+        <v>46098</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.5324534177780151</v>
+        <v>0.278542638</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>22501005</t>
+          <t>22500992</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46099.83333333334</v>
+        <v>46099.79166666666</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.5209299325942993</v>
+        <v>0.7294707894325256</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>22501002</t>
+          <t>22500999</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46099.85416666666</v>
+        <v>46099.8125</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.1570685207843781</v>
+        <v>0.2439689189195633</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>22501006</t>
+          <t>22501001</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46099.85416666666</v>
+        <v>46099.8125</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.494267612695694</v>
+        <v>0.2842900454998016</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>22500651</t>
+          <t>22501000</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46099.89583333334</v>
+        <v>46099.83333333334</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.3276689648628235</v>
+        <v>0.5209299325942993</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>22501007</t>
+          <t>22501002</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46100.79166666666</v>
+        <v>46099.83333333334</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.156985729932785</v>
+        <v>0.6554064154624939</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>22501009</t>
+          <t>22501004</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46100.79166666666</v>
+        <v>46099.83333333334</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.5466242432594299</v>
+        <v>0.5324534177780151</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>22501008</t>
+          <t>22501005</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46100.83333333334</v>
+        <v>46099.85416666666</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.462356299161911</v>
+        <v>0.494267612695694</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>22501011</t>
+          <t>22500651</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46100.83333333334</v>
+        <v>46099.85416666666</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.499740868806839</v>
+        <v>0.1570685207843781</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>22501010</t>
+          <t>22501006</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46100.83333333334</v>
+        <v>46099.89583333334</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.6886867880821228</v>
+        <v>0.3276689648628235</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>22501012</t>
+          <t>22501007</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46100.83333333334</v>
+        <v>46100.79166666666</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.5898500084877014</v>
+        <v>0.156985729932785</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>22501013</t>
+          <t>22501009</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46100.875</v>
+        <v>46100.79166666666</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.5481546521186829</v>
+        <v>0.5466242432594299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>22501014</t>
+          <t>22501008</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46100.91666666666</v>
+        <v>46100.83333333334</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.7287593483924866</v>
+        <v>0.462356299161911</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>22501015</t>
+          <t>22501011</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46101.8125</v>
+        <v>46100.83333333334</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.4748657643795013</v>
+        <v>0.5898500084877014</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>22501017</t>
+          <t>22501013</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46101.8125</v>
+        <v>46100.83333333334</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.3670358955860138</v>
+        <v>0.6886867880821228</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>22501016</t>
+          <t>22501012</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46101.83333333334</v>
+        <v>46100.83333333334</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.2312954813241959</v>
+        <v>0.499740868806839</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>22501018</t>
+          <t>22501010</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46101.83333333334</v>
+        <v>46100.875</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.336741179227829</v>
+        <v>0.5481546521186829</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>22501020</t>
+          <t>22501014</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46101.83333333334</v>
+        <v>46100.91666666666</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.275350421667099</v>
+        <v>0.7287593483924866</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>22501019</t>
+          <t>22501015</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46101.875</v>
+        <v>46101.8125</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.5892381072044373</v>
+        <v>0.4748657643795013</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>22501021</t>
+          <t>22501017</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46102.70833333334</v>
+        <v>46101.8125</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.3804706037044525</v>
+        <v>0.3670358955860138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>22501022</t>
+          <t>22501016</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46102.79166666666</v>
+        <v>46101.83333333334</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.5733375549316406</v>
+        <v>0.2312954813241959</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>22501024</t>
+          <t>22501018</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46102.79166666666</v>
+        <v>46101.83333333334</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.4314593970775604</v>
+        <v>0.336741179227829</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>22501025</t>
+          <t>22501020</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46102.79166666666</v>
+        <v>46101.83333333334</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.8523814678192139</v>
+        <v>0.275350421667099</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>22501023</t>
+          <t>22501019</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46102.83333333334</v>
+        <v>46101.875</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.8768197298049927</v>
+        <v>0.5892381072044373</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>22501026</t>
+          <t>22501021</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46102.83333333334</v>
+        <v>46102.70833333334</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.8616619110107422</v>
+        <v>0.3804706037044525</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>22501028</t>
+          <t>22501022</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46102.83333333334</v>
+        <v>46102.79166666666</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.4926076531410217</v>
+        <v>0.5733375549316406</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>22501027</t>
+          <t>22501024</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46102.85416666666</v>
+        <v>46102.79166666666</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.4836676120758057</v>
+        <v>0.4314593970775604</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>22501029</t>
+          <t>22501025</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46102.89583333334</v>
+        <v>46102.79166666666</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.443777859210968</v>
+        <v>0.8523814678192139</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>22501030</t>
+          <t>22501023</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46102.91666666666</v>
+        <v>46102.83333333334</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.7414435744285583</v>
+        <v>0.8616619110107422</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>22501031</t>
+          <t>22501028</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46103.70833333334</v>
+        <v>46102.83333333334</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.6782870292663574</v>
+        <v>0.8768197298049927</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>22501032</t>
+          <t>22501026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46103.75</v>
+        <v>46102.83333333334</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.6460906267166138</v>
+        <v>0.4926076531410217</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>22501033</t>
+          <t>22501027</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46103.8125</v>
+        <v>46102.85416666666</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.8850165605545044</v>
+        <v>0.4836676120758057</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>22501034</t>
+          <t>22501029</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46103.83333333334</v>
+        <v>46102.89583333334</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.7512719631195068</v>
+        <v>0.443777859210968</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>22501035</t>
+          <t>22501030</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46103.875</v>
+        <v>46102.91666666666</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -3005,7 +2985,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3014,1511 +2994,1511 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.5605062246322632</v>
+        <v>0.7414435744285583</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>22501036</t>
+          <t>22501031</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46104.79166666666</v>
+        <v>46103.70833333334</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.5200976729393005</v>
+        <v>0.6782870292663574</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>22501041</t>
+          <t>22501032</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46104.79166666666</v>
+        <v>46103.75</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.7137834429740906</v>
+        <v>0.6460906267166138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>22501039</t>
+          <t>22501033</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46104.79166666666</v>
+        <v>46103.8125</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.6078159809112549</v>
+        <v>0.8850165605545044</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>22501038</t>
+          <t>22501034</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46104.79166666666</v>
+        <v>46103.83333333334</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.2557961344718933</v>
+        <v>0.7512719631195068</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>22501040</t>
+          <t>22501035</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46104.8125</v>
+        <v>46103.875</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.8431744575500488</v>
+        <v>0.5605062246322632</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>22501037</t>
+          <t>22501036</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46104.83333333334</v>
+        <v>46104.79166666666</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.5208929777145386</v>
+        <v>0.5200976729393005</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>22501042</t>
+          <t>22501041</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46104.875</v>
+        <v>46104.79166666666</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.3560488522052765</v>
+        <v>0.7137834429740906</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>22501043</t>
+          <t>22501039</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46104.89583333334</v>
+        <v>46104.79166666666</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.6753662824630737</v>
+        <v>0.6078159809112549</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>22501044</t>
+          <t>22501038</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46104.91666666666</v>
+        <v>46104.79166666666</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.7495328187942505</v>
+        <v>0.2557961344718933</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>22501045</t>
+          <t>22501040</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46104.9375</v>
+        <v>46104.8125</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.7013514041900635</v>
+        <v>0.8431744575500488</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>22501046</t>
+          <t>22501037</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46105.79166666666</v>
+        <v>46104.83333333334</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.7356671094894409</v>
+        <v>0.5208929777145386</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>22501047</t>
+          <t>22501042</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46105.8125</v>
+        <v>46104.875</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.7157652378082275</v>
+        <v>0.3560488522052765</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>22501048</t>
+          <t>22501043</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46105.83333333334</v>
+        <v>46104.89583333334</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.7073813676834106</v>
+        <v>0.6753662824630737</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>22501049</t>
+          <t>22501044</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46105.95833333334</v>
+        <v>46104.91666666666</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.4800166189670563</v>
+        <v>0.7495328187942505</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>22501050</t>
+          <t>22501045</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46106.79166666666</v>
+        <v>46104.9375</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.3540230095386505</v>
+        <v>0.7013514041900635</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>22501052</t>
+          <t>22501046</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46106.79166666666</v>
+        <v>46105.79166666666</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.5882400870323181</v>
+        <v>0.7356671094894409</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>22501051</t>
+          <t>22501047</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46106.79166666666</v>
+        <v>46105.8125</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.7345883250236511</v>
+        <v>0.7157652378082275</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>22501053</t>
+          <t>22501048</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46106.8125</v>
+        <v>46105.83333333334</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.5735021829605103</v>
+        <v>0.7073813676834106</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>22501054</t>
+          <t>22501049</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46106.8125</v>
+        <v>46105.95833333334</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.6663347482681274</v>
+        <v>0.4800166189670563</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>22501055</t>
+          <t>22501050</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46106.83333333334</v>
+        <v>46106.79166666666</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.3558185696601868</v>
+        <v>0.3540230095386505</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>22501056</t>
+          <t>22501052</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46106.875</v>
+        <v>46106.79166666666</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.7327764630317688</v>
+        <v>0.5882400870323181</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>22501057</t>
+          <t>22501051</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46106.89583333334</v>
+        <v>46106.79166666666</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.7012732028961182</v>
+        <v>0.7345883250236511</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>22501058</t>
+          <t>22501053</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46106.91666666666</v>
+        <v>46106.8125</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.6992468237876892</v>
+        <v>0.6663347482681274</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>22501061</t>
+          <t>22501055</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46106.91666666666</v>
+        <v>46106.8125</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.7136558294296265</v>
+        <v>0.5735021829605103</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>22501059</t>
+          <t>22501054</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46106.91666666666</v>
+        <v>46106.83333333334</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.8636989593505859</v>
+        <v>0.3558185696601868</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>22501060</t>
+          <t>22501056</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46106.9375</v>
+        <v>46106.875</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.4335979521274567</v>
+        <v>0.7327764630317688</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>22501062</t>
+          <t>22501057</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46108.79166666666</v>
+        <v>46106.89583333334</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.3163451850414276</v>
+        <v>0.7012732028961182</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>22501066</t>
+          <t>22501058</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46108.8125</v>
+        <v>46106.91666666666</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.7299258708953857</v>
+        <v>0.6992468237876892</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>22501068</t>
+          <t>22501061</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46108.8125</v>
+        <v>46106.91666666666</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.6011347770690918</v>
+        <v>0.7136558294296265</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>22501067</t>
+          <t>22501059</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46108.83333333334</v>
+        <v>46106.91666666666</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.8295520544052124</v>
+        <v>0.8636989593505859</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>22501070</t>
+          <t>22501060</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46108.83333333334</v>
+        <v>46106.9375</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.3269562125205994</v>
+        <v>0.4335979521274567</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>22501069</t>
+          <t>22501062</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46108.85416666666</v>
+        <v>46108.79166666666</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.6670945882797241</v>
+        <v>0.3163451850414276</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>22501071</t>
+          <t>22501066</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46108.875</v>
+        <v>46108.8125</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.8279622793197632</v>
+        <v>0.7299258708953857</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>22501072</t>
+          <t>22501068</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46108.91666666666</v>
+        <v>46108.8125</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.7883844375610352</v>
+        <v>0.6011347770690918</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>22501074</t>
+          <t>22501067</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46108.91666666666</v>
+        <v>46108.83333333334</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.7257824540138245</v>
+        <v>0.8295520544052124</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>22501073</t>
+          <t>22501070</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46108.9375</v>
+        <v>46108.83333333334</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.8457854390144348</v>
+        <v>0.3269562125205994</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>22501075</t>
+          <t>22501069</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46109.625</v>
+        <v>46108.85416666666</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.3542602062225342</v>
+        <v>0.6670945882797241</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>22501076</t>
+          <t>22501071</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46109.72916666666</v>
+        <v>46108.875</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.4755303859710693</v>
+        <v>0.8279622793197632</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>22501080</t>
+          <t>22501072</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46109.75</v>
+        <v>46108.91666666666</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.6064226627349854</v>
+        <v>0.7883844375610352</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>22501077</t>
+          <t>22501074</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46109.8125</v>
+        <v>46108.91666666666</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.7755086421966553</v>
+        <v>0.7257824540138245</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>22501078</t>
+          <t>22501073</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46109.83333333334</v>
+        <v>46108.9375</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.3101013600826263</v>
+        <v>0.8457854390144348</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>22501079</t>
+          <t>22501075</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46109.91666666666</v>
+        <v>46109.625</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.8269034624099731</v>
+        <v>0.3542602062225342</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>22501081</t>
+          <t>22501076</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46111.79166666666</v>
+        <v>46109.72916666666</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.4759908616542816</v>
+        <v>0.4755303859710693</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>22501091</t>
+          <t>22501080</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46111.8125</v>
+        <v>46109.75</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.3622306883335114</v>
+        <v>0.6064226627349854</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>22501092</t>
+          <t>22501077</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46111.83333333334</v>
+        <v>46109.8125</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.1846820116043091</v>
+        <v>0.7755086421966553</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>22501093</t>
+          <t>22501078</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46111.83333333334</v>
+        <v>46109.83333333334</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4528,723 +4508,723 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.7859463095664978</v>
+        <v>0.3101013600826263</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>22501094</t>
+          <t>22501079</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46111.85416666666</v>
+        <v>46109.91666666666</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.2331387102603912</v>
+        <v>0.8269034624099731</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>22501095</t>
+          <t>22501081</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46111.875</v>
+        <v>46111.79166666666</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.3524667322635651</v>
+        <v>0.4759908616542816</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>22501096</t>
+          <t>22501091</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46111.89583333334</v>
+        <v>46111.8125</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.607979416847229</v>
+        <v>0.3622306883335114</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>22501097</t>
+          <t>22501092</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46111.91666666666</v>
+        <v>46111.83333333334</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.7356448173522949</v>
+        <v>0.1846820116043091</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>22501098</t>
+          <t>22501093</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46112.79166666666</v>
+        <v>46111.83333333334</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.4455626606941223</v>
+        <v>0.7859463095664978</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>22501099</t>
+          <t>22501094</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46112.8125</v>
+        <v>46111.85416666666</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.3104596138000488</v>
+        <v>0.2331387102603912</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>22501100</t>
+          <t>22501095</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46112.83333333334</v>
+        <v>46111.875</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.3904860615730286</v>
+        <v>0.3524667322635651</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>22501102</t>
+          <t>22501096</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46112.83333333334</v>
+        <v>46111.89583333334</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.5768108367919922</v>
+        <v>0.607979416847229</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>22500652</t>
+          <t>22501097</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46112.83333333334</v>
+        <v>46111.91666666666</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.629755437374115</v>
+        <v>0.7356448173522949</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>22501101</t>
+          <t>22501098</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46112.9375</v>
+        <v>46112.79166666666</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.6365575194358826</v>
+        <v>0.4455626606941223</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>22501103</t>
+          <t>22501099</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46112.95833333334</v>
+        <v>46112.8125</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.5477316975593567</v>
+        <v>0.3104596138000488</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>22501104</t>
+          <t>22501100</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46113.79166666666</v>
+        <v>46112.83333333334</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.3167918026447296</v>
+        <v>0.5768108367919922</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>22501105</t>
+          <t>22500652</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46113.8125</v>
+        <v>46112.83333333334</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.3006761372089386</v>
+        <v>0.629755437374115</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>22501107</t>
+          <t>22501101</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46113.8125</v>
+        <v>46112.83333333334</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.4533692002296448</v>
+        <v>0.3904860615730286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>22501106</t>
+          <t>22501102</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46113.83333333334</v>
+        <v>46112.9375</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.7200018763542175</v>
+        <v>0.6365575194358826</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>22501108</t>
+          <t>22501103</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46113.83333333334</v>
+        <v>46112.95833333334</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.334742397069931</v>
+        <v>0.5477316975593567</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>22501003</t>
+          <t>22501104</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46113.83333333334</v>
+        <v>46113.79166666666</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.6811369657516479</v>
+        <v>0.3167918026447296</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>22501109</t>
+          <t>22501105</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46113.83333333334</v>
+        <v>46113.8125</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.7958841919898987</v>
+        <v>0.3006761372089386</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>22501110</t>
+          <t>22501107</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46113.875</v>
+        <v>46113.8125</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.3026004433631897</v>
+        <v>0.4533692002296448</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>22501112</t>
+          <t>22501106</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46113.91666666666</v>
+        <v>46113.83333333334</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.3299661874771118</v>
+        <v>0.7200018763542175</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>22501113</t>
+          <t>22501108</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46115.79166666666</v>
+        <v>46113.83333333334</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.5093315839767456</v>
+        <v>0.334742397069931</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>22501121</t>
+          <t>22501003</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46115.79166666666</v>
+        <v>46113.83333333334</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5254,770 +5234,770 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.7051196098327637</v>
+        <v>0.6811369657516479</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>22501120</t>
+          <t>22501109</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46115.8125</v>
+        <v>46113.83333333334</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.869844377040863</v>
+        <v>0.7958841919898987</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>22501123</t>
+          <t>22501110</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46115.8125</v>
+        <v>46113.875</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.313143253326416</v>
+        <v>0.3026004433631897</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>22501122</t>
+          <t>22501112</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46115.83333333334</v>
+        <v>46113.91666666666</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.3213936686515808</v>
+        <v>0.3299661874771118</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>22501126</t>
+          <t>22501113</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46115.83333333334</v>
+        <v>46115.79166666666</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.8550282120704651</v>
+        <v>0.7051196098327637</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>22501124</t>
+          <t>22501120</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46115.83333333334</v>
+        <v>46115.79166666666</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.236572340130806</v>
+        <v>0.5093315839767456</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>22501125</t>
+          <t>22501121</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46115.85416666666</v>
+        <v>46115.8125</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.4103548228740692</v>
+        <v>0.869844377040863</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>22501127</t>
+          <t>22501123</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46115.91666666666</v>
+        <v>46115.8125</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.7199352979660034</v>
+        <v>0.313143253326416</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>22501128</t>
+          <t>22501122</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46116.625</v>
+        <v>46115.83333333334</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.6822111010551453</v>
+        <v>0.3213936686515808</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>22501129</t>
+          <t>22501126</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46116.625</v>
+        <v>46115.83333333334</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.6619012355804443</v>
+        <v>0.236572340130806</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>22501130</t>
+          <t>22501125</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46116.79166666666</v>
+        <v>46115.83333333334</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.5364096760749817</v>
+        <v>0.8550282120704651</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>22501131</t>
+          <t>22501124</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46117.64583333334</v>
+        <v>46115.85416666666</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.4391545355319977</v>
+        <v>0.4103548228740692</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>22501133</t>
+          <t>22501127</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46117.64583333334</v>
+        <v>46115.91666666666</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.209761306643486</v>
+        <v>0.7199352979660034</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>22501134</t>
+          <t>22501128</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46117.64583333334</v>
+        <v>46116.625</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.6839718818664551</v>
+        <v>0.6619012355804443</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>22501135</t>
+          <t>22501130</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46117.64583333334</v>
+        <v>46116.625</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.6894626617431641</v>
+        <v>0.6822111010551453</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>22501132</t>
+          <t>22501129</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46117.75</v>
+        <v>46116.79166666666</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.5989465713500977</v>
+        <v>0.5364096760749817</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>22501136</t>
+          <t>22501131</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46117.79166666666</v>
+        <v>46117.64583333334</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.8973514437675476</v>
+        <v>0.209761306643486</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>22501139</t>
+          <t>22501134</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46117.79166666666</v>
+        <v>46117.64583333334</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.5532301664352417</v>
+        <v>0.6839718818664551</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>22501138</t>
+          <t>22501135</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46117.79166666666</v>
+        <v>46117.64583333334</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.6429611444473267</v>
+        <v>0.6894626617431641</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>22501137</t>
+          <t>22501132</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46117.8125</v>
+        <v>46117.64583333334</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.3314782083034515</v>
+        <v>0.4391545355319977</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>22501140</t>
+          <t>22501133</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46117.875</v>
+        <v>46117.75</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.2489812076091766</v>
+        <v>0.5989465713500977</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>22501141</t>
+          <t>22501136</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46117.91666666666</v>
+        <v>46117.79166666666</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.4032554924488068</v>
+        <v>0.6429611444473267</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>22501142</t>
+          <t>22501137</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46118.79166666666</v>
+        <v>46117.79166666666</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.5972306132316589</v>
+        <v>0.8973514437675476</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>22501143</t>
+          <t>22501139</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46118.79166666666</v>
+        <v>46117.79166666666</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
           <t>Orlando Magic</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.2161738723516464</v>
+        <v>0.5532301664352417</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -6026,875 +6006,875 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>22501144</t>
+          <t>22501138</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46118.83333333334</v>
+        <v>46117.8125</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.6878817677497864</v>
+        <v>0.3314782083034515</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>22501146</t>
+          <t>22501140</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46118.83333333334</v>
+        <v>46117.875</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.3576884865760803</v>
+        <v>0.2489812076091766</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>22501145</t>
+          <t>22501141</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46118.875</v>
+        <v>46117.91666666666</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>0.5550410151481628</v>
+        <v>0.4032554924488068</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>22501147</t>
+          <t>22501142</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46119.79166666666</v>
+        <v>46118.79166666666</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>0.3282864689826965</v>
+        <v>0.5972306132316589</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>22501148</t>
+          <t>22501143</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46119.8125</v>
+        <v>46118.79166666666</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>0.8373758792877197</v>
+        <v>0.2161738723516464</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>22501151</t>
+          <t>22501144</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46119.8125</v>
+        <v>46118.83333333334</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>0.6930505633354187</v>
+        <v>0.6878817677497864</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>22501149</t>
+          <t>22501146</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46119.8125</v>
+        <v>46118.83333333334</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>0.5698964595794678</v>
+        <v>0.3576884865760803</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>22501150</t>
+          <t>22501145</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46119.83333333334</v>
+        <v>46118.875</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>0.6395388245582581</v>
+        <v>0.5550410151481628</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>22501152</t>
+          <t>22501147</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46119.83333333334</v>
+        <v>46119.79166666666</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>0.4932611286640167</v>
+        <v>0.3282864689826965</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>22501153</t>
+          <t>22501148</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46119.91666666666</v>
+        <v>46119.8125</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>0.6486186981201172</v>
+        <v>0.8373758792877197</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>22501154</t>
+          <t>22501151</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46119.9375</v>
+        <v>46119.8125</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>0.484617680311203</v>
+        <v>0.5698964595794678</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>22501155</t>
+          <t>22501150</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46119.9375</v>
+        <v>46119.8125</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>0.8861657381057739</v>
+        <v>0.6930505633354187</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>22501156</t>
+          <t>22501149</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46119.95833333334</v>
+        <v>46119.83333333334</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>0.4802132546901703</v>
+        <v>0.4932611286640167</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>22501157</t>
+          <t>22501153</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46120.79166666666</v>
+        <v>46119.83333333334</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>0.5356937646865845</v>
+        <v>0.6395388245582581</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>22501158</t>
+          <t>22501152</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46120.79166666666</v>
+        <v>46119.91666666666</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>0.4664558172225952</v>
+        <v>0.6486186981201172</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>22501159</t>
+          <t>22501154</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46120.79166666666</v>
+        <v>46119.9375</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>0.6002041697502136</v>
+        <v>0.484617680311203</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>22501160</t>
+          <t>22501155</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46120.875</v>
+        <v>46119.9375</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>0.8839766979217529</v>
+        <v>0.8861657381057739</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>22501162</t>
+          <t>22501156</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46120.89583333334</v>
+        <v>46119.95833333334</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>0.5398016571998596</v>
+        <v>0.4802132546901703</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>22501161</t>
+          <t>22501157</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46120.91666666666</v>
+        <v>46120.79166666666</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>0.3676699697971344</v>
+        <v>0.5356937646865845</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>22501163</t>
+          <t>22501158</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46120.91666666666</v>
+        <v>46120.79166666666</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>0.73008793592453</v>
+        <v>0.6002041697502136</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>22501164</t>
+          <t>22501160</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46121.79166666666</v>
+        <v>46120.79166666666</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>0.7684751152992249</v>
+        <v>0.4664558172225952</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>22501165</t>
+          <t>22501159</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46121.79166666666</v>
+        <v>46120.875</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>0.2770043313503265</v>
+        <v>0.8839766979217529</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>22501166</t>
+          <t>22501162</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46121.8125</v>
+        <v>46120.89583333334</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>0.4195958077907562</v>
+        <v>0.5398016571998596</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>22501167</t>
+          <t>22501161</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46121.8125</v>
+        <v>46120.91666666666</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>0.3564230799674988</v>
+        <v>0.3676699697971344</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>22501168</t>
+          <t>22501163</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46121.83333333334</v>
+        <v>46120.91666666666</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>0.6835659146308899</v>
+        <v>0.73008793592453</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>22501169</t>
+          <t>22501164</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46121.91666666666</v>
+        <v>46121.79166666666</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>0.3815212249755859</v>
+        <v>0.2770043313503265</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>22501170</t>
+          <t>22501166</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46122.79166666666</v>
+        <v>46121.79166666666</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6904,480 +6884,645 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>0.4738925993442535</v>
+        <v>0.7684751152992249</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>22501172</t>
+          <t>22501165</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46122.79166666666</v>
+        <v>46121.8125</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>0.672922670841217</v>
+        <v>0.4195958077907562</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>22501173</t>
+          <t>22501167</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46122.79166666666</v>
+        <v>46121.8125</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>0.5150246024131775</v>
+        <v>0.3564230799674988</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>22501171</t>
+          <t>22501168</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46122.8125</v>
+        <v>46121.83333333334</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>0.9048323035240173</v>
+        <v>0.6835659146308899</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>22501174</t>
+          <t>22501169</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46122.8125</v>
+        <v>46121.91666666666</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>0.535803496837616</v>
+        <v>0.3815212249755859</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>22501175</t>
+          <t>22501170</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46122.8125</v>
+        <v>46122.79166666666</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>0.5096167325973511</v>
+        <v>0.4738925993442535</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>New York Knicks</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>22501176</t>
+          <t>22501172</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46122.83333333334</v>
+        <v>46122.79166666666</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>0.111219123005867</v>
+        <v>0.5150246024131775</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>22501177</t>
+          <t>22501171</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46122.83333333334</v>
+        <v>46122.79166666666</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>0.7083379030227661</v>
+        <v>0.672922670841217</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>22501179</t>
+          <t>22501173</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46122.83333333334</v>
+        <v>46122.8125</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>0.8614312410354614</v>
+        <v>0.535803496837616</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>22501180</t>
+          <t>22501175</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46122.875</v>
+        <v>46122.8125</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>0.6415862441062927</v>
+        <v>0.9048323035240173</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>22501182</t>
+          <t>22501174</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46122.89583333334</v>
+        <v>46122.8125</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>0.6991291046142578</v>
+        <v>0.5096167325973511</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>22501178</t>
+          <t>22501176</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46122.89583333334</v>
+        <v>46122.83333333334</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>0.3756789565086365</v>
+        <v>0.111219123005867</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>22501181</t>
+          <t>22501177</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46122.91666666666</v>
+        <v>46122.83333333334</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>0.4845962822437286</v>
+        <v>0.7083379030227661</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>22501184</t>
+          <t>22501179</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46122.91666666666</v>
+        <v>46122.83333333334</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>0.6735097765922546</v>
+        <v>0.8614312410354614</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>22501183</t>
+          <t>22501180</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
+        <v>46122.875</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>0.6415862441062927</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>22501182</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>46122.89583333334</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>0.6991291046142578</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>22501178</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>46122.89583333334</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>0.3756789565086365</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>22501181</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>46122.91666666666</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>0.4845962822437286</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>22501184</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>46122.91666666666</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>0.6735097765922546</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>22501183</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
         <v>46122.9375</v>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="B216" t="inlineStr">
         <is>
           <t>Los Angeles Lakers</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
+      <c r="C216" t="inlineStr">
         <is>
           <t>Phoenix Suns</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
+      <c r="D216" t="inlineStr">
         <is>
           <t>Los Angeles Lakers</t>
         </is>
       </c>
-      <c r="E211" t="n">
+      <c r="E216" t="n">
         <v>0.5701608061790466</v>
       </c>
-      <c r="F211" t="inlineStr">
+      <c r="F216" t="inlineStr">
         <is>
           <t>Los Angeles Lakers</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
+      <c r="G216" t="inlineStr">
         <is>
           <t>22501185</t>
         </is>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G227"/>
+  <dimension ref="A1:G230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -598,29 +598,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.646850802</v>
+        <v>0.297013835</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>22500960</v>
+        <v>22500954</v>
       </c>
     </row>
     <row r="8">
@@ -629,29 +629,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.654368185</v>
+        <v>0.749628073</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>22500953</v>
+        <v>22500958</v>
       </c>
     </row>
     <row r="9">
@@ -660,29 +660,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.8596300650000001</v>
+        <v>0.859049225</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>22500956</v>
+        <v>22500957</v>
       </c>
     </row>
     <row r="10">
@@ -691,29 +691,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.631213677</v>
+        <v>0.847037727</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>22500959</v>
+        <v>22500955</v>
       </c>
     </row>
     <row r="11">
@@ -722,28 +722,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Dallas Mavericks</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.654368189</v>
+        <v>0.641633512</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>22501111</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -751,29 +753,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.847037727</v>
+        <v>0.631213677</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>22500955</v>
+        <v>22500959</v>
       </c>
     </row>
     <row r="13">
@@ -782,29 +784,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.859049225</v>
+        <v>0.8596300650000001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>22500957</v>
+        <v>22500956</v>
       </c>
     </row>
     <row r="14">
@@ -813,29 +815,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.641633512</v>
+        <v>0.654368185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dallas Mavericks</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>22501111</v>
+        <v>22500953</v>
       </c>
     </row>
     <row r="15">
@@ -844,29 +846,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.749628073</v>
+        <v>0.646850802</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>22500958</v>
+        <v>22500960</v>
       </c>
     </row>
     <row r="16">
@@ -875,30 +877,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.297013835</v>
+        <v>0.654368189</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>22500954</v>
-      </c>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1154,29 +1154,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brooklyn Nets</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.577502131</v>
+        <v>0.5777215959999999</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>22500969</v>
+        <v>22500975</v>
       </c>
     </row>
     <row r="26">
@@ -1185,29 +1185,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.652437568</v>
+        <v>0.652546704</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>22500973</v>
+        <v>22500974</v>
       </c>
     </row>
     <row r="27">
@@ -1216,29 +1216,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.842924058</v>
+        <v>0.499302298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>22500970</v>
+        <v>22500972</v>
       </c>
     </row>
     <row r="28">
@@ -1247,29 +1247,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.499302298</v>
+        <v>0.857488632</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>22500972</v>
+        <v>22500971</v>
       </c>
     </row>
     <row r="29">
@@ -1278,29 +1278,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.5777215959999999</v>
+        <v>0.652437568</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>22500975</v>
+        <v>22500973</v>
       </c>
     </row>
     <row r="30">
@@ -1309,29 +1309,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Brooklyn Nets</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.857488632</v>
+        <v>0.577502131</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>22500971</v>
+        <v>22500969</v>
       </c>
     </row>
     <row r="31">
@@ -1340,29 +1340,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.652546704</v>
+        <v>0.842924058</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>22500974</v>
+        <v>22500970</v>
       </c>
     </row>
     <row r="32">
@@ -1619,29 +1619,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.657446146</v>
+        <v>0.278542638</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Denver Nuggets</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>22500997</v>
+        <v>22500992</v>
       </c>
     </row>
     <row r="41">
@@ -1650,29 +1650,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sacramento Kings</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.388431966</v>
+        <v>0.513797641</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>22500998</v>
+        <v>22500996</v>
       </c>
     </row>
     <row r="42">
@@ -1681,29 +1681,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.266292274</v>
+        <v>0.5540216569999999</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>22500995</v>
+        <v>22500991</v>
       </c>
     </row>
     <row r="43">
@@ -1712,29 +1712,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.5540216569999999</v>
+        <v>0.155862674</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>22500991</v>
+        <v>22500993</v>
       </c>
     </row>
     <row r="44">
@@ -1743,29 +1743,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Sacramento Kings</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.155862674</v>
+        <v>0.388431966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>22500993</v>
+        <v>22500998</v>
       </c>
     </row>
     <row r="45">
@@ -1774,29 +1774,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.513797641</v>
+        <v>0.657446146</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>22500996</v>
+        <v>22500997</v>
       </c>
     </row>
     <row r="46">
@@ -1805,29 +1805,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.278542638</v>
+        <v>0.266292274</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>22500992</v>
+        <v>22500995</v>
       </c>
     </row>
     <row r="47">
@@ -2177,29 +2177,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.688686788</v>
+        <v>0.462356299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>22501012</v>
+        <v>22501011</v>
       </c>
     </row>
     <row r="59">
@@ -2208,29 +2208,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.499740869</v>
+        <v>0.589850008</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>22501010</v>
+        <v>22501013</v>
       </c>
     </row>
     <row r="60">
@@ -2239,29 +2239,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.589850008</v>
+        <v>0.688686788</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>22501013</v>
+        <v>22501012</v>
       </c>
     </row>
     <row r="61">
@@ -2270,29 +2270,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.462356299</v>
+        <v>0.499740869</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>22501011</v>
+        <v>22501010</v>
       </c>
     </row>
     <row r="62">
@@ -2580,29 +2580,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>New Orleans Pelicans</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.5733375550000001</v>
+        <v>0.431459397</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>22501024</v>
+        <v>22501025</v>
       </c>
     </row>
     <row r="72">
@@ -2611,29 +2611,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>New Orleans Pelicans</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.431459397</v>
+        <v>0.852381468</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>22501025</v>
+        <v>22501023</v>
       </c>
     </row>
     <row r="73">
@@ -2642,29 +2642,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.852381468</v>
+        <v>0.5733375550000001</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>22501023</v>
+        <v>22501024</v>
       </c>
     </row>
     <row r="74">
@@ -3014,29 +3014,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.255796134</v>
+        <v>0.520097673</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>22501040</v>
+        <v>22501041</v>
       </c>
     </row>
     <row r="86">
@@ -3045,29 +3045,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.607815981</v>
+        <v>0.713783443</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>22501038</v>
+        <v>22501039</v>
       </c>
     </row>
     <row r="87">
@@ -3076,29 +3076,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.713783443</v>
+        <v>0.255796134</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>22501039</v>
+        <v>22501040</v>
       </c>
     </row>
     <row r="88">
@@ -3107,29 +3107,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.520097673</v>
+        <v>0.607815981</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>22501041</v>
+        <v>22501038</v>
       </c>
     </row>
     <row r="89">
@@ -3448,29 +3448,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Indiana Pacers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.35402301</v>
+        <v>0.588240087</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Los Angeles Lakers</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>22501052</v>
+        <v>22501051</v>
       </c>
     </row>
     <row r="100">
@@ -3479,29 +3479,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.588240087</v>
+        <v>0.734588325</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>22501051</v>
+        <v>22501053</v>
       </c>
     </row>
     <row r="101">
@@ -3510,29 +3510,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Indiana Pacers</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.734588325</v>
+        <v>0.35402301</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>22501053</v>
+        <v>22501052</v>
       </c>
     </row>
     <row r="102">
@@ -4378,29 +4378,29 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Chicago Bulls</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.78594631</v>
+        <v>0.184682012</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>San Antonio Spurs</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>22501094</v>
+        <v>22501093</v>
       </c>
     </row>
     <row r="130">
@@ -4409,29 +4409,29 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>Chicago Bulls</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.184682012</v>
+        <v>0.78594631</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Phoenix Suns</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>22501093</v>
+        <v>22501094</v>
       </c>
     </row>
     <row r="131">
@@ -4812,29 +4812,29 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.4533692</v>
+        <v>0.300676137</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>22501106</v>
+        <v>22501107</v>
       </c>
     </row>
     <row r="144">
@@ -4843,29 +4843,29 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.300676137</v>
+        <v>0.4533692</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>22501107</v>
+        <v>22501106</v>
       </c>
     </row>
     <row r="145">
@@ -5184,29 +5184,29 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Milwaukee Bucks</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Utah Jazz</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.321393669</v>
+        <v>0.855028212</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Boston Celtics</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>22501126</v>
+        <v>22501124</v>
       </c>
     </row>
     <row r="156">
@@ -5215,29 +5215,29 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Memphis Grizzlies</t>
+          <t>Milwaukee Bucks</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.23657234</v>
+        <v>0.321393669</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="G156" t="n">
-        <v>22501125</v>
+        <v>22501126</v>
       </c>
     </row>
     <row r="157">
@@ -5246,29 +5246,29 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Memphis Grizzlies</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Utah Jazz</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.855028212</v>
+        <v>0.23657234</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="G157" t="n">
-        <v>22501124</v>
+        <v>22501125</v>
       </c>
     </row>
     <row r="158">
@@ -6641,29 +6641,29 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Washington Wizards</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>0.473892599</v>
+        <v>0.672922671</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="G202" t="n">
-        <v>22501172</v>
+        <v>22501173</v>
       </c>
     </row>
     <row r="203">
@@ -6672,29 +6672,29 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Washington Wizards</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>0.515024602</v>
+        <v>0.473892599</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Detroit Pistons</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="G203" t="n">
-        <v>22501171</v>
+        <v>22501172</v>
       </c>
     </row>
     <row r="204">
@@ -6703,29 +6703,29 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>0.672922671</v>
+        <v>0.515024602</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="G204" t="n">
-        <v>22501173</v>
+        <v>22501171</v>
       </c>
     </row>
     <row r="205">
@@ -7435,6 +7435,99 @@
       </c>
       <c r="G227" t="n">
         <v>42520038</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>46136.79166666666</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>0.4534924924373627</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="G228" t="n">
+        <v>42520014</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>46136.83333333334</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>0.6931077837944031</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="G229" t="n">
+        <v>42520044</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>46136.91666666666</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>0.511742115020752</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>42520032</v>
       </c>
     </row>
   </sheetData>

--- a/output/all_predictions.xlsx
+++ b/output/all_predictions.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -417,48 +429,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Predicted Winner</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>probability_home_win</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>gameId</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Actual Winner</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>market_prob_home_win</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>46159.83333333334</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -477,14 +494,123 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.6666666865348816</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>42500207</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6279</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46160.85416666666</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8002</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>42500311</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6778999999999999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46161.83333333334</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>42500301</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0.6841</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46162.85416666666</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6623931623931624</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>42500312</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
